--- a/data_extactor/batch/551_600.xlsx
+++ b/data_extactor/batch/551_600.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sarbazi\code\sarbazi\data_extactor\batch\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{110671F1-E021-4F77-B5C5-B62A397E5D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,1579 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="522">
+  <si>
+    <t>33-9091.00</t>
+  </si>
+  <si>
+    <t>Crossing Guards and Flaggers</t>
+  </si>
+  <si>
+    <t>Adult Crossing Guard | Community Service Officer | Crossing Guard | Road Crossing Guard | School Crossing Guard | Substitute Crossing Guard</t>
+  </si>
+  <si>
+    <t>Microsoft Word | Payroll software | Visual Computer Solutions Crossing Guard Scheduling</t>
+  </si>
+  <si>
+    <t>Speaking</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Customer and Personal Service | English Language</t>
+  </si>
+  <si>
+    <t>Oral Expression | Problem Sensitivity | Oral Comprehension | Speech Clarity | Far Vision | Selective Attention | Speech Recognition | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Spend Time Standing | Deal With External Customers or the Public in General | Exposed to Very Hot or Cold Temperatures | Exposed to Contaminants | Freedom to Make Decisions | Frequency of Decision Making | Physical Proximity | Contact With Others | Spend Time Walking or Running | Consequence of Error | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Importance of Being Exact or Accurate | Spend Time Making Repetitive Motions | Determine Tasks, Priorities and Goals | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Air Traffic Controllers | Bridge and Lock Tenders | Bus Drivers, Transit and Intercity | Dispatchers, Except Police, Fire, and Ambulance | Highway Maintenance Workers | Lifeguards, Ski Patrol, and Other Recreational Protective Service Workers | Locomotive Engineers | Parking Enforcement Workers | Passenger Attendants | Police and Sheriff's Patrol Officers | Public Safety Telecommunicators | Rail Yard Engineers, Dinkey Operators, and Hostlers | Railroad Brake, Signal, and Switch Operators and Locomotive Firers | Railroad Conductors and Yardmasters | School Bus Monitors | Security Guards | Subway and Streetcar Operators | Traffic Technicians | Transit and Railroad Police | Transportation Security Screeners</t>
+  </si>
+  <si>
+    <t>Guide or control vehicular or pedestrian traffic at such places as streets, schools, railroad crossings, or construction sites.</t>
+  </si>
+  <si>
+    <t>Communicate traffic and crossing rules and other information to students and adults. | Direct or escort pedestrians across streets, stopping traffic, as necessary. | Direct traffic movement or warn of hazards, using signs, flags, lanterns, and hand signals. | Discuss traffic routing plans and control-point locations with superiors. | Distribute traffic control signs and markers at designated points. | Guide or control vehicular or pedestrian traffic at such places as street and railroad crossings and construction sites. | Inform drivers of detour routes through construction sites. | Learn the location and purpose of street traffic signs within assigned patrol areas. | Monitor traffic flow to locate safe gaps through which pedestrians can cross streets. | Record license numbers of vehicles disregarding traffic signals, and report infractions to appropriate authorities. | Report unsafe behavior of children to school officials. | Stop speeding vehicles to warn drivers of traffic laws.</t>
+  </si>
+  <si>
+    <t>33-9092.00</t>
+  </si>
+  <si>
+    <t>Lifeguards, Ski Patrol, and Other Recreational Protective Service Workers</t>
+  </si>
+  <si>
+    <t>Beach Attendant | Beach Lifeguard | Lifeguard | Marine Safety Officer | Ocean Lifeguard | Ocean Lifeguard Specialist | Pool Attendant | Pool Lifeguard | Ski Patrol Paramedic | Ski Patroller</t>
+  </si>
+  <si>
+    <t>GroupMe | Microsoft Excel | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Monitoring | Speaking | Learning Strategies | Active Listening | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Public Safety and Security | English Language | Education and Training | Medicine and Dentistry</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Far Vision | Oral Expression | Oral Comprehension | Selective Attention | Speech Clarity | Speech Recognition | Flexibility of Closure | Deductive Reasoning | Perceptual Speed | Speed of Closure | Information Ordering | Inductive Reasoning | Near Vision | Stamina | Trunk Strength | Time Sharing</t>
+  </si>
+  <si>
+    <t>Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Health and Safety of Other Workers | E-Mail | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Consequence of Error | Physical Proximity | Deal With External Customers or the Public in General | Indoors, Environmentally Controlled | Freedom to Make Decisions | Outdoors, Exposed to All Weather Conditions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Telephone Conversations | Exposed to Very Hot or Cold Temperatures</t>
+  </si>
+  <si>
+    <t>Ambulance Drivers and Attendants, Except Emergency Medical Technicians | Amusement and Recreation Attendants | Athletic Trainers | Commercial Divers | Emergency Medical Technicians | Exercise Trainers and Group Fitness Instructors | Fire Inspectors and Investigators | Firefighters | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Firefighting and Prevention Workers | First-Line Supervisors of Personal Service Workers | Forest Fire Inspectors and Prevention Specialists | Health and Safety Engineers, Except Mining Safety Engineers and Inspectors | Occupational Health and Safety Specialists | Occupational Health and Safety Technicians | Orderlies | Paramedics | Parking Enforcement Workers | Recreation Workers | Security Guards</t>
+  </si>
+  <si>
+    <t>Monitor recreational areas, such as pools, beaches, or ski slopes, to provide assistance and protection to participants.</t>
+  </si>
+  <si>
+    <t>Complete and maintain records of weather and beach conditions, emergency medical treatments performed, and other relevant incident information. | Contact emergency medical personnel in case of serious injury. | Examine injured persons and administer first aid or cardiopulmonary resuscitation, if necessary, using training and medical supplies and equipment. | Inspect recreational equipment, such as rope tows, T-bars, J-bars, or chair lifts, for safety hazards and damage or wear. | Inspect recreational facilities for cleanliness. | Instruct participants in skiing, swimming, or other recreational activities and provide safety precaution information. | Maintain quality of pool water by testing chemical levels. | Observe activities in assigned areas, using binoculars, to detect hazards, disturbances, or safety infractions. | Operate underwater recovery units. | Participate in recreational demonstrations to entertain resort guests. | Patrol or monitor recreational areas, such as trails, slopes, or swimming areas, on foot, in vehicles, or from towers. | Provide assistance in the safe use of equipment, such as ski lifts. | Provide assistance with staff selection, training, and supervision. | Rescue distressed persons, using rescue techniques and equipment. | Warn recreational participants of inclement weather, unsafe areas, or illegal conduct.</t>
+  </si>
+  <si>
+    <t>33-9093.00</t>
+  </si>
+  <si>
+    <t>Transportation Security Screeners</t>
+  </si>
+  <si>
+    <t>Security Screener | Transportation Security Officer (TSO)</t>
+  </si>
+  <si>
+    <t>Applicant tracking software | Email software | Linux | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Oracle Java | Oracle Taleo | Rapiscan Threat Image Projection | Slack | Web browser software</t>
+  </si>
+  <si>
+    <t>Speaking | Monitoring | Critical Thinking | Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Selective Attention | Deductive Reasoning | Oral Expression | Oral Comprehension | Flexibility of Closure | Inductive Reasoning | Speech Clarity | Speech Recognition | Near Vision | Information Ordering | Perceptual Speed | Far Vision | Category Flexibility | Written Comprehension | Multilimb Coordination | Finger Dexterity | Manual Dexterity</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Indoors, Environmentally Controlled | Dealing With Unpleasant, Angry, or Discourteous People | Work With or Contribute to a Work Group or Team | Contact With Others | Physical Proximity | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Being Exact or Accurate | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Deal With External Customers or the Public in General | Spend Time Making Repetitive Motions | Exposed to Contaminants | E-Mail | Consequence of Error | Frequency of Decision Making | Exposed to Radiation | Conflict Situations | Importance of Repeating Same Tasks | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Air Traffic Controllers | Aircraft Cargo Handling Supervisors | Airfield Operations Specialists | Baggage Porters and Bellhops | Bus Drivers, Transit and Intercity | Compliance Officers | Crossing Guards and Flaggers | Customs and Border Protection Officers | Dispatchers, Except Police, Fire, and Ambulance | First-Line Supervisors of Security Workers | Flight Attendants | Parking Enforcement Workers | Passenger Attendants | Railroad Conductors and Yardmasters | Reservation and Transportation Ticket Agents and Travel Clerks | Security Guards | Security Management Specialists | Security Managers | Subway and Streetcar Operators | Transit and Railroad Police</t>
+  </si>
+  <si>
+    <t>Conduct screening of passengers, baggage, or cargo to ensure compliance with Transportation Security Administration (TSA) regulations. May operate basic security equipment such as x-ray machines and hand wands at screening checkpoints.</t>
+  </si>
+  <si>
+    <t>Ask passengers to remove shoes and divest themselves of metal objects prior to walking through metal detectors. | Challenge suspicious people, requesting their badges and asking what their business is in a particular areas. | Check passengers' tickets to ensure that they are valid, and to determine whether passengers have designations that require special handling, such as providing photo identification. | Close entry areas following security breaches or reopen areas after receiving notification that the airport is secure. | Confiscate dangerous items and hazardous materials found in opened bags and turn them over to airlines for disposal. | Contact leads or supervisors to discuss objects of concern that are not on prohibited object lists. | Contact police directly in cases of urgent security issues, using phones or two-way radios. | Decide whether baggage that triggers alarms should be searched or should be allowed to pass through. | Direct passengers to areas where they can pick up their baggage after screening is complete. | Follow those who breach security until police or other security personnel arrive to apprehend them. | Inform other screeners when baggage should not be opened because it might contain explosives. | Inform passengers of how to mail prohibited items to themselves, or confiscate these items. | Inspect carry-on items, using x-ray viewing equipment, to determine whether items contain objects that warrant further investigation. | Inspect checked baggage for signs of tampering. | Locate suspicious bags pictured in printouts sent from remote monitoring areas, and set these bags aside for inspection. | Monitor passenger flow through screening checkpoints to ensure order and efficiency. | Notify supervisors or other appropriate personnel when security breaches occur. | Patrol work areas to detect any suspicious items. | Perform pat-down or hand-held wand searches of passengers who have triggered machine alarms, who are unable to pass through metal detectors, or who have been randomly identified for such searches. | Provide directions and respond to passenger inquiries. | Record information about any baggage that sets off alarms in monitoring equipment. | Search carry-on or checked baggage by hand when it is suspected to contain prohibited items such as weapons. | Send checked baggage through automated screening machines, and set bags aside for searching or rescreening as indicated by equipment. | Test baggage for any explosive materials, using equipment such as explosive detection machines or chemical swab systems. | View images of checked bags and cargo, using remote screening equipment, and alert baggage screeners or handlers to any possible problems. | Watch for potentially dangerous persons whose pictures are posted at checkpoints.</t>
+  </si>
+  <si>
+    <t>33-9094.00</t>
+  </si>
+  <si>
+    <t>School Bus Monitors</t>
+  </si>
+  <si>
+    <t>Bus Aide | Bus Attendant | Bus Monitor | School Bus Aide | School Bus Assistant | School Bus Attendant | School Bus Monitor | Student Transportation Aide | Bus Chaperone | Transportation Aide</t>
+  </si>
+  <si>
+    <t>Microsoft Windows | Web browser software</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Speaking | Critical Thinking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Public Safety and Security | English Language | Education and Training | Psychology | Transportation</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Near Vision | Problem Sensitivity | Information Ordering | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Selective Attention | Category Flexibility | Time Sharing | Finger Dexterity | Manual Dexterity | Far Vision | Memorization | Fluency of Ideas | Auditory Attention | Reaction Time | Static Strength</t>
+  </si>
+  <si>
+    <t>In an Enclosed Vehicle or Operate Enclosed Equipment | Contact With Others | Physical Proximity | Deal With External Customers or the Public in General | Face-to-Face Discussions with Individuals and Within Teams | Dealing With Unpleasant, Angry, or Discourteous People | Health and Safety of Other Workers | Consequence of Error | Importance of Repeating Same Tasks | Spend Time Sitting | Spend Time Standing | Frequency of Decision Making | Exposed to Whole Body Vibration | Work With or Contribute to a Work Group or Team | Time Pressure | Outdoors, Exposed to All Weather Conditions</t>
+  </si>
+  <si>
+    <t>Bus Drivers, School | Bus Drivers, Transit and Intercity | Crossing Guards and Flaggers | Dispatchers, Except Police, Fire, and Ambulance | Education Administrators, Kindergarten through Secondary | Educational, Guidance, and Career Counselors and Advisors | Elementary School Teachers, Except Special Education | Flight Attendants | Passenger Attendants | Railroad Conductors and Yardmasters | School Psychologists | Shuttle Drivers and Chauffeurs | Special Education Teachers, Elementary School | Special Education Teachers, Secondary School | Subway and Streetcar Operators | Taxi Drivers | Teaching Assistants, Preschool, Elementary, Middle, and Secondary School, Except Special Education | Teaching Assistants, Special Education | Transit and Railroad Police | Tutors</t>
+  </si>
+  <si>
+    <t>Maintain order among students on a school bus. Duties include helping students safely board and exit and communicating behavioral problems. May perform pretrip and posttrip inspections and prepare for and assist in emergency evacuations.</t>
+  </si>
+  <si>
+    <t>Announce routes or stops. | Assist children with disabilities or children with psychological, emotional, or behavioral issues with boarding and exiting the school bus. | Buckle seatbelts or fasten wheelchair tie-down straps to secure passengers for transportation. | Clean school bus interiors by picking up waste, wiping down windows, or vacuuming. | Direct students boarding and exiting the school bus. | Direct students evacuating the bus during safety drills. | Escort young children across roads or highways. | Evacuate students from the school bus in emergency situations. | Guide the driver when the bus is moving in reverse gear. | Monitor for trains at railroad crossings and signal the bus driver when it is safe to proceed. | Monitor the conduct of students to maintain discipline and safety. | Open and close school bus doors for students. | Operate a wheelchair lift to load or unload wheelchairs. | Prevent or defuse altercations between students. | Report delays, accidents, or other traffic and transportation situations to dispatchers or other bus drivers, using phones or mobile two-way radios. | Respond to students' questions, requests, or complaints. | Talk to children's parents or guardians about problematic behaviors, emotional or developmental problems, or related issues. | Write and submit reports that include data such as the number of passengers or trips, hours worked, mileage driven, or fuel consumed.</t>
+  </si>
+  <si>
+    <t>33-9099.00</t>
+  </si>
+  <si>
+    <t>Protective Service Workers, All Other</t>
+  </si>
+  <si>
+    <t>Campus Safety Officer | Court Security Officer | Fire Watch | Loss Prevention Officer | Protective Services Worker | Public Safety Officer | Safety Attendant | Security Officer | Surveillance Officer | Patrol Officer</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Word | Email software | Web browser software | Database software | Scheduling software | Microsoft Outlook | Inventory management systems | Microsoft Office software | Computerized maintenance management system CMMS | Microsoft PowerPoint</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Reading Comprehension | Critical Thinking | Monitoring | Writing</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Customer and Personal Service | Law and Government | English Language | Psychology | Computers and Electronics | Telecommunications</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Near Vision | Problem Sensitivity | Information Ordering | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Selective Attention | Category Flexibility | Time Sharing | Finger Dexterity | Manual Dexterity | Far Vision | Memorization | Fluency of Ideas | Reaction Time | Static Strength | Stamina | Auditory Attention | Depth Perception</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Deal With External Customers or the Public in General | Telephone Conversations | Consequence of Error | Frequency of Decision Making | Health and Safety of Other Workers | Physical Proximity | Dealing With Unpleasant, Angry, or Discourteous People | Dealing with Violent or Physically Aggressive People | Spend Time Standing | Spend Time Walking or Running | Exposed to Hazardous Conditions | Outdoors, Exposed to All Weather Conditions | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Time Pressure | E-Mail</t>
+  </si>
+  <si>
+    <t>Security Guards | Retail Loss Prevention Specialists | Transportation Security Screeners | Crossing Guards and Flaggers | Lifeguards, Ski Patrol, and Other Recreational Protective Service Workers | School Bus Monitors | Parking Enforcement Workers | Animal Control Workers | Gambling Surveillance Officers and Gambling Investigators | Private Detectives and Investigators | Correctional Officers and Jailers | Bailiffs | Police and Sheriff's Patrol Officers | Transit and Railroad Police | Customs and Border Protection Officers | Fish and Game Wardens | Firefighters | First-Line Supervisors of Security Workers | First-Line Supervisors of Protective Service Workers, All Other | Public Safety Telecommunicators</t>
+  </si>
+  <si>
+    <t>All protective service workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Perform protective service duties in roles not classified separately. | Patrol assigned areas on foot or by vehicle to deter and detect violations. | Monitor surveillance cameras, alarms, and access control systems. | Control entry and exit of persons and vehicles and verify credentials. | Respond to alarms, disturbances, and emergency situations. | Detain individuals suspected of violations pending arrival of authorities. | Provide directions, assistance, and information to the public. | Write incident reports, activity logs, and daily patrol records. | Inspect facilities for safety hazards, unsecured areas, and equipment faults. | Enforce rules, regulations, and organizational policies. | Coordinate with law enforcement and emergency responders as needed. | Escort persons, valuables, and deposits to secure locations. | Administer first aid and summon medical assistance when required. | Test and maintain security and emergency equipment.</t>
+  </si>
+  <si>
+    <t>33-9099.02</t>
+  </si>
+  <si>
+    <t>Retail Loss Prevention Specialists</t>
+  </si>
+  <si>
+    <t>Asset Protection Associate (APA) | Loss Prevention Agent | Loss Prevention Associate (LPA) | Loss Prevention Detective | Loss Prevention Investigator | Loss Prevention Officer | Loss Prevention Specialist | Retail Asset Protection Specialist</t>
+  </si>
+  <si>
+    <t>Aspect Loss Prevention Aspect EliteLP | Case management system software | Database software | Enterprise application integration EAI software | Epicor Loss Prevention | McAfee | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | NortonLifeLock cybersecurity software | Structured query language SQL</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Speaking | Monitoring | Active Listening | Active Learning | Reading Comprehension | Writing</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | English Language | Law and Government | Customer and Personal Service | Education and Training | Administration and Management | Computers and Electronics | Personnel and Human Resources | Administrative | Mathematics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Problem Sensitivity | Oral Expression | Deductive Reasoning | Inductive Reasoning | Speech Recognition | Speech Clarity | Written Comprehension | Near Vision | Selective Attention | Far Vision | Information Ordering | Flexibility of Closure | Written Expression | Category Flexibility</t>
+  </si>
+  <si>
+    <t>Contact With Others | Work With or Contribute to a Work Group or Team | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Freedom to Make Decisions | E-Mail | Importance of Being Exact or Accurate | Deal With External Customers or the Public in General | Impact of Decisions on Co-workers or Company Results | Frequency of Decision Making | Physical Proximity | Health and Safety of Other Workers | Determine Tasks, Priorities and Goals | Importance of Repeating Same Tasks | Dealing With Unpleasant, Angry, or Discourteous People | Conflict Situations | Coordinate or Lead Others in Accomplishing Work Activities | Level of Competition | Consequence of Error</t>
+  </si>
+  <si>
+    <t>Business Continuity Planners | Compliance Managers | Detectives and Criminal Investigators | Emergency Management Directors | Financial Risk Specialists | First-Line Supervisors of Security Workers | Fraud Examiners, Investigators and Analysts | Gambling Surveillance Officers and Gambling Investigators | Health and Safety Engineers, Except Mining Safety Engineers and Inspectors | Information Security Analysts | Intelligence Analysts | Loss Prevention Managers | Management Analysts | Occupational Health and Safety Specialists | Occupational Health and Safety Technicians | Penetration Testers | Private Detectives and Investigators | Security Guards | Security Management Specialists | Security Managers</t>
+  </si>
+  <si>
+    <t>Implement procedures and systems to prevent merchandise loss. Conduct audits and investigations of employee activity. May assist in developing policies, procedures, and systems for safeguarding assets.</t>
+  </si>
+  <si>
+    <t>Apprehend shoplifters in accordance with guidelines. | Collaborate with law enforcement agencies to report or investigate crimes. | Conduct employee background investigations and review reports with operational or human resources managers. | Conduct store audits to identify problem areas or procedural deficiencies. | Coordinate with risk management, human resources, or other departments to assist in company programs, investigations, or training. | Direct work of contract security officers or other loss prevention agents. | Identify and report merchandise or stock shortages. | Identify and report safety concerns to maintain a safe shopping and working environment. | Implement or monitor processes to reduce property or financial losses. | Inspect buildings, equipment, or access points to determine security risks. | Investigate known or suspected internal theft, external theft, or vendor fraud. | Maintain documentation or reports on security-related incidents or investigations. | Monitor compliance with standard operating procedures for loss prevention, physical security, or risk management. | Perform covert surveillance of areas susceptible to loss, such loading docks, distribution centers, or warehouses. | Prepare written reports on investigations. | Recommend methods to reduce potential financial fraud losses. | Recommend new or improved processes or equipment to reduce risk exposure. | Respond to critical incidents, such as catastrophic events, violent weather, or civil disorders. | Testify in civil or criminal court proceedings. | Train establishment personnel in loss prevention activities. | Verify proper functioning of physical security systems, such as closed-circuit televisions, alarms, sensor tag systems, or locks.</t>
+  </si>
+  <si>
+    <t>35-1011.00</t>
+  </si>
+  <si>
+    <t>Chefs and Head Cooks</t>
+  </si>
+  <si>
+    <t>Banquet Chef | Chef | Cook | Executive Chef (Ex Chef) | Executive Pastry Chef | Executive Sous Chef | Food and Beverage Director | Head Cook | Kitchen Manager | Sous Chef</t>
+  </si>
+  <si>
+    <t>ADP eTIME | Axxya Systems Nutritionist Pro | Barrington Software CookenPro Commercial | CostGuard | Culinary Software Services ChefTec | Delphi Technology | EGS CALCMENU | Email software | Enggist &amp; Grandjean EGS F&amp;B Control | Facebook | GNOME Gnutrition | Google Sheets | GroupMe | IPro Restaurant Inventory, Recipe &amp; Menu Software | Menu planning software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Nutrition analysis software | ReServe Interactive | Sage MAS 90 ERP | SoftCafe MenuPro</t>
+  </si>
+  <si>
+    <t>Monitoring | Speaking | Critical Thinking | Active Listening | Reading Comprehension | Active Learning | Learning Strategies | Writing | Mathematics</t>
+  </si>
+  <si>
+    <t>Food Production | Production and Processing | Customer and Personal Service | Personnel and Human Resources | Administration and Management | Mathematics | Education and Training | English Language | Economics and Accounting | Administrative</t>
+  </si>
+  <si>
+    <t>Oral Expression | Problem Sensitivity | Oral Comprehension | Information Ordering | Speech Clarity | Deductive Reasoning | Inductive Reasoning | Near Vision | Speech Recognition | Written Comprehension | Originality | Selective Attention | Fluency of Ideas | Category Flexibility | Visualization | Time Sharing | Trunk Strength | Finger Dexterity | Manual Dexterity | Arm-Hand Steadiness | Number Facility | Written Expression | Far Vision | Mathematical Reasoning | Visual Color Discrimination | Perceptual Speed | Memorization | Extent Flexibility</t>
+  </si>
+  <si>
+    <t>E-Mail | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Time Pressure | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Frequency of Decision Making | Contact With Others | Telephone Conversations | Exposed to Minor Burns, Cuts, Bites, or Stings | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Work With or Contribute to a Work Group or Team | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Exposed to Very Hot or Cold Temperatures | Spend Time Making Repetitive Motions | Physical Proximity | Impact of Decisions on Co-workers or Company Results | Health and Safety of Other Workers | Work Outcomes and Results of Other Workers | Exposed to Hazardous Equipment | Level of Competition | Dealing With Unpleasant, Angry, or Discourteous People | Coordinate or Lead Others in Accomplishing Work Activities | Importance of Repeating Same Tasks | Written Letters and Memos | Deal With External Customers or the Public in General | Exposed to Contaminants | Conflict Situations | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate</t>
+  </si>
+  <si>
+    <t>Bakers | Baristas | Butchers and Meat Cutters | Cooks, Fast Food | Cooks, Institution and Cafeteria | Cooks, Private Household | Cooks, Restaurant | Cooks, Short Order | Dietetic Technicians | Dining Room and Cafeteria Attendants and Bartender Helpers | Fast Food and Counter Workers | First-Line Supervisors of Food Preparation and Serving Workers | Food Batchmakers | Food Cooking Machine Operators and Tenders | Food Preparation Workers | Food Servers, Nonrestaurant | Food Service Managers | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Hosts and Hostesses, Restaurant, Lounge, and Coffee Shop | Waiters and Waitresses</t>
+  </si>
+  <si>
+    <t>Direct and may participate in the preparation, seasoning, and cooking of salads, soups, fish, meats, vegetables, desserts, or other foods. May plan and price menu items, order supplies, and keep records and accounts.</t>
+  </si>
+  <si>
+    <t>Analyze recipes to assign prices to menu items, based on food, labor, and overhead costs. | Arrange for equipment purchases or repairs. | Check the quality of raw or cooked food products to ensure that standards are met. | Check the quantity and quality of received products. | Collaborate with other personnel to plan and develop recipes or menus, taking into account such factors as seasonal availability of ingredients or the likely number of customers. | Coordinate planning, budgeting, or purchasing for all the food operations within establishments such as clubs, hotels, or restaurant chains. | Demonstrate new cooking techniques or equipment to staff. | Determine how food should be presented and create decorative food displays. | Determine production schedules and staff requirements necessary to ensure timely delivery of services. | Estimate amounts and costs of required supplies, such as food and ingredients. | Inspect supplies, equipment, or work areas to ensure conformance to established standards. | Instruct cooks or other workers in the preparation, cooking, garnishing, or presentation of food. | Meet with customers to discuss menus for special occasions, such as weddings, parties, or banquets. | Meet with sales representatives to negotiate prices or order supplies. | Monitor sanitation practices to ensure that employees follow standards and regulations. | Order or requisition food or other supplies needed to ensure efficient operation. | Plan, direct, or supervise food preparation or cooking activities of multiple kitchens or restaurants in an establishment such as a restaurant chain, hospital, or hotel. | Prepare and cook foods of all types, either on a regular basis or for special guests or functions. | Record production or operational data on specified forms. | Recruit and hire staff, such as cooks and other kitchen workers. | Supervise or coordinate activities of cooks or workers engaged in food preparation.</t>
+  </si>
+  <si>
+    <t>35-1012.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Food Preparation and Serving Workers</t>
+  </si>
+  <si>
+    <t>Cafeteria Manager | Dietary Supervisor | Dining Services Director | Food Production Supervisor | Food Service Supervisor | Food and Beverage Director | Food and Nutrition Services Supervisor | Kitchen Manager | Kitchen Supervisor | Restaurant Manager</t>
+  </si>
+  <si>
+    <t>ADP Workforce Now | CBORD Foodservice Suite | CBORD Group Menu Management System | CaterPro | Compeat Restaurant Accounting Systems | Compris Advanced Manager's Workstation | Compris software | CostGuard | Delphi Technology | Evernote | IBM Domino | Intuit QuickBooks Point of Sale | MICROS Systems HSI Profits Series | Microsoft Dynamics | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft Word | NCR Advanced Checkout Solution | NCR NeighborhoodPOS | Ordering and purchasing software | ParTech PixelPoint POS | Quizlet | Regnow Chrysanth Inventory Manager | Restaurant Operations &amp; Management Spreadsheet Library | Sage 50 Accounting | SoftCafe ScheduleWriter | Staff scheduling software | The General Store</t>
+  </si>
+  <si>
+    <t>Speaking | Monitoring | Active Listening | Reading Comprehension | Critical Thinking | Learning Strategies | Active Learning | Mathematics | Writing</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Administration and Management | Food Production | English Language | Production and Processing | Sales and Marketing | Education and Training | Personnel and Human Resources</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Deductive Reasoning | Speech Clarity | Speech Recognition | Written Comprehension | Near Vision | Trunk Strength | Time Sharing | Selective Attention | Visualization | Category Flexibility | Information Ordering | Inductive Reasoning | Fluency of Ideas | Written Expression | Far Vision</t>
+  </si>
+  <si>
+    <t>Telephone Conversations | Indoors, Environmentally Controlled | Contact With Others | Work With or Contribute to a Work Group or Team | Physical Proximity | Importance of Being Exact or Accurate | Deal With External Customers or the Public in General | Coordinate or Lead Others in Accomplishing Work Activities | Face-to-Face Discussions with Individuals and Within Teams | Health and Safety of Other Workers | Spend Time Standing | Freedom to Make Decisions | Spend Time Making Repetitive Motions | Work Outcomes and Results of Other Workers | Determine Tasks, Priorities and Goals | Importance of Repeating Same Tasks | Public Speaking</t>
+  </si>
+  <si>
+    <t>Chefs and Head Cooks | Dining Room and Cafeteria Attendants and Bartender Helpers | Fast Food and Counter Workers | First-Line Supervisors of Construction Trades and Extraction Workers | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Farming, Fishing, and Forestry Workers | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Landscaping, Lawn Service, and Groundskeeping Workers | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Mechanics, Installers, and Repairers | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Office and Administrative Support Workers | First-Line Supervisors of Passenger Attendants | First-Line Supervisors of Personal Service Workers | First-Line Supervisors of Production and Operating Workers | First-Line Supervisors of Retail Sales Workers | Food Preparation Workers | Food Service Managers | General and Operations Managers</t>
+  </si>
+  <si>
+    <t>Directly supervise and coordinate activities of workers engaged in preparing and serving food.</t>
+  </si>
+  <si>
+    <t>Analyze operational problems, such as theft and wastage, and establish procedures to alleviate these problems. | Assess nutritional needs of patients, plan special menus, supervise the assembly of regular and special diet trays, and oversee the delivery of food trolleys to hospital patients. | Assign duties, responsibilities, and work stations to employees in accordance with work requirements. | Compile and balance cash receipts at the end of the day or shift. | Conduct meetings and collaborate with other personnel for menu planning, serving arrangements, and related details. | Control inventories of food, equipment, smallware, and liquor, and report shortages to designated personnel. | Develop departmental objectives, budgets, policies, procedures, and strategies. | Develop equipment maintenance schedules and arrange for repairs. | Estimate ingredients and supplies required to prepare a recipe. | Evaluate new products for usefulness and suitability. | Forecast staff, equipment, and supply requirements, based on a master menu. | Greet and seat guests, and present menus and wine lists. | Inspect supplies, equipment, and work areas to ensure efficient service and conformance to standards. | Observe and evaluate workers and work procedures to ensure quality standards and service, and complete disciplinary write-ups. | Perform food preparation and serving duties, such as carving meat, preparing flambe dishes, or serving wine and liquor. | Perform personnel actions, such as hiring and firing staff, providing employee orientation and training, and conducting supervisory activities, such as creating work schedules or organizing employee time sheets. | Perform various financial activities, such as cash handling, deposit preparation, and payroll. | Present bills and accept payments. | Purchase or requisition supplies and equipment needed to ensure quality and timely delivery of services. | Recommend measures for improving work procedures and worker performance to increase service quality and enhance job safety. | Record production, operational, and personnel data on specified forms. | Resolve customer complaints regarding food service. | Schedule parties and take reservations. | Specify food portions and courses, production and time sequences, and workstation and equipment arrangements. | Supervise and participate in kitchen and dining area cleaning activities. | Train workers in food preparation, and in service, sanitation, and safety procedures.</t>
+  </si>
+  <si>
+    <t>35-2011.00</t>
+  </si>
+  <si>
+    <t>Cooks, Fast Food</t>
+  </si>
+  <si>
+    <t>Cook | Deep Fat Fryer Operator | Fast Food Cook | Fry Cook | Fryer | Grill Cook | Line Cook | Pizza Cook | Pizza Maker | Prep Cook (Preparatory Cook)</t>
+  </si>
+  <si>
+    <t>Aldelo Systems Aldelo for Restaurants Pro | Foodman Home-Delivery | Microsoft Excel | Microsoft Outlook | Microsoft Word | Plexis Software Plexis POS | RestaurantPlus PRO</t>
+  </si>
+  <si>
+    <t>Active Listening</t>
+  </si>
+  <si>
+    <t>Administration and Management | Transportation | Communications and Media | Customer and Personal Service | Public Safety and Security | English Language</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Near Vision | Information Ordering | Speech Recognition</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Spend Time Standing | Importance of Being Exact or Accurate | Consequence of Error | Work With or Contribute to a Work Group or Team | Impact of Decisions on Co-workers or Company Results | Dealing With Unpleasant, Angry, or Discourteous People | Physical Proximity | Telephone Conversations | Deal With External Customers or the Public in General</t>
+  </si>
+  <si>
+    <t>Bakers | Baristas | Butchers and Meat Cutters | Chefs and Head Cooks | Cooks, Institution and Cafeteria | Cooks, Private Household | Cooks, Restaurant | Cooks, Short Order | Dining Room and Cafeteria Attendants and Bartender Helpers | Dishwashers | Fast Food and Counter Workers | Food Batchmakers | Food Cooking Machine Operators and Tenders | Food Preparation Workers | Food Servers, Nonrestaurant | Food Service Managers | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Graders and Sorters, Agricultural Products | Meat, Poultry, and Fish Cutters and Trimmers | Waiters and Waitresses</t>
+  </si>
+  <si>
+    <t>Prepare and cook food in a fast food restaurant with a limited menu. Duties of these cooks are limited to preparation of a few basic items and normally involve operating large-volume single-purpose cooking equipment.</t>
+  </si>
+  <si>
+    <t>Clean food preparation areas, cooking surfaces, and utensils. | Clean, stock, and restock workstations and display cases. | Cook and package batches of food, such as hamburgers or fried chicken, prepared to order or kept warm until sold. | Cook the exact number of items ordered by each customer, working on several different orders simultaneously. | Maintain sanitation, health, and safety standards in work areas. | Measure ingredients required for specific food items. | Mix ingredients, such as pancake or waffle batters. | Operate large-volume cooking equipment, such as grills, deep-fat fryers, or griddles. | Order and take delivery of supplies. | Pre-cook items, such as bacon, to prepare them for later use. | Prepare and serve beverages, such as coffee or fountain drinks. | Prepare dough, following recipe. | Prepare specialty foods, such as pizzas, fish and chips, sandwiches, or tacos, following specific methods that usually require short preparation time. | Read food order slips or receive verbal instructions as to food required by patron, and prepare and cook food according to instructions. | Schedule activities and equipment use with managers, using information about daily menus to help coordinate cooking times. | Serve orders to customers at windows, counters, or tables. | Take food and drink orders and receive payment from customers. | Verify that prepared food meets requirements for quality and quantity. | Wash, cut, and prepare foods designated for cooking.</t>
+  </si>
+  <si>
+    <t>35-2012.00</t>
+  </si>
+  <si>
+    <t>Cooks, Institution and Cafeteria</t>
+  </si>
+  <si>
+    <t>Cafeteria Cook | Cook | Dietary Cook | Dinner Cook | Food Service Specialist | Food Service Worker | Prep Cook (Preparatory Cook) | School Cook | Sous Chef</t>
+  </si>
+  <si>
+    <t>GNOME Gnutrition | IBM Lotus 1-2-3 | Meals Plus | Microsoft Excel | Microsoft Word | PCS Revenue Control Systems FASTRAK School Meal Software</t>
+  </si>
+  <si>
+    <t>Speaking | Monitoring | Critical Thinking | Active Listening</t>
+  </si>
+  <si>
+    <t>English Language | Food Production | Customer and Personal Service | Mathematics | Administration and Management | Production and Processing</t>
+  </si>
+  <si>
+    <t>Oral Expression | Near Vision | Speech Clarity | Problem Sensitivity | Oral Comprehension | Category Flexibility | Information Ordering | Deductive Reasoning | Visualization | Inductive Reasoning | Written Comprehension | Speech Recognition | Trunk Strength | Finger Dexterity | Manual Dexterity | Arm-Hand Steadiness | Time Sharing | Selective Attention</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Spend Time Standing | Indoors, Environmentally Controlled | Contact With Others | Work With or Contribute to a Work Group or Team | Time Pressure | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Minor Burns, Cuts, Bites, or Stings | Spend Time Walking or Running | Health and Safety of Other Workers | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Physical Proximity | Frequency of Decision Making | Work Outcomes and Results of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Making Repetitive Motions | Freedom to Make Decisions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable</t>
+  </si>
+  <si>
+    <t>Bakers | Baristas | Butchers and Meat Cutters | Chefs and Head Cooks | Cooks, Fast Food | Cooks, Private Household | Cooks, Restaurant | Cooks, Short Order | Dietetic Technicians | Dining Room and Cafeteria Attendants and Bartender Helpers | Dishwashers | Fast Food and Counter Workers | First-Line Supervisors of Food Preparation and Serving Workers | Food Batchmakers | Food Cooking Machine Operators and Tenders | Food Preparation Workers | Food Servers, Nonrestaurant | Food Service Managers | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Waiters and Waitresses</t>
+  </si>
+  <si>
+    <t>Prepare and cook large quantities of food for institutions, such as schools, hospitals, or cafeterias.</t>
+  </si>
+  <si>
+    <t>Apportion and serve food to facility residents, employees, or patrons. | Bake breads, rolls, or other pastries. | Clean and inspect galley equipment, kitchen appliances, and work areas to ensure cleanliness and functional operation. | Clean, cut, and cook meat, fish, or poultry. | Compile and maintain records of food use and expenditures. | Cook foodstuffs according to menus, special dietary or nutritional restrictions, or numbers of portions to be served. | Determine meal prices, based on calculations of ingredient prices. | Direct activities of one or more workers who assist in preparing and serving meals. | Monitor and record food temperatures to ensure food safety. | Monitor menus and spending to ensure that meals are prepared economically. | Monitor use of government food commodities to ensure that proper procedures are followed. | Plan menus that are varied, nutritionally balanced, and appetizing, taking advantage of foods in season and local availability. | Requisition food supplies, kitchen equipment, and appliances, based on estimates of future needs. | Rotate and store food supplies. | Take inventory of supplies and equipment. | Train new employees. | Wash pots, pans, dishes, utensils, or other cooking equipment.</t>
+  </si>
+  <si>
+    <t>35-2013.00</t>
+  </si>
+  <si>
+    <t>Cooks, Private Household</t>
+  </si>
+  <si>
+    <t>Certified Personal Chef (CPC) | Personal Chef | Personal Private Chef | Private Chef</t>
+  </si>
+  <si>
+    <t>APPCA Personal Chef Office | Cooking e-books | Cost tracking software | Email software | Food inventory software | Intuit QuickBooks | Web browser software | WordPress | Work scheduling software | YouTube</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Speaking | Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Food Production | Sales and Marketing | Administration and Management | Production and Processing | Mathematics</t>
+  </si>
+  <si>
+    <t>Near Vision | Fluency of Ideas | Problem Sensitivity | Finger Dexterity | Manual Dexterity | Information Ordering | Deductive Reasoning | Oral Expression | Originality | Written Comprehension | Oral Comprehension | Speech Recognition | Trunk Strength | Arm-Hand Steadiness | Selective Attention | Category Flexibility | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | E-Mail | Time Pressure | Freedom to Make Decisions | Indoors, Environmentally Controlled | Determine Tasks, Priorities and Goals | Telephone Conversations | Spend Time Making Repetitive Motions | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Impact of Decisions on Co-workers or Company Results | Importance of Being Exact or Accurate</t>
+  </si>
+  <si>
+    <t>Bakers | Baristas | Bartenders | Butchers and Meat Cutters | Chefs and Head Cooks | Cooks, Fast Food | Cooks, Institution and Cafeteria | Cooks, Restaurant | Cooks, Short Order | Dietetic Technicians | Dining Room and Cafeteria Attendants and Bartender Helpers | Dishwashers | Fast Food and Counter Workers | First-Line Supervisors of Food Preparation and Serving Workers | Food Preparation Workers | Food Scientists and Technologists | Food Servers, Nonrestaurant | Food Service Managers | Hosts and Hostesses, Restaurant, Lounge, and Coffee Shop | Waiters and Waitresses</t>
+  </si>
+  <si>
+    <t>Prepare meals in private homes. Includes personal chefs.</t>
+  </si>
+  <si>
+    <t>Cool, package, label, and freeze foods for later consumption and provide instructions for reheating. | Create and explore new cuisines. | Direct the operation and organization of kitchens and all food-related activities, including the presentation and serving of food. | Keep records pertaining to menus, finances, and other business-related issues. | Peel, wash, trim, and cook vegetables and meats, and bake breads and pastries. | Plan and prepare food for parties, holiday meals, luncheons, special functions, and other social events. | Plan menus according to employers' needs and diet restrictions. | Prepare meals in private homes according to employers' recipes or tastes, handling all meals for the family and possibly for other household staff. | Serve meals and snacks to employing families and their guests. | Shop for or order food and kitchen supplies and equipment. | Specialize in preparing fancy dishes or food for special diets. | Stock, organize, and clean kitchens and cooking utensils. | Travel with employers to vacation homes to provide meal preparation at those locations.</t>
+  </si>
+  <si>
+    <t>35-2014.00</t>
+  </si>
+  <si>
+    <t>Cooks, Restaurant</t>
+  </si>
+  <si>
+    <t>Back Line Cook | Banquet Cook | Breakfast Cook | Cook | Fry Cook | Grill Cook | Line Cook | Prep Cook (Preparation Cook) | Prep Person (Preparation Person) | Saucier</t>
+  </si>
+  <si>
+    <t>Facebook | Food safety labeling systems | Menu planning software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Point of sale POS restaurant software | Recipe cost control software</t>
+  </si>
+  <si>
+    <t>Monitoring | Speaking | Critical Thinking</t>
+  </si>
+  <si>
+    <t>Food Production | English Language</t>
+  </si>
+  <si>
+    <t>Near Vision | Manual Dexterity | Problem Sensitivity | Selective Attention | Perceptual Speed | Information Ordering | Oral Expression | Oral Comprehension | Speech Recognition | Visual Color Discrimination | Speech Clarity | Trunk Strength | Control Precision | Finger Dexterity | Arm-Hand Steadiness | Time Sharing</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Indoors, Environmentally Controlled | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Contact With Others | Importance of Being Exact or Accurate | Work With or Contribute to a Work Group or Team | Spend Time Making Repetitive Motions | Frequency of Decision Making | Physical Proximity | Impact of Decisions on Co-workers or Company Results | Health and Safety of Other Workers | Determine Tasks, Priorities and Goals | Exposed to Minor Burns, Cuts, Bites, or Stings | Freedom to Make Decisions | Work Outcomes and Results of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities</t>
+  </si>
+  <si>
+    <t>Bakers | Baristas | Butchers and Meat Cutters | Chefs and Head Cooks | Cooks, Fast Food | Cooks, Institution and Cafeteria | Cooks, Private Household | Cooks, Short Order | Dining Room and Cafeteria Attendants and Bartender Helpers | Dishwashers | Fast Food and Counter Workers | First-Line Supervisors of Food Preparation and Serving Workers | Food Batchmakers | Food Cooking Machine Operators and Tenders | Food Preparation Workers | Food Servers, Nonrestaurant | Food Service Managers | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Graders and Sorters, Agricultural Products | Meat, Poultry, and Fish Cutters and Trimmers</t>
+  </si>
+  <si>
+    <t>Prepare, season, and cook dishes such as soups, meats, vegetables, or desserts in restaurants. May order supplies, keep records and accounts, price items on menu, or plan menu.</t>
+  </si>
+  <si>
+    <t>Bake breads, rolls, cakes, and pastries. | Bake, roast, broil, and steam meats, fish, vegetables, and other foods. | Butcher and dress animals, fowl, or shellfish, or cut and bone meat prior to cooking. | Carve and trim meats such as beef, veal, ham, pork, and lamb for hot or cold service, or for sandwiches. | Consult with supervisory staff to plan menus, taking into consideration factors such as costs and special event needs. | Coordinate and supervise work of kitchen staff. | Ensure food is stored and cooked at correct temperature by regulating temperature of ovens, broilers, grills, and roasters. | Ensure freshness of food and ingredients by checking for quality, keeping track of old and new items, and rotating stock. | Estimate expected food consumption, requisition or purchase supplies, or procure food from storage. | Inspect and clean food preparation areas, such as equipment, work surfaces, and serving areas, to ensure safe and sanitary food-handling practices. | Keep records and accounts. | Observe and test foods to determine if they have been cooked sufficiently, using methods such as tasting, smelling, or piercing them with utensils. | Plan and price menu items. | Portion, arrange, and garnish food, and serve food to waiters or patrons. | Prepare relishes and hors d'oeuvres. | Season and cook food according to recipes or personal judgment and experience. | Substitute for or assist other cooks during emergencies or rush periods. | Turn or stir foods to ensure even cooking. | Wash, peel, cut, and seed fruits and vegetables to prepare them for consumption. | Weigh, measure, and mix ingredients according to recipes or personal judgment, using various kitchen utensils and equipment.</t>
+  </si>
+  <si>
+    <t>35-2015.00</t>
+  </si>
+  <si>
+    <t>Cooks, Short Order</t>
+  </si>
+  <si>
+    <t>Broiler Cook | Cook | Deli Cook (Delicatessen Cook) | Food and Beverage Attendant | Grill Cook | Line Cook | Pizza Maker | Prep Cook (Preparation Cook) | Short Order Cook | Snack Bar Cook</t>
+  </si>
+  <si>
+    <t>Aldelo Systems Aldelo for Restaurants Pro | Foodman Home-Delivery | Inventory control software | Plexis Software Plexis POS | RestaurantPlus PRO</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Active Listening | Speaking</t>
+  </si>
+  <si>
+    <t>Food Production | Customer and Personal Service | English Language</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Near Vision | Trunk Strength | Manual Dexterity | Information Ordering | Arm-Hand Steadiness | Time Sharing | Selective Attention | Problem Sensitivity | Control Precision | Finger Dexterity</t>
+  </si>
+  <si>
+    <t>Spend Time Standing | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Freedom to Make Decisions | Physical Proximity | Exposed to Minor Burns, Cuts, Bites, or Stings | Work With or Contribute to a Work Group or Team | Spend Time Making Repetitive Motions | Exposed to Very Hot or Cold Temperatures | Contact With Others | Coordinate or Lead Others in Accomplishing Work Activities | Time Pressure</t>
+  </si>
+  <si>
+    <t>Bakers | Baristas | Butchers and Meat Cutters | Chefs and Head Cooks | Cooks, Fast Food | Cooks, Institution and Cafeteria | Cooks, Private Household | Cooks, Restaurant | Dining Room and Cafeteria Attendants and Bartender Helpers | Dishwashers | Fast Food and Counter Workers | Food Batchmakers | Food Cooking Machine Operators and Tenders | Food Preparation Workers | Food Servers, Nonrestaurant | Food Service Managers | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Graders and Sorters, Agricultural Products | Meat, Poultry, and Fish Cutters and Trimmers | Waiters and Waitresses</t>
+  </si>
+  <si>
+    <t>Prepare and cook to order a variety of foods that require only a short preparation time. May take orders from customers and serve patrons at counters or tables.</t>
+  </si>
+  <si>
+    <t>Accept payments, and make change or write charge slips as necessary. | Clean food preparation equipment, work areas, and counters or tables. | Complete orders from steam tables, placing food on plates and serving customers at tables or counters. | Grill and garnish hamburgers or other meats, such as steaks and chops. | Grill, cook, and fry foods such as french fries, eggs, and pancakes. | Order supplies and stock them on shelves. | Perform food preparation tasks, such as making sandwiches, carving meats, making soups or salads, baking breads or desserts, and brewing coffee or tea. | Perform general cleaning activities in kitchen and dining areas. | Plan work on orders so that items served together are finished at the same time. | Restock kitchen supplies, rotate food, and stamp the time and date on food in coolers. | Take orders from customers and cook foods requiring short preparation times, according to customer requirements.</t>
+  </si>
+  <si>
+    <t>35-2019.00</t>
+  </si>
+  <si>
+    <t>Cooks, All Other</t>
+  </si>
+  <si>
+    <t>Banquet Cook | Camp Cook | Cafeteria Cook | Catering Cook | Cook | Grill Cook | Kitchen Cook | Mess Cook | Prep Cook | Specialty Cook</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Word | Email software | Web browser software | Database software | Scheduling software | Microsoft Outlook | Inventory management systems | Microsoft Office software | Computerized maintenance management system CMMS</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Critical Thinking | Reading Comprehension | Speaking</t>
+  </si>
+  <si>
+    <t>Food Production | Customer and Personal Service | English Language | Production and Processing | Administration and Management | Education and Training</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Finger Dexterity | Arm-Hand Steadiness | Multilimb Coordination | Control Precision | Static Strength | Trunk Strength | Stamina | Near Vision | Far Vision | Depth Perception | Gross Body Coordination | Gross Body Equilibrium | Extent Flexibility | Reaction Time | Problem Sensitivity | Oral Comprehension | Selective Attention | Oral Expression | Information Ordering</t>
+  </si>
+  <si>
+    <t>Spend Time Standing | Indoors, Not Environmentally Controlled | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Very Hot or Cold Temperatures | Exposed to Minor Burns, Cuts, Bites, or Stings | Exposed to Hazardous Equipment | Time Pressure | Importance of Repeating Same Tasks | Spend Time Making Repetitive Motions | Physical Proximity | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Importance of Being Exact or Accurate | Spend Time Walking or Running | Health and Safety of Other Workers | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets</t>
+  </si>
+  <si>
+    <t>Cooks, Restaurant | Cooks, Institution and Cafeteria | Cooks, Short Order | Cooks, Fast Food | Cooks, Private Household | Food Preparation Workers | Chefs and Head Cooks | First-Line Supervisors of Food Preparation and Serving Workers | Bakers | Butchers and Meat Cutters | Food Service Managers | Bartenders | Fast Food and Counter Workers | Dining Room and Cafeteria Attendants and Bartender Helpers | Dishwashers | Food Servers, Nonrestaurant | Waiters and Waitresses | Food Preparation and Serving Related Workers, All Other | Food Batchmakers | Dietetic Technicians</t>
+  </si>
+  <si>
+    <t>All cooks not listed separately.</t>
+  </si>
+  <si>
+    <t>Prepare and cook food in settings not classified separately. | Read menus, recipes, and production sheets to determine preparation requirements. | Measure, mix, and prepare ingredients according to recipes and portion standards. | Cook food using ranges, ovens, grills, fryers, steamers, and specialized equipment. | Monitor cooking temperatures, times, and food quality throughout preparation. | Season and taste dishes to verify flavor and adjust as needed. | Portion, plate, and garnish food for service. | Store, label, and rotate food supplies according to safety standards. | Inspect ingredients and supplies for freshness, quality, and quantity. | Clean and sanitize work areas, utensils, and cooking equipment. | Follow food safety, sanitation, and personal hygiene regulations. | Estimate food requirements and assist with ordering supplies. | Operate and perform basic maintenance on kitchen equipment. | Train and direct kitchen helpers and assistants.</t>
+  </si>
+  <si>
+    <t>35-2021.00</t>
+  </si>
+  <si>
+    <t>Food Preparation Workers</t>
+  </si>
+  <si>
+    <t>Cook | Cook Aide | Deli Clerk (Delicatessen Clerk) | Diet Aide | Dietary Aide | Food Prep (Food Preparer) | Food Service Aide | Food Service Worker (FSW) | Line Cook | Nutrition Aide</t>
+  </si>
+  <si>
+    <t>Barrington Software CookenPro Commercial | CBORD Foodservice Suite | CBORD NetRecipe | Culinary Software Services ChefTec | EGS CALCMENU | Master Cook Deluxe Professional Cook | Mealmaster Cookbook Wizard | MicroBlast Recipe Wizard for Windows | Microsoft Excel | Microsoft Office software | Quizlet | Recipe software | ValuSoft MasterCook | YouTube | iPro</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Near Vision | Trunk Strength | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Spend Time Standing | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Contact With Others | Importance of Being Exact or Accurate | Face-to-Face Discussions with Individuals and Within Teams | Time Pressure | Work With or Contribute to a Work Group or Team | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls</t>
+  </si>
+  <si>
+    <t>Bakers | Baristas | Butchers and Meat Cutters | Chefs and Head Cooks | Cooks, Fast Food | Cooks, Institution and Cafeteria | Cooks, Private Household | Cooks, Restaurant | Cooks, Short Order | Dining Room and Cafeteria Attendants and Bartender Helpers | Dishwashers | Fast Food and Counter Workers | First-Line Supervisors of Food Preparation and Serving Workers | Food Batchmakers | Food Cooking Machine Operators and Tenders | Food Servers, Nonrestaurant | Food Service Managers | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Graders and Sorters, Agricultural Products | Meat, Poultry, and Fish Cutters and Trimmers</t>
+  </si>
+  <si>
+    <t>Perform a variety of food preparation duties other than cooking, such as preparing cold foods and shellfish, slicing meat, and brewing coffee or tea.</t>
+  </si>
+  <si>
+    <t>Add cutlery, napkins, food, and other items to trays on assembly lines in hospitals, cafeterias, airline kitchens, and similar establishments. | Assemble meal trays with foods in accordance with patients' diets. | Assist cooks and kitchen staff with various tasks as needed, and provide cooks with needed items. | Butcher and clean fowl, fish, poultry, and shellfish to prepare for cooking or serving. | Carry food supplies, equipment, and utensils to and from storage and work areas. | Clean and sanitize work areas, equipment, utensils, dishes, or silverware. | Cut, slice or grind meat, poultry, and seafood to prepare for cooking. | Distribute food to waiters and waitresses to serve to customers. | Distribute menus to hospital patients, collect diet sheets, and deliver food trays and snacks to nursing units or directly to patients. | Inform supervisors when equipment is not working properly and when food and supplies are getting low, and order needed items. | Keep records of the quantities of food used. | Load dishes, glasses, and tableware into dishwashing machines. | Make special dressings and sauces as condiments for sandwiches. | Mix ingredients for green salads, molded fruit salads, vegetable salads, and pasta salads. | Operate cash register, handle money, and give correct change. | Package take-out foods or serve food to customers. | Place food trays over food warmers for immediate service, or store them in refrigerated storage cabinets. | Portion and wrap food, or place it directly on plates for service to patrons. | Prepare a variety of foods, such as meats, vegetables, or desserts, according to customers' orders or supervisors' instructions, following approved procedures. | Prepare and serve a variety of beverages, such as coffee, tea, and soft drinks. | Receive and store food supplies, equipment, and utensils in refrigerators, cupboards, and other storage areas. | Remove trash and clean kitchen garbage containers. | Scrape leftovers from dishes into garbage containers. | Stir and strain soups and sauces. | Stock cupboards and refrigerators, and tend salad bars and buffet meals. | Store food in designated containers and storage areas to prevent spoilage. | Take and record temperature of food and food storage areas, such as refrigerators and freezers. | Use manual or electric appliances to clean, peel, slice, and trim foods. | Vacuum dining area and sweep and mop kitchen floor. | Wash, peel, and cut various foods, such as fruits and vegetables, to prepare for cooking or serving. | Weigh or measure ingredients.</t>
+  </si>
+  <si>
+    <t>35-3011.00</t>
+  </si>
+  <si>
+    <t>Bartenders</t>
+  </si>
+  <si>
+    <t>Banquet Bartender | Bar Captain | Bartender | Mixologist</t>
+  </si>
+  <si>
+    <t>AZZ CardFile | Compris software | Facebook | Focus point of sale POS software | Intuit QuickBooks Point of Sale | MICROS Systems HSI Profits Series | Microsoft Outlook | NCR Advanced Checkout Solution | NCR NeighborhoodPOS | The General Store | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Critical Thinking | Monitoring | Active Learning | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Education and Training | Sales and Marketing</t>
+  </si>
+  <si>
+    <t>Oral Expression | Oral Comprehension | Information Ordering | Near Vision | Speech Recognition | Speech Clarity | Manual Dexterity | Arm-Hand Steadiness | Selective Attention | Memorization | Inductive Reasoning | Deductive Reasoning | Problem Sensitivity | Written Expression | Written Comprehension | Auditory Attention | Trunk Strength | Finger Dexterity</t>
+  </si>
+  <si>
+    <t>Contact With Others | Spend Time Standing | Deal With External Customers or the Public in General | Face-to-Face Discussions with Individuals and Within Teams | Physical Proximity | Freedom to Make Decisions | Indoors, Environmentally Controlled | Dealing With Unpleasant, Angry, or Discourteous People | Importance of Being Exact or Accurate | Spend Time Making Repetitive Motions | Spend Time Walking or Running | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Frequency of Decision Making | Work With or Contribute to a Work Group or Team</t>
+  </si>
+  <si>
+    <t>Bakers | Baristas | Chefs and Head Cooks | Cooks, Fast Food | Cooks, Institution and Cafeteria | Cooks, Private Household | Cooks, Restaurant | Cooks, Short Order | Dining Room and Cafeteria Attendants and Bartender Helpers | Dishwashers | Door-to-Door Sales Workers, News and Street Vendors, and Related Workers | Fast Food and Counter Workers | First-Line Supervisors of Food Preparation and Serving Workers | Food Preparation Workers | Food Servers, Nonrestaurant | Food Service Managers | Hosts and Hostesses, Restaurant, Lounge, and Coffee Shop | Locker Room, Coatroom, and Dressing Room Attendants | Maids and Housekeeping Cleaners | Waiters and Waitresses</t>
+  </si>
+  <si>
+    <t>Mix and serve drinks to patrons, directly or through waitstaff.</t>
+  </si>
+  <si>
+    <t>Arrange bottles and glasses to make attractive displays. | Ask customers who become loud and obnoxious to leave, or physically remove them. | Attempt to limit problems and liability related to customers' excessive drinking by taking steps such as persuading customers to stop drinking, or ordering taxis or other transportation for intoxicated patrons. | Balance cash receipts. | Check identification of customers to verify age requirements for purchase of alcohol. | Clean bars, work areas, and tables. | Clean glasses, utensils, and bar equipment. | Collect money for drinks served. | Create drink recipes. | Mix ingredients, such as liquor, soda, water, sugar, and bitters, to prepare cocktails and other drinks. | Order or requisition liquors and supplies. | Plan bar menus. | Plan, organize, and control the operations of a cocktail lounge or bar. | Prepare appetizers such as pickles, cheese, and cold meats. | Serve snacks or food items to customers seated at the bar. | Serve wine, and bottled or draft beer. | Slice and pit fruit for garnishing drinks. | Stock bar with beer, wine, liquor, and related supplies such as ice, glassware, napkins, or straws. | Supervise the work of bar staff and other bartenders. | Take beverage orders from serving staff or directly from patrons.</t>
+  </si>
+  <si>
+    <t>35-3023.00</t>
+  </si>
+  <si>
+    <t>Fast Food and Counter Workers</t>
+  </si>
+  <si>
+    <t>Cafe Server | Cafeteria Server | Cafeteria Worker | Counter Worker | Deli Worker (Delicatessen Worker) | Dietary Aide | Food Server | Food Service Worker | Server | Snack Bar Attendant</t>
+  </si>
+  <si>
+    <t>Aldelo Systems Aldelo for Restaurants Pro | Compris software | Facebook | Foodman Home-Delivery | Intuit QuickBooks Point of Sale | MICROS Systems HSI Profits Series | Menu and nutrition database software | Microsoft Excel | Microsoft Office software | Microsoft Windows | NCR Advanced Checkout Solution | NCR NeighborhoodPOS | Plexis Software Plexis POS | Quizlet | RestaurantPlus PRO | The General Store</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Food Production | Mathematics</t>
+  </si>
+  <si>
+    <t>Speech Clarity | Speech Recognition | Near Vision | Oral Expression | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Contact With Others | Work With or Contribute to a Work Group or Team | Deal With External Customers or the Public in General | Dealing With Unpleasant, Angry, or Discourteous People | Spend Time Standing | Freedom to Make Decisions | Face-to-Face Discussions with Individuals and Within Teams | Physical Proximity | Determine Tasks, Priorities and Goals | Indoors, Environmentally Controlled | Spend Time Making Repetitive Motions | Importance of Being Exact or Accurate | Importance of Repeating Same Tasks | Spend Time Walking or Running | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Bending or Twisting Your Body | Frequency of Decision Making</t>
+  </si>
+  <si>
+    <t>Bakers | Baristas | Bartenders | Butchers and Meat Cutters | Cashiers | Chefs and Head Cooks | Cooks, Fast Food | Cooks, Institution and Cafeteria | Cooks, Private Household | Cooks, Restaurant | Cooks, Short Order | Dining Room and Cafeteria Attendants and Bartender Helpers | Dishwashers | First-Line Supervisors of Food Preparation and Serving Workers | Food Batchmakers | Food Preparation Workers | Food Servers, Nonrestaurant | Food Service Managers | Hosts and Hostesses, Restaurant, Lounge, and Coffee Shop | Waiters and Waitresses</t>
+  </si>
+  <si>
+    <t>Perform duties such as taking orders and serving food and beverages. Serve customers at counter or from a steam table. May take payment. May prepare food and beverages.</t>
+  </si>
+  <si>
+    <t>Accept payment from customers, and make change as necessary. | Add relishes and garnishes to food orders, according to instructions. | Arrange tables and decorations according to instructions. | Balance receipts and payments in cash registers. | Brew coffee and tea, and fill containers with requested beverages. | Clean and organize eating, service, and kitchen areas. | Collect and return dirty dishes to the kitchen for washing. | Communicate with customers regarding orders, comments, and complaints. | Deliver orders to kitchens, and pick up and serve food when it is ready. | Distribute food to servers. | Monitor and order supplies or food items, and restock as necessary to maintain inventory. | Notify kitchen personnel of shortages or special orders. | Perform cleaning duties, such as sweeping, mopping, and washing dishes, to keep equipment and facilities sanitary. | Perform personnel activities, such as supervising and training employees. | Plan, prepare, and deliver meals to individuals with special dietary needs. | Prepare and serve cold drinks, frozen milk drinks, or desserts, using drink-dispensing, milkshake, or frozen-custard machines. | Prepare daily food items, and cook simple foods and beverages, such as sandwiches, salads, soups, pizza, or coffee, using proper safety precautions and sanitary measures. | Replenish foods at serving stations. | Request and record customer orders, and compute bills, using cash registers, multi-counting machines, or pencil and paper. | Scrub and polish counters, steam tables, and other equipment, and clean glasses, dishes, and fountain equipment. | Select food items from serving or storage areas and place them in dishes, on serving trays, or in take-out bags. | Serve customers in eating places that specialize in fast service and inexpensive carry-out food. | Serve food, beverages, or desserts to customers in such settings as take-out counters of restaurants or lunchrooms, business or industrial establishments, hotel rooms, and cars. | Set up dining areas for meals, and clear them following meals. | Take customers' orders and write ordered items on tickets, giving ticket stubs to customers when needed to identify filled orders. | Wash dishes, glassware, and silverware after meals. | Wrap menu items such as sandwiches, hot entrees, and desserts for serving or for takeout.</t>
+  </si>
+  <si>
+    <t>35-3023.01</t>
+  </si>
+  <si>
+    <t>Baristas</t>
+  </si>
+  <si>
+    <t>Barista | Catering Barista</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Office software | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Monitoring | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Sales and Marketing</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Near Vision | Finger Dexterity | Arm-Hand Steadiness | Time Sharing | Information Ordering | Problem Sensitivity | Written Comprehension | Trunk Strength | Control Precision | Manual Dexterity</t>
+  </si>
+  <si>
+    <t>Spend Time Standing | Contact With Others | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Deal With External Customers or the Public in General | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Making Repetitive Motions | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Physical Proximity | Indoors, Environmentally Controlled | Dealing With Unpleasant, Angry, or Discourteous People | Importance of Being Exact or Accurate</t>
+  </si>
+  <si>
+    <t>Bakers | Bartenders | Butchers and Meat Cutters | Chefs and Head Cooks | Cooks, Fast Food | Cooks, Institution and Cafeteria | Cooks, Private Household | Cooks, Restaurant | Cooks, Short Order | Dining Room and Cafeteria Attendants and Bartender Helpers | Dishwashers | Door-to-Door Sales Workers, News and Street Vendors, and Related Workers | Fast Food and Counter Workers | First-Line Supervisors of Food Preparation and Serving Workers | Food Preparation Workers | Food Servers, Nonrestaurant | Food Service Managers | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Hosts and Hostesses, Restaurant, Lounge, and Coffee Shop | Waiters and Waitresses</t>
+  </si>
+  <si>
+    <t>Prepare or serve specialty coffee or other beverages. Serve food such as baked goods or sandwiches to patrons.</t>
+  </si>
+  <si>
+    <t>Check temperatures of freezers, refrigerators, or heating equipment to ensure proper functioning. | Clean or sanitize work areas, utensils, or equipment. | Clean service or seating areas. | Create signs to advertise store products or events. | Demonstrate the use of retail equipment, such as espresso machines. | Describe menu items to customers, or suggest products that might appeal to them. | Order, receive, or stock supplies or retail products. | Prepare or serve hot or cold beverages, such as coffee, espresso drinks, blended coffees, or teas. | Prepare or serve menu items, such as sandwiches or salads. | Provide customers with product details, such as coffee blend or preparation descriptions. | Receive and process customer payments. | Serve prepared foods, such as muffins, biscotti, or bagels. | Set up or restock product displays. | Slice fruits, vegetables, desserts, or meats for use in food service. | Stock customer service stations with paper products or beverage preparation items. | Take customer orders and convey them to other employees for preparation. | Take out garbage. | Weigh, grind, or pack coffee beans for customers. | Wrap, label, or date food items for sale.</t>
+  </si>
+  <si>
+    <t>35-3031.00</t>
+  </si>
+  <si>
+    <t>Waiters and Waitresses</t>
+  </si>
+  <si>
+    <t>Banquet Server | Busser | Cocktail Server | Food Runner | Food Server | Restaurant Server | Room Service Server | Server | Waiter | Waitress</t>
+  </si>
+  <si>
+    <t>Blink | Compris Advanced Manager's Workstation | Compris software | Facebook | Hospitality Control Solutions Aloha Point-of-Sale | Intuit QuickBooks Point of Sale | MICROS Systems HSI Profits Series | NCR Advanced Checkout Solution | NCR NeighborhoodPOS | The General Store</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Monitoring</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Recognition | Speech Clarity | Time Sharing | Trunk Strength | Stamina | Problem Sensitivity | Manual Dexterity | Arm-Hand Steadiness | Deductive Reasoning | Information Ordering | Near Vision</t>
+  </si>
+  <si>
+    <t>Contact With Others | Spend Time Standing | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Walking or Running | Work With or Contribute to a Work Group or Team | Indoors, Environmentally Controlled | Physical Proximity | Coordinate or Lead Others in Accomplishing Work Activities | Health and Safety of Other Workers | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Making Repetitive Motions | Telephone Conversations | Importance of Being Exact or Accurate</t>
+  </si>
+  <si>
+    <t>Baristas | Bartenders | Cashiers | Chefs and Head Cooks | Concierges | Cooks, Fast Food | Cooks, Institution and Cafeteria | Cooks, Private Household | Cooks, Restaurant | Cooks, Short Order | Dining Room and Cafeteria Attendants and Bartender Helpers | Dishwashers | Fast Food and Counter Workers | First-Line Supervisors of Food Preparation and Serving Workers | Food Preparation Workers | Food Servers, Nonrestaurant | Food Service Managers | Hosts and Hostesses, Restaurant, Lounge, and Coffee Shop | Hotel, Motel, and Resort Desk Clerks | Locker Room, Coatroom, and Dressing Room Attendants</t>
+  </si>
+  <si>
+    <t>Take orders and serve food and beverages to patrons at tables in dining establishment.</t>
+  </si>
+  <si>
+    <t>Assist host or hostess by answering phones to take reservations or to-go orders, and by greeting, seating, and thanking guests. | Bring wine selections to tables with appropriate glasses, and pour the wines for customers. | Check patrons' identification to ensure that they meet minimum age requirements for consumption of alcoholic beverages. | Check with customers to ensure that they are enjoying their meals, and take action to correct any problems. | Clean tables or counters after patrons have finished dining. | Collect payments from customers. | Describe and recommend wines to customers. | Escort customers to their tables. | Explain how various menu items are prepared, describing ingredients and cooking methods. | Fill salt, pepper, sugar, cream, condiment, and napkin containers. | Garnish and decorate dishes in preparation for serving. | Inform customers of daily specials. | Perform cleaning duties, such as sweeping and mopping floors, vacuuming carpet, tidying up server station, taking out trash, or checking and cleaning bathroom. | Perform food preparation duties, such as preparing salads, appetizers, and cold dishes, portioning desserts, and brewing coffee. | Prepare checks that itemize and total meal costs and sales taxes. | Prepare hot, cold, and mixed drinks for patrons, and chill bottles of wine. | Prepare tables for meals, including setting up items such as linens, silverware, and glassware. | Present menus to patrons and answer questions about menu items, making recommendations upon request. | Provide guests with information about local areas, including directions. | Remove dishes and glasses from tables or counters, and take them to kitchen for cleaning. | Roll silverware, set up food stations, or set up dining areas to prepare for the next shift or for large parties. | Serve food or beverages to patrons, and prepare or serve specialty dishes at tables as required. | Stock service areas with supplies such as coffee, food, tableware, and linens. | Take orders from patrons for food or beverages. | Write patrons' food orders on order slips, memorize orders, or enter orders into computers for transmittal to kitchen staff.</t>
+  </si>
+  <si>
+    <t>35-3041.00</t>
+  </si>
+  <si>
+    <t>Food Servers, Nonrestaurant</t>
+  </si>
+  <si>
+    <t>Food Server | Food Service Worker | Kitchen Runner | Room Server | Room Service Server | Tray Server</t>
+  </si>
+  <si>
+    <t>CBORD Nutrition Service Suite | Capital Codeworks MenuMax | Facebook | Microsoft Office software | Microsoft Outlook | Microsoft Windows | Picis CareSuite</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening</t>
+  </si>
+  <si>
+    <t>English Language | Customer and Personal Service | Food Production</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Near Vision | Oral Expression | Speech Clarity | Speech Recognition | Selective Attention</t>
+  </si>
+  <si>
+    <t>Spend Time Standing | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Walking or Running | Time Pressure | Physical Proximity | Work With or Contribute to a Work Group or Team | Contact With Others | Spend Time Bending or Twisting Your Body | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Health and Safety of Other Workers | Importance of Being Exact or Accurate | Coordinate or Lead Others in Accomplishing Work Activities | Frequency of Decision Making | Determine Tasks, Priorities and Goals | Dealing With Unpleasant, Angry, or Discourteous People | Freedom to Make Decisions | Importance of Repeating Same Tasks | Deal With External Customers or the Public in General | Impact of Decisions on Co-workers or Company Results | Work Outcomes and Results of Other Workers | Spend Time Making Repetitive Motions | Indoors, Environmentally Controlled</t>
+  </si>
+  <si>
+    <t>Baggage Porters and Bellhops | Baristas | Bartenders | Chefs and Head Cooks | Cooks, Fast Food | Cooks, Institution and Cafeteria | Cooks, Private Household | Cooks, Restaurant | Cooks, Short Order | Dining Room and Cafeteria Attendants and Bartender Helpers | Dishwashers | Fast Food and Counter Workers | First-Line Supervisors of Food Preparation and Serving Workers | Food Preparation Workers | Food Service Managers | Hosts and Hostesses, Restaurant, Lounge, and Coffee Shop | Hotel, Motel, and Resort Desk Clerks | Locker Room, Coatroom, and Dressing Room Attendants | Maids and Housekeeping Cleaners | Waiters and Waitresses</t>
+  </si>
+  <si>
+    <t>Serve food to individuals outside of a restaurant environment, such as in hotel rooms, hospital rooms, residential care facilities, or cars.</t>
+  </si>
+  <si>
+    <t>Carry food, silverware, or linen on trays or use carts to carry trays. | Clean or sterilize dishes, kitchen utensils, equipment, or facilities. | Determine where patients or patrons would like to eat their meals and help them get situated. | Examine trays to ensure that they contain required items. | Load trays with accessories, such as eating utensils, napkins, or condiments. | Monitor food distribution, ensuring that meals are delivered to the correct recipients and that guidelines, such as those for special diets, are followed. | Monitor food preparation or serving techniques to ensure that proper procedures are followed. | Place food servings on plates or trays according to orders or instructions. | Prepare food items, such as sandwiches, salads, soups, or beverages. | Record amounts and types of special food items served to customers. | Remove trays and stack dishes for return to kitchen after meals are finished. | Stock service stations with items, such as ice, napkins, or straws. | Take food orders and relay orders to kitchens or serving counters so they can be filled. | Total checks, present them to customers, and accept payment for services.</t>
+  </si>
+  <si>
+    <t>35-9011.00</t>
+  </si>
+  <si>
+    <t>Dining Room and Cafeteria Attendants and Bartender Helpers</t>
+  </si>
+  <si>
+    <t>Barback | Buffet Attendant | Bus Boy | Bus Person | Busser | Dining Room Attendant | Food Service Aide | Food Service Helper | Server Assistant | Server's Assistant</t>
+  </si>
+  <si>
+    <t>Cafe Cartel Systems | Facebook | Microsoft Excel | Microsoft Windows | Plexis Software Plexis POS | RestaurantPlus PRO</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Food Production | English Language | Sales and Marketing</t>
+  </si>
+  <si>
+    <t>Trunk Strength | Stamina | Manual Dexterity | Arm-Hand Steadiness | Static Strength | Information Ordering | Oral Expression | Oral Comprehension | Speech Clarity | Speech Recognition | Near Vision | Extent Flexibility</t>
+  </si>
+  <si>
+    <t>Spend Time Walking or Running | Spend Time Standing | Contact With Others | Work With or Contribute to a Work Group or Team | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Physical Proximity | Spend Time Making Repetitive Motions | Deal With External Customers or the Public in General | Importance of Being Exact or Accurate | Indoors, Environmentally Controlled | Spend Time Bending or Twisting Your Body | Impact of Decisions on Co-workers or Company Results | Telephone Conversations | Dealing With Unpleasant, Angry, or Discourteous People</t>
+  </si>
+  <si>
+    <t>Baggage Porters and Bellhops | Baristas | Bartenders | Cashiers | Chefs and Head Cooks | Cooks, Fast Food | Cooks, Institution and Cafeteria | Cooks, Private Household | Cooks, Restaurant | Cooks, Short Order | Dishwashers | Fast Food and Counter Workers | First-Line Supervisors of Food Preparation and Serving Workers | Food Preparation Workers | Food Servers, Nonrestaurant | Food Service Managers | Hosts and Hostesses, Restaurant, Lounge, and Coffee Shop | Locker Room, Coatroom, and Dressing Room Attendants | Maids and Housekeeping Cleaners | Waiters and Waitresses</t>
+  </si>
+  <si>
+    <t>Facilitate food service. Clean tables; remove dirty dishes; replace soiled table linens; set tables; replenish supply of clean linens, silverware, glassware, and dishes; supply service bar with food; and serve items such as water, condiments, and coffee to patrons.</t>
+  </si>
+  <si>
+    <t>Carry food, dishes, trays, or silverware from kitchens or supply departments to serving counters. | Carry linens to or from laundry areas. | Carry trays from food counters to tables for cafeteria patrons. | Clean and polish counters, shelves, walls, furniture, or equipment in food service areas or other areas of restaurants and mop or vacuum floors. | Clean up spilled food or drink or broken dishes and remove empty bottles and trash. | Fill beverage or ice dispensers. | Garnish foods and position them on tables to make them visible and accessible. | Greet and seat customers. | Locate items requested by customers. | Maintain adequate supplies of items, such as clean linens, silverware, glassware, dishes, or trays. | Mix and prepare flavors for mixed drinks. | Perform serving, cleaning, or stocking duties in establishments, such as cafeterias or dining rooms, to facilitate customer service. | Replenish supplies of food or equipment at steam tables or service bars. | Run cash registers. | Scrape and stack dirty dishes and carry dishes and other tableware to kitchens for cleaning. | Serve food to customers when waiters or waitresses need assistance. | Serve ice water, coffee, rolls, or butter to patrons. | Set tables with clean linens, condiments, or other supplies. | Slice and pit fruit used to garnish drinks. | Stock cabinets or serving areas with condiments and refill condiment containers. | Stock refrigerating units with wines or bottled beer or replace empty beer kegs. | Wash glasses or other serving equipment at bars. | Wipe tables or seats with dampened cloths or replace dirty tablecloths.</t>
+  </si>
+  <si>
+    <t>35-9021.00</t>
+  </si>
+  <si>
+    <t>Dishwashers</t>
+  </si>
+  <si>
+    <t>Busser | Dish Machine Operator (DMO) | Dish Room Worker | Dish Runner | Dish Technician (Dish Tech) | Dishwasher | Kitchen Helper | Kitchen Steward | Steward | Utility Worker</t>
+  </si>
+  <si>
+    <t>Facebook | Microsoft Windows</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Speaking | Critical Thinking</t>
+  </si>
+  <si>
+    <t>English Language</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Near Vision | Extent Flexibility | Trunk Strength | Arm-Hand Steadiness</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Standing | Health and Safety of Other Workers | Contact With Others | Work With or Contribute to a Work Group or Team | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls</t>
+  </si>
+  <si>
+    <t>Cleaners of Vehicles and Equipment | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Cooks, Fast Food | Cooks, Short Order | Dining Room and Cafeteria Attendants and Bartender Helpers | Fast Food and Counter Workers | Food Cooking Machine Operators and Tenders | Food Preparation Workers | Food Servers, Nonrestaurant | Food and Tobacco Roasting, Baking, and Drying Machine Operators and Tenders | Helpers--Production Workers | Janitors and Cleaners, Except Maids and Housekeeping Cleaners | Laborers and Freight, Stock, and Material Movers, Hand | Laundry and Dry-Cleaning Workers | Machine Feeders and Offbearers | Maids and Housekeeping Cleaners | Mixing and Blending Machine Setters, Operators, and Tenders | Packaging and Filling Machine Operators and Tenders | Packers and Packagers, Hand | Recycling and Reclamation Workers</t>
+  </si>
+  <si>
+    <t>Clean dishes, kitchen, food preparation equipment, or utensils.</t>
+  </si>
+  <si>
+    <t>Clean garbage cans with water or steam. | Clean or prepare various foods for cooking or serving. | Load or unload trucks that deliver or pick up food or supplies. | Maintain kitchen work areas, equipment, or utensils in clean and orderly condition. | Place clean dishes, utensils, or cooking equipment in storage areas. | Prepare and package individual place settings. | Receive and store supplies. | Set up banquet tables. | Sort and remove trash, placing it in designated pickup areas. | Stock supplies, such as food or utensils, in serving stations, cupboards, refrigerators, or salad bars. | Sweep or scrub floors. | Transfer supplies or equipment between storage and work areas, by hand or using hand trucks. | Wash dishes, glassware, flatware, pots, or pans, using dishwashers or by hand.</t>
+  </si>
+  <si>
+    <t>35-9031.00</t>
+  </si>
+  <si>
+    <t>Hosts and Hostesses, Restaurant, Lounge, and Coffee Shop</t>
+  </si>
+  <si>
+    <t>Buffet Hostess | Dining Coordinator | General Teller | Greeter | Hospitality Coordinator | Host | Host Coordinator | Hostess | Maitre D' (Maitre d'hotel) | Seater</t>
+  </si>
+  <si>
+    <t>Avenista Table Reservations | Facebook | GuestBridge Reserve | Hospitality Control Solutions Aloha Point-of-Sale | Microsoft Excel | Microsoft Office software | Microsoft Windows | OpenTable | Reservation software | iMagic Restaurant Reservation</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Recognition | Speech Clarity | Written Comprehension | Near Vision | Inductive Reasoning | Deductive Reasoning | Problem Sensitivity</t>
+  </si>
+  <si>
+    <t>Spend Time Standing | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Work With or Contribute to a Work Group or Team | Spend Time Walking or Running | Telephone Conversations | Physical Proximity | Spend Time Making Repetitive Motions | Frequency of Decision Making | Freedom to Make Decisions | Deal With External Customers or the Public in General | Importance of Being Exact or Accurate | Determine Tasks, Priorities and Goals | Coordinate or Lead Others in Accomplishing Work Activities | Dealing With Unpleasant, Angry, or Discourteous People</t>
+  </si>
+  <si>
+    <t>Baristas | Bartenders | Cashiers | Chefs and Head Cooks | Concierges | Cooks, Private Household | Demonstrators and Product Promoters | Dining Room and Cafeteria Attendants and Bartender Helpers | Fast Food and Counter Workers | First-Line Supervisors of Food Preparation and Serving Workers | Food Preparation Workers | Food Servers, Nonrestaurant | Food Service Managers | Hotel, Motel, and Resort Desk Clerks | Locker Room, Coatroom, and Dressing Room Attendants | Lodging Managers | Meeting, Convention, and Event Planners | Passenger Attendants | Ushers, Lobby Attendants, and Ticket Takers | Waiters and Waitresses</t>
+  </si>
+  <si>
+    <t>Welcome patrons, seat them at tables or in lounge, and help ensure quality of facilities and service.</t>
+  </si>
+  <si>
+    <t>Answer telephone calls and respond to inquiries or transfer calls. | Assign patrons to tables suitable for their needs and according to rotation so that servers receive an appropriate number of seatings. | Assist other restaurant workers by serving food and beverages, or by bussing tables. | Confer with other staff to help plan establishments' menus. | Direct patrons to coatrooms and waiting areas, such as lounges. | Greet guests and seat them at tables or in waiting areas. | Hire, train, and supervise food and beverage service staff. | Inform patrons of establishment specialties and features. | Inspect dining and serving areas to ensure cleanliness and proper setup. | Inspect restrooms for cleanliness and availability of supplies, and clean restrooms when necessary. | Maintain contact with kitchen staff, management, serving staff, and customers to ensure that dining details are handled properly and customers' concerns are addressed. | Operate cash registers to accept payments for food and beverages. | Order or requisition supplies and equipment for tables and serving stations. | Perform marketing and advertising services. | Prepare cash receipts after establishments close, and make bank deposits. | Provide guests with menus. | Receive and record patrons' dining reservations. | Speak with patrons to ensure satisfaction with food and service, to respond to complaints, or to make conversation. | Supervise and coordinate activities of dining room staff to ensure that patrons receive prompt and courteous service. | Take and prepare to-go orders.</t>
+  </si>
+  <si>
+    <t>35-9099.00</t>
+  </si>
+  <si>
+    <t>Food Preparation and Serving Related Workers, All Other</t>
+  </si>
+  <si>
+    <t>Cafeteria Worker | Canteen Worker | Concession Worker | Food Runner | Food Service Worker | Kitchen Assistant | Kitchen Helper | Pantry Worker | Service Assistant | Vending Attendant</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Food Production | English Language | Production and Processing | Education and Training</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Finger Dexterity | Arm-Hand Steadiness | Multilimb Coordination | Control Precision | Static Strength | Trunk Strength | Stamina | Near Vision | Far Vision | Depth Perception | Gross Body Coordination | Gross Body Equilibrium | Extent Flexibility | Reaction Time | Problem Sensitivity | Oral Comprehension | Selective Attention | Oral Expression | Speech Clarity</t>
+  </si>
+  <si>
+    <t>Spend Time Standing | Indoors, Not Environmentally Controlled | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Very Hot or Cold Temperatures | Exposed to Minor Burns, Cuts, Bites, or Stings | Exposed to Hazardous Equipment | Time Pressure | Importance of Repeating Same Tasks | Spend Time Making Repetitive Motions | Physical Proximity | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Importance of Being Exact or Accurate | Spend Time Walking or Running | Health and Safety of Other Workers | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Deal With External Customers or the Public in General</t>
+  </si>
+  <si>
+    <t>Food Preparation Workers | Fast Food and Counter Workers | Dining Room and Cafeteria Attendants and Bartender Helpers | Dishwashers | Food Servers, Nonrestaurant | Waiters and Waitresses | Baristas | Bartenders | Hosts and Hostesses, Restaurant, Lounge, and Coffee Shop | Cooks, Fast Food | Cooks, Institution and Cafeteria | Cooks, Restaurant | Cooks, Short Order | Cooks, All Other | Chefs and Head Cooks | First-Line Supervisors of Food Preparation and Serving Workers | Food Service Managers | Cashiers | Counter and Rental Clerks | Amusement and Recreation Attendants</t>
+  </si>
+  <si>
+    <t>All food preparation and serving related workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Perform food preparation and service duties not classified separately. | Assemble, portion, and package food items for service or distribution. | Stock service lines, display cases, and vending equipment. | Serve food and beverages to customers, patients, or residents. | Operate cash registers and process payments for food purchases. | Clean and sanitize dining areas, service counters, and equipment. | Wash, peel, cut, and prepare fruits, vegetables, and other ingredients. | Receive, inspect, and store food deliveries and supplies. | Monitor food temperatures and discard items past safe holding times. | Set up and break down serving stations, buffets, and catering events. | Respond to customer requests and report complaints to supervisors. | Follow sanitation, food safety, and personal hygiene requirements. | Remove trash, recycling, and food waste from work areas. | Assist cooks and servers during peak service periods.</t>
+  </si>
+  <si>
+    <t>37-1011.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Housekeeping and Janitorial Workers</t>
+  </si>
+  <si>
+    <t>Building Services Supervisor | Buildings and Grounds Supervisor | Custodian Supervisor | Environmental Services Supervisor (EVS) | Executive Housekeeper | Housekeeping Supervisor | Janitorial Supervisor | Laundry Supervisor | Maintenance Supervisor</t>
+  </si>
+  <si>
+    <t>Computerized bed control system software | Computerized maintenance management system CMMS | Email software | Facebook | Facility use software | Help desk software | Inventory tracking software | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | SAP software</t>
+  </si>
+  <si>
+    <t>Monitoring | Speaking | Active Listening | Critical Thinking | Learning Strategies | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Administration and Management | Education and Training | Public Safety and Security | Personnel and Human Resources | Administrative</t>
+  </si>
+  <si>
+    <t>Oral Expression | Oral Comprehension | Problem Sensitivity | Information Ordering | Near Vision | Speech Recognition | Speech Clarity | Category Flexibility | Deductive Reasoning | Written Expression | Written Comprehension | Far Vision | Manual Dexterity | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | E-Mail | Indoors, Environmentally Controlled | Telephone Conversations | Work Outcomes and Results of Other Workers | Contact With Others | Time Pressure | Health and Safety of Other Workers | Coordinate or Lead Others in Accomplishing Work Activities | Importance of Being Exact or Accurate | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals | Spend Time Standing | Frequency of Decision Making | Spend Time Walking or Running | Freedom to Make Decisions</t>
+  </si>
+  <si>
+    <t>Administrative Services Managers | Facilities Managers | First-Line Supervisors of Construction Trades and Extraction Workers | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Farming, Fishing, and Forestry Workers | First-Line Supervisors of Food Preparation and Serving Workers | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Landscaping, Lawn Service, and Groundskeeping Workers | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Mechanics, Installers, and Repairers | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Office and Administrative Support Workers | First-Line Supervisors of Passenger Attendants | First-Line Supervisors of Personal Service Workers | First-Line Supervisors of Production and Operating Workers | First-Line Supervisors of Retail Sales Workers | First-Line Supervisors of Security Workers | General and Operations Managers | Maids and Housekeeping Cleaners | Recycling Coordinators</t>
+  </si>
+  <si>
+    <t>Directly supervise and coordinate work activities of cleaning personnel in hotels, hospitals, offices, and other establishments.</t>
+  </si>
+  <si>
+    <t>Advise managers, desk clerks, or admitting personnel of rooms ready for occupancy. | Check and maintain equipment to ensure that it is in working order. | Confer with staff to resolve performance and personnel problems, and to discuss company policies. | Coordinate activities with other departments to ensure that services are provided in an efficient and timely manner. | Direct activities for stopping the spread of infections in facilities, such as hospitals. | Establish and implement operational standards and procedures for the departments supervised. | Evaluate employee performance and recommend personnel actions, such as promotions, transfers, and dismissals. | Forecast necessary levels of staffing and stock at different times to facilitate effective scheduling and ordering. | Inspect and evaluate the physical condition of facilities to determine the type of work required. | Inspect work performed to ensure that it meets specifications and established standards. | Instruct staff in work policies and procedures, and the use and maintenance of equipment. | Inventory stock to ensure that supplies and equipment are available in adequate amounts. | Investigate complaints about service and equipment, and take corrective action. | Issue supplies and equipment to workers. | Maintain required records of work hours, budgets, payrolls, and other information. | Perform financial tasks, such as estimating costs and preparing and managing budgets. | Perform grounds maintenance tasks, such as removing snow and mowing the lawn. | Perform or assist with cleaning duties as necessary. | Plan and prepare employee work schedules. | Prepare reports on activity, personnel, and information, such as occupancy, hours worked, facility usage, work performed, and departmental expenses. | Recommend changes that could improve service and increase operational efficiency. | Recommend or arrange for additional services, such as painting, repair work, renovations, and the replacement of furnishings and equipment. | Screen job applicants, and hire new employees. | Select and order or purchase new equipment, supplies, or furnishings. | Select the most suitable cleaning materials for different types of linens, furniture, flooring, and surfaces. | Supervise in-house services, such as laundries, maintenance and repair, dry cleaning, or valet services.</t>
+  </si>
+  <si>
+    <t>37-1012.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Landscaping, Lawn Service, and Groundskeeping Workers</t>
+  </si>
+  <si>
+    <t>Field Manager | Golf Course Superintendent | Grounds Crew Supervisor | Grounds Foreman | Grounds Maintenance Supervisor | Grounds Manager | Grounds Supervisor | Groundskeeper Supervisor | Landscape Manager | Landscape Supervisor</t>
+  </si>
+  <si>
+    <t>Facebook | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Payroll software | Work order software</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Speaking | Critical Thinking | Reading Comprehension | Learning Strategies | Active Learning | Writing</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Administration and Management | Mathematics | Public Safety and Security | Personnel and Human Resources | Mechanical | Education and Training | Chemistry | Building and Construction | Design | Administrative</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Near Vision | Speech Recognition | Speech Clarity | Written Comprehension | Visualization | Arm-Hand Steadiness | Time Sharing | Perceptual Speed | Flexibility of Closure | Information Ordering | Far Vision | Inductive Reasoning | Deductive Reasoning | Written Expression | Fluency of Ideas | Static Strength | Multilimb Coordination | Control Precision | Finger Dexterity | Manual Dexterity | Selective Attention</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Telephone Conversations | Coordinate or Lead Others in Accomplishing Work Activities | Health and Safety of Other Workers | Exposed to Minor Burns, Cuts, Bites, or Stings | Frequency of Decision Making | Work Outcomes and Results of Other Workers | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Determine Tasks, Priorities and Goals | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Time Pressure | In an Enclosed Vehicle or Operate Enclosed Equipment | Exposed to Very Hot or Cold Temperatures | Impact of Decisions on Co-workers or Company Results | Exposed to Hazardous Equipment | Freedom to Make Decisions | E-Mail | Deal With External Customers or the Public in General | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Being Exact or Accurate | Exposed to Contaminants | Spend Time Standing | Spend Time Walking or Running | Consequence of Error | Physical Proximity | Conflict Situations</t>
+  </si>
+  <si>
+    <t>Civil Engineering Technologists and Technicians | Construction Managers | First-Line Supervisors of Construction Trades and Extraction Workers | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Farming, Fishing, and Forestry Workers | First-Line Supervisors of Food Preparation and Serving Workers | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Mechanics, Installers, and Repairers | First-Line Supervisors of Office and Administrative Support Workers | First-Line Supervisors of Passenger Attendants | First-Line Supervisors of Personal Service Workers | First-Line Supervisors of Production and Operating Workers | First-Line Supervisors of Security Workers | Forest and Conservation Technicians | General and Operations Managers | Landscaping and Groundskeeping Workers | Maintenance and Repair Workers, General | Solar Energy Installation Managers</t>
+  </si>
+  <si>
+    <t>Directly supervise and coordinate activities of workers engaged in landscaping or groundskeeping activities. Work may involve reviewing contracts to ascertain service, machine, and workforce requirements; answering inquiries from potential customers regarding methods, material, and price ranges; and preparing estimates according to labor, material, and machine costs.</t>
+  </si>
+  <si>
+    <t>Answer inquiries from current or prospective customers regarding methods, materials, or price ranges. | Confer with managers or landscape architects to develop plans or schedules for landscaping maintenance or improvement. | Confer with other supervisors to coordinate work activities with those of other departments or units. | Design or supervise the installation of sprinkler systems, calculating water pressure, or valve and pipe coverage needs. | Direct activities of workers who perform duties, such as landscaping, cultivating lawns, or pruning trees and shrubs. | Direct or assist workers engaged in the maintenance or repair of equipment, such as power tools or motorized equipment. | Direct or perform mixing or application of fertilizers, insecticides, herbicides, or fungicides. | Establish and enforce operating procedures and work standards that will ensure adequate performance and personnel safety. | Identify diseases or pests affecting landscaping and order appropriate treatments. | Inspect completed work to ensure conformance to specifications, standards, and contract requirements. | Install or maintain landscaped areas, performing tasks such as removing snow, pouring cement curbs, or repairing sidewalks. | Inventory supplies of tools, equipment, or materials to ensure that sufficient supplies are available and items are in usable condition. | Investigate work-related complaints to verify problems and to determine responses. | Maintain required records, such as personnel information or project records. | Monitor project activities to ensure that instructions are followed, deadlines are met, and schedules are maintained. | Negotiate with customers regarding fees for landscaping, lawn service, or groundskeeping work. | Order the performance of corrective work when problems occur and recommend procedural changes to avoid such problems. | Perform administrative duties, such as authorizing leaves or processing time sheets. | Perform personnel-related activities, such as hiring workers, evaluating staff performance, or taking disciplinary actions when performance problems occur. | Plant or maintain vegetation through activities such as mulching, fertilizing, watering, mowing, or pruning. | Prepare or maintain required records, such as work activity or personnel reports. | Prepare service estimates based on labor, material, and machine costs and maintain budgets for individual projects. | Provide workers with assistance in performing duties as necessary to meet deadlines. | Recommend changes in working conditions or equipment used to increase crew efficiency. | Review contracts or work assignments to determine service, machine, or workforce requirements for jobs. | Schedule work for crews, depending on work priorities, crew or equipment availability, or weather conditions. | Tour grounds, such as parks, botanical gardens, cemeteries, or golf courses, to inspect conditions of plants and soil. | Train workers in tasks such as transplanting or pruning trees or shrubs, finishing cement, using equipment, or caring for turf.</t>
+  </si>
+  <si>
+    <t>37-2011.00</t>
+  </si>
+  <si>
+    <t>Janitors and Cleaners, Except Maids and Housekeeping Cleaners</t>
+  </si>
+  <si>
+    <t>Building Custodian | Building Services Technician (Building Services Tech) | Building Services Worker | Cleaner | Custodial Worker | Custodian | Facilities Worker | Heavy Duty Custodian | Janitor | School Custodian</t>
+  </si>
+  <si>
+    <t>Eko | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Squeegee</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Administration and Management</t>
+  </si>
+  <si>
+    <t>Trunk Strength | Near Vision | Extent Flexibility | Static Strength | Manual Dexterity | Arm-Hand Steadiness | Problem Sensitivity | Oral Expression | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Walking or Running | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Standing | Health and Safety of Other Workers | Contact With Others</t>
+  </si>
+  <si>
+    <t>Carpet Installers | Cleaners of Vehicles and Equipment | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Coating, Painting, and Spraying Machine Setters, Operators, and Tenders | Construction Laborers | Dishwashers | First-Line Supervisors of Housekeeping and Janitorial Workers | Floor Sanders and Finishers | Furniture Finishers | Hazardous Materials Removal Workers | Helpers--Extraction Workers | Helpers--Painters, Paperhangers, Plasterers, and Stucco Masons | Laborers and Freight, Stock, and Material Movers, Hand | Landscaping and Groundskeeping Workers | Laundry and Dry-Cleaning Workers | Maids and Housekeeping Cleaners | Maintenance and Repair Workers, General | Recycling and Reclamation Workers | Septic Tank Servicers and Sewer Pipe Cleaners | Water and Wastewater Treatment Plant and System Operators</t>
+  </si>
+  <si>
+    <t>Keep buildings in clean and orderly condition. Perform heavy cleaning duties, such as cleaning floors, shampooing rugs, washing walls and glass, and removing rubbish. Duties may include tending furnace and boiler, performing routine maintenance activities, notifying management of need for repairs, and cleaning snow or debris from sidewalk.</t>
+  </si>
+  <si>
+    <t>Clean and polish furniture and fixtures. | Clean building floors by sweeping, mopping, scrubbing, or vacuuming. | Clean chimneys, flues, and connecting pipes, using power or hand tools. | Clean windows, glass partitions, or mirrors, using soapy water or other cleaners, sponges, or squeegees. | Drive vans, industrial trucks, or other vehicles required to travel to, or to perform, cleaning work. | Dust furniture, walls, machines, or equipment. | Follow procedures for the use of chemical cleaners and power equipment to prevent damage to floors and fixtures. | Gather and empty trash. | Make adjustments or minor repairs to heating, cooling, ventilating, plumbing, or electrical systems. | Mix water and detergents or acids in containers to prepare cleaning solutions, according to specifications. | Monitor building security and safety by performing tasks such as locking doors after operating hours or checking electrical appliance use to ensure that hazards are not created. | Move heavy furniture, equipment, or supplies, either manually or with hand trucks. | Mow or trim lawns or shrubbery, using mowers or hand or power trimmers, and clear debris from grounds. | Notify managers concerning the need for major repairs or additions to building operating systems. | Remove snow from sidewalks, driveways, or parking areas, using snowplows, snow blowers, or snow shovels, or spread snow-melting chemicals. | Requisition supplies or equipment needed for cleaning and maintenance duties. | Service, clean, or supply restrooms. | Set up, arrange, or remove decorations, tables, chairs, ladders, or scaffolding to prepare facilities for events, such as banquets or meetings. | Spray insecticides or fumigants to prevent insect or rodent infestation. | Steam-clean or shampoo carpets. | Strip, seal, finish, and polish floors.</t>
+  </si>
+  <si>
+    <t>37-2012.00</t>
+  </si>
+  <si>
+    <t>Maids and Housekeeping Cleaners</t>
+  </si>
+  <si>
+    <t>Chambermaid | Cleaner | Cottage Attendant | Environmental Services Aide | Environmental Services Worker | Guest Room Attendant (GRA) | Housekeeper | Housekeeping Laundry Worker | Room Cleaner</t>
+  </si>
+  <si>
+    <t>Blink | Computerized bed control system software | Computerized maintenance management system CMMS | Eko | Email software | Facebook | Inventory tracking software | Microsoft Excel | Microsoft Windows</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Public Safety and Security</t>
+  </si>
+  <si>
+    <t>Trunk Strength | Near Vision | Extent Flexibility | Stamina | Oral Expression | Oral Comprehension</t>
+  </si>
+  <si>
+    <t>Spend Time Standing | Spend Time Making Repetitive Motions | Spend Time Walking or Running | Spend Time Bending or Twisting Your Body | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Work With or Contribute to a Work Group or Team | Time Pressure | Contact With Others | Exposed to Contaminants | Importance of Being Exact or Accurate | Spend Time Kneeling, Crouching, Stooping, or Crawling</t>
+  </si>
+  <si>
+    <t>Carpet Installers | Cleaners of Vehicles and Equipment | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Dining Room and Cafeteria Attendants and Bartender Helpers | Dishwashers | Fast Food and Counter Workers | First-Line Supervisors of Housekeeping and Janitorial Workers | Floor Sanders and Finishers | Food Preparation Workers | Food Servers, Nonrestaurant | Furniture Finishers | Helpers--Painters, Paperhangers, Plasterers, and Stucco Masons | Helpers--Production Workers | Hotel, Motel, and Resort Desk Clerks | Janitors and Cleaners, Except Maids and Housekeeping Cleaners | Laundry and Dry-Cleaning Workers | Locker Room, Coatroom, and Dressing Room Attendants | Painting, Coating, and Decorating Workers | Pressers, Textile, Garment, and Related Materials | Recycling and Reclamation Workers</t>
+  </si>
+  <si>
+    <t>Perform any combination of light cleaning duties to maintain private households or commercial establishments, such as hotels and hospitals, in a clean and orderly manner. Duties may include making beds, replenishing linens, cleaning rooms and halls, and vacuuming.</t>
+  </si>
+  <si>
+    <t>Carry linens, towels, toilet items, and cleaning supplies, using wheeled carts. | Clean rooms, hallways, lobbies, lounges, restrooms, corridors, elevators, stairways, locker rooms, and other work areas so that health standards are met. | Clean rugs, carpets, upholstered furniture, and draperies, using vacuum cleaners and shampooers. | Deliver television sets, ironing boards, baby cribs, and rollaway beds to guests' rooms. | Disinfect equipment and supplies, using germicides or steam-operated sterilizers. | Dust and polish furniture and equipment. | Empty wastebaskets, empty and clean ashtrays, and transport other trash and waste to disposal areas. | Hang draperies and dust window blinds. | Keep storage areas and carts well-stocked, clean, and tidy. | Move and arrange furniture and turn mattresses. | Observe precautions required to protect hotel and guest property and report damage, theft, and found articles to supervisors. | Polish silver accessories and metalwork, such as fixtures and fittings. | Prepare rooms for meetings and arrange decorations, media equipment, and furniture for social or business functions. | Replace light bulbs. | Replenish supplies, such as drinking glasses, linens, writing supplies, and bathroom items. | Request repair services and wait for repair workers to arrive. | Sort clothing and other articles, load washing machines, and iron and fold dried items. | Sort, count, and mark clean linens and store them in linen closets. | Sweep, scrub, wax, or polish floors, using brooms, mops, or powered scrubbing and waxing machines. | Wash windows, walls, ceilings, and woodwork, waxing and polishing as necessary.</t>
+  </si>
+  <si>
+    <t>37-2019.00</t>
+  </si>
+  <si>
+    <t>Building Cleaning Workers, All Other</t>
+  </si>
+  <si>
+    <t>Cleaning Technician | Carpet Cleaner | Building Cleaner | Floor Care Technician | Industrial Cleaner | Pressure Washer Operator | Window Cleaner | Sanitation Worker | Custodial Worker | Restoration Cleaning Technician</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Chemistry | Public Safety and Security | Administration and Management | Mechanical</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Finger Dexterity | Arm-Hand Steadiness | Multilimb Coordination | Control Precision | Static Strength | Trunk Strength | Stamina | Near Vision | Far Vision | Depth Perception | Gross Body Coordination | Gross Body Equilibrium | Extent Flexibility | Reaction Time | Problem Sensitivity | Oral Comprehension | Selective Attention</t>
+  </si>
+  <si>
+    <t>Spend Time Standing | Spend Time Walking or Running | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Spend Time Bending or Twisting Your Body | Spend Time Making Repetitive Motions | Exposed to Contaminants | Indoors, Not Environmentally Controlled | Importance of Repeating Same Tasks | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Physical Proximity | Contact With Others | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Health and Safety of Other Workers | Exposed to Hazardous Conditions | Freedom to Make Decisions | Spend Time Climbing Ladders, Scaffolds, or Poles | Exposed to High Places | Spend Time Kneeling, Crouching, Stooping, or Crawling</t>
+  </si>
+  <si>
+    <t>Janitors and Cleaners, Except Maids and Housekeeping Cleaners | Maids and Housekeeping Cleaners | First-Line Supervisors of Housekeeping and Janitorial Workers | Pest Control Workers | Landscaping and Groundskeeping Workers | Grounds Maintenance Workers, All Other | Hazardous Materials Removal Workers | Laundry and Dry-Cleaning Workers | Maintenance and Repair Workers, General | Facilities Managers | Helpers--Installation, Maintenance, and Repair Workers | Industrial Truck and Tractor Operators | Laborers and Freight, Stock, and Material Movers, Hand | Cleaners of Vehicles and Equipment | Recycling and Reclamation Workers | Refuse and Recyclable Material Collectors | Security Guards | First-Line Supervisors of Landscaping, Lawn Service, and Groundskeeping Workers | Pesticide Handlers, Sprayers, and Applicators, Vegetation | Septic Tank Servicers and Sewer Pipe Cleaners</t>
+  </si>
+  <si>
+    <t>All building cleaning workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Perform building cleaning duties in roles not classified separately. | Clean interior and exterior surfaces using specialized equipment and chemicals. | Operate pressure washers, extractors, floor machines, and steam cleaners. | Mix and apply cleaning solutions according to manufacturer instructions. | Clean carpets, upholstery, windows, ducts, and hard-to-reach surfaces. | Inspect areas before and after cleaning to verify results meet standards. | Move and protect furniture, equipment, and fixtures during cleaning. | Follow safety procedures for chemicals, ladders, and powered equipment. | Maintain and perform minor repairs on cleaning equipment. | Monitor supply levels and request replacement materials. | Report maintenance problems, damage, and safety hazards to supervisors. | Dispose of waste and hazardous materials according to regulations. | Record work completed, areas serviced, and time expended. | Respond to customer requests and special cleaning assignments.</t>
+  </si>
+  <si>
+    <t>37-2021.00</t>
+  </si>
+  <si>
+    <t>Pest Control Workers</t>
+  </si>
+  <si>
+    <t>Certified Pest Control Technician | Commercial Pest Control Technician | Exterminator | Pest Control Applicator | Pest Control Chemical Technician | Pest Control Operator | Pest Control Technician (Pest Control Tech) | Pest Technician | Residential Pest Control Technician | Termite Technician</t>
+  </si>
+  <si>
+    <t>Database software | Email software | Intuit QuickBooks | Marathon Data Systems PestPac | Microsoft Excel | Microsoft Office software | Microsoft SharePoint | Microsoft Word | Report writing software | Supply inventory software | Work scheduling software | YouTube</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening | Writing | Monitoring | Speaking | Active Learning | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Public Safety and Security | English Language</t>
+  </si>
+  <si>
+    <t>Near Vision | Oral Comprehension | Oral Expression | Speech Clarity | Written Expression | Problem Sensitivity | Deductive Reasoning | Speech Recognition | Far Vision | Inductive Reasoning | Written Comprehension | Information Ordering | Category Flexibility | Flexibility of Closure | Extent Flexibility | Trunk Strength | Control Precision | Manual Dexterity | Arm-Hand Steadiness | Time Sharing | Selective Attention | Visualization | Visual Color Discrimination</t>
+  </si>
+  <si>
+    <t>In an Enclosed Vehicle or Operate Enclosed Equipment | Face-to-Face Discussions with Individuals and Within Teams | Outdoors, Exposed to All Weather Conditions | Telephone Conversations | Exposed to Contaminants | Freedom to Make Decisions | Frequency of Decision Making | Contact With Others | Determine Tasks, Priorities and Goals | Impact of Decisions on Co-workers or Company Results | Time Pressure | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Being Exact or Accurate | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Deal With External Customers or the Public in General | Spend Time Walking or Running | Spend Time Standing | Spend Time Making Repetitive Motions | Exposed to Very Hot or Cold Temperatures | Exposed to Minor Burns, Cuts, Bites, or Stings | Exposed to Cramped Work Space, Awkward Positions</t>
+  </si>
+  <si>
+    <t>Agricultural Inspectors | Agricultural Technicians | Brownfield Redevelopment Specialists and Site Managers | Construction and Building Inspectors | Environmental Engineering Technologists and Technicians | Environmental Engineers | Environmental Science and Protection Technicians, Including Health | Farmworkers and Laborers, Crop, Nursery, and Greenhouse | First-Line Supervisors of Farming, Fishing, and Forestry Workers | First-Line Supervisors of Landscaping, Lawn Service, and Groundskeeping Workers | Hazardous Materials Removal Workers | Highway Maintenance Workers | Janitors and Cleaners, Except Maids and Housekeeping Cleaners | Landscaping and Groundskeeping Workers | Maintenance and Repair Workers, General | Occupational Health and Safety Specialists | Pesticide Handlers, Sprayers, and Applicators, Vegetation | Septic Tank Servicers and Sewer Pipe Cleaners | Soil and Plant Scientists | Water and Wastewater Treatment Plant and System Operators</t>
+  </si>
+  <si>
+    <t>Apply or release chemical solutions or toxic gases and set traps to kill or remove pests and vermin that infest buildings and surrounding areas.</t>
+  </si>
+  <si>
+    <t>Clean and remove blockages from infested areas to facilitate spraying procedures and provide drainage, using brooms, mops, shovels, or rakes. | Clean work site after completion of job. | Cut or bore openings in building or surrounding concrete, access infested areas, insert nozzle, and inject pesticide to impregnate ground. | Direct, or assist other workers in, treatment or extermination processes to eliminate or control rodents, insects, or weeds. | Drive truck equipped with power spraying equipment. | Inspect premises to identify infestation source and extent of damage to property, wall, or roof porosity and access to infested locations. | Measure area dimensions requiring treatment, calculate fumigant requirements, and estimate cost for service. | Post warning signs and lock building doors to secure area to be fumigated. | Recommend treatment and prevention methods for pest problems to clients. | Record work activities performed. | Set mechanical traps, or place poisonous paste or bait in sewers, burrows, or ditches. | Spray or dust chemical solutions, powders, or gases into rooms, onto clothing, furnishings, or wood, or over marshlands, ditches, or catch basins. | Study preliminary reports or diagrams of infested area and determine treatment type required to eliminate and prevent recurrence of infestation.</t>
+  </si>
+  <si>
+    <t>37-3011.00</t>
+  </si>
+  <si>
+    <t>Landscaping and Groundskeeping Workers</t>
+  </si>
+  <si>
+    <t>Gardener | Greenskeeper | Grounds Maintenance Worker | Grounds Person | Grounds Specialist | Grounds Worker | Groundskeeper | Landscape Specialist | Landscape Technician | Outside Maintenance Worker</t>
+  </si>
+  <si>
+    <t>Facebook | IBM Notes | Microsoft Excel | Microsoft Office software | Microsoft Windows | Microsoft Word</t>
+  </si>
+  <si>
+    <t>English Language | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Multilimb Coordination | Manual Dexterity | Trunk Strength | Arm-Hand Steadiness | Extent Flexibility | Static Strength | Control Precision | Near Vision | Stamina | Visualization | Problem Sensitivity</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Exposed to Very Hot or Cold Temperatures | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Hazardous Equipment | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Contaminants | Physical Proximity | Spend Time Walking or Running | Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | In an Open Vehicle or Operating Equipment | Pace Determined by Speed of Equipment | Exposed to Minor Burns, Cuts, Bites, or Stings</t>
+  </si>
+  <si>
+    <t>Agricultural Equipment Operators | Cement Masons and Concrete Finishers | Construction Laborers | Fallers | Farm Equipment Mechanics and Service Technicians | Farmworkers and Laborers, Crop, Nursery, and Greenhouse | First-Line Supervisors of Landscaping, Lawn Service, and Groundskeeping Workers | Forest and Conservation Workers | Helpers--Painters, Paperhangers, Plasterers, and Stucco Masons | Helpers--Pipelayers, Plumbers, Pipefitters, and Steamfitters | Highway Maintenance Workers | Janitors and Cleaners, Except Maids and Housekeeping Cleaners | Maintenance and Repair Workers, General | Operating Engineers and Other Construction Equipment Operators | Paving, Surfacing, and Tamping Equipment Operators | Pesticide Handlers, Sprayers, and Applicators, Vegetation | Plumbers, Pipefitters, and Steamfitters | Roustabouts, Oil and Gas | Septic Tank Servicers and Sewer Pipe Cleaners | Tree Trimmers and Pruners</t>
+  </si>
+  <si>
+    <t>Landscape or maintain grounds of property using hand or power tools or equipment. Workers typically perform a variety of tasks, which may include any combination of the following: sod laying, mowing, trimming, planting, watering, fertilizing, digging, raking, sprinkler installation, and installation of mortarless segmental concrete masonry wall units.</t>
+  </si>
+  <si>
+    <t>Advise customers on plant selection or care. | Attach wires from planted trees to support stakes. | Build forms and mix and pour cement to form garden borders. | Care for artificial turf fields, periodically removing the turf and replacing cushioning pads or vacuuming and disinfecting the turf after use to prevent the growth of harmful bacteria. | Care for established lawns by mulching, aerating, weeding, grubbing, removing thatch, or trimming or edging around flower beds, walks, or walls. | Care for natural turf fields, making sure the underlying soil has the required composition to allow proper drainage and to support the grasses. | Decorate gardens with stones or plants. | Follow planned landscaping designs to determine where to lay sod, sow grass, or plant flowers or foliage. | Gather and remove litter. | Haul or spread topsoil, or spread straw over seeded soil to hold soil in place. | Install rock gardens, ponds, decks, drainage systems, irrigation systems, retaining walls, fences, planters, or playground equipment. | Maintain irrigation systems, including winterizing the systems and starting them up in spring. | Maintain or repair tools, equipment, or structures, such as buildings, greenhouses, fences, or benches, using hand or power tools. | Mix and spray or spread fertilizers, herbicides, or insecticides onto grass, shrubs, or trees, using hand or automatic sprayers or spreaders. | Mow or edge lawns, using power mowers or edgers. | Operate vehicles or powered equipment, such as mowers, tractors, twin-axle vehicles, snow blowers, chainsaws, electric clippers, sod cutters, or pruning saws. | Plan or cultivate lawns or gardens. | Plant seeds, bulbs, foliage, flowering plants, grass, ground covers, trees, or shrubs, and apply mulch for protection, using gardening tools. | Provide proper upkeep of sidewalks, driveways, parking lots, fountains, planters, burial sites, or other grounds features. | Prune or trim trees, shrubs, or hedges, using shears, pruners, or chain saws. | Rake, mulch, and compost leaves. | Shovel snow from walks, driveways, or parking lots, and spread salt in those areas. | Trim or pick flowers and clean flower beds. | Use hand tools, such as shovels, rakes, pruning saws, saws, hedge or brush trimmers, or axes. | Use irrigation methods to adjust the amount of water consumption and to prevent waste. | Water lawns, trees, or plants, using portable sprinkler systems, hoses, or watering cans.</t>
+  </si>
+  <si>
+    <t>37-3012.00</t>
+  </si>
+  <si>
+    <t>Pesticide Handlers, Sprayers, and Applicators, Vegetation</t>
+  </si>
+  <si>
+    <t>Chemical Applicator | Integrated Pest Management Technician (IPM Technician) | Lawn Specialist | Lawn Technician | Licensed Pesticide Applicator | Pest Control Technician | Pesticide Applicator | Spray Applicator | Spray Technician | Tree and Shrub Technician</t>
+  </si>
+  <si>
+    <t>Customer database software | Facebook | Geographic information system GIS systems | Google Android | Materials inventory software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Rate calculation software | Unit conversion software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Critical Thinking | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Biology | Production and Processing | English Language | Administration and Management | Public Safety and Security | Education and Training | Law and Government | Mathematics | Transportation | Chemistry | Mechanical</t>
+  </si>
+  <si>
+    <t>Near Vision | Control Precision | Arm-Hand Steadiness | Speech Recognition | Oral Comprehension | Problem Sensitivity | Deductive Reasoning | Multilimb Coordination | Manual Dexterity | Oral Expression | Written Comprehension | Speech Clarity | Depth Perception | Static Strength | Selective Attention | Category Flexibility | Information Ordering | Inductive Reasoning</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | In an Enclosed Vehicle or Operate Enclosed Equipment | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Frequency of Decision Making | Exposed to Contaminants | Impact of Decisions on Co-workers or Company Results | Freedom to Make Decisions | Face-to-Face Discussions with Individuals and Within Teams | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Being Exact or Accurate | Telephone Conversations | Time Pressure | Exposed to Hazardous Conditions | Deal With External Customers or the Public in General | Exposed to Minor Burns, Cuts, Bites, or Stings | Consequence of Error | Determine Tasks, Priorities and Goals | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Contact With Others | Exposed to Very Hot or Cold Temperatures | Work With or Contribute to a Work Group or Team | Coordinate or Lead Others in Accomplishing Work Activities | Exposed to Hazardous Equipment</t>
+  </si>
+  <si>
+    <t>Agricultural Equipment Operators | Agricultural Technicians | Chemical Plant and System Operators | Cleaners of Vehicles and Equipment | Cleaning, Washing, and Metal Pickling Equipment Operators and Tenders | Coating, Painting, and Spraying Machine Setters, Operators, and Tenders | Farmworkers and Laborers, Crop, Nursery, and Greenhouse | Hazardous Materials Removal Workers | Landscaping and Groundskeeping Workers | Laundry and Dry-Cleaning Workers | Mixing and Blending Machine Setters, Operators, and Tenders | Painting, Coating, and Decorating Workers | Pest Control Workers | Plating Machine Setters, Operators, and Tenders, Metal and Plastic | Pump Operators, Except Wellhead Pumpers | Separating, Filtering, Clarifying, Precipitating, and Still Machine Setters, Operators, and Tenders | Septic Tank Servicers and Sewer Pipe Cleaners | Soil and Plant Scientists | Tree Trimmers and Pruners | Water and Wastewater Treatment Plant and System Operators</t>
+  </si>
+  <si>
+    <t>Mix or apply pesticides, herbicides, fungicides, or insecticides through sprays, dusts, vapors, soil incorporation, or chemical application on trees, shrubs, lawns, or crops. Usually requires specific training and state or federal certification.</t>
+  </si>
+  <si>
+    <t>Clean or service machinery to ensure operating efficiency, using water, gasoline, lubricants, or hand tools. | Connect hoses and nozzles selected according to terrain, distribution pattern requirements, types of infestations, and velocities. | Cover areas to specified depths with pesticides, applying knowledge of weather conditions, droplet sizes, elevation-to-distance ratios, and obstructions. | Fill sprayer tanks with water and chemicals, according to formulas. | Identify lawn or plant diseases to determine the appropriate course of treatment. | Lift, push, and swing nozzles, hoses, and tubes to direct spray over designated areas. | Mix pesticides, herbicides, or fungicides for application to trees, shrubs, lawns, or botanical crops. | Plant grass with seed spreaders, and operate straw blowers to cover seeded areas with mixtures of asphalt and straw. | Provide driving instructions to truck drivers to ensure complete coverage of designated areas, using hand and horn signals. | Start motors and engage machinery, such as sprayer agitators or pumps or portable spray equipment.</t>
+  </si>
+  <si>
+    <t>37-3013.00</t>
+  </si>
+  <si>
+    <t>Tree Trimmers and Pruners</t>
+  </si>
+  <si>
+    <t>Arborist | Climber | Grounds Worker | Groundsman | Laborer | Plant Health Care Technician | Tree Climber | Tree Trimmer | Trimmer</t>
+  </si>
+  <si>
+    <t>Facebook | Microsoft Excel | Microsoft Outlook | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Monitoring | Speaking</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Mechanical</t>
+  </si>
+  <si>
+    <t>Control Precision | Manual Dexterity | Multilimb Coordination | Reaction Time | Problem Sensitivity | Static Strength | Extent Flexibility | Arm-Hand Steadiness | Oral Comprehension | Trunk Strength | Near Vision | Selective Attention | Dynamic Strength | Far Vision | Deductive Reasoning | Stamina | Gross Body Equilibrium | Depth Perception | Finger Dexterity | Visualization | Inductive Reasoning | Oral Expression | Spatial Orientation | Flexibility of Closure | Information Ordering | Auditory Attention | Gross Body Coordination | Rate Control | Speech Clarity | Speech Recognition</t>
+  </si>
+  <si>
+    <t>Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Outdoors, Exposed to All Weather Conditions | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Frequency of Decision Making | Exposed to Hazardous Equipment | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Impact of Decisions on Co-workers or Company Results | Work With or Contribute to a Work Group or Team | Contact With Others | Spend Time Standing | Exposed to Very Hot or Cold Temperatures | In an Enclosed Vehicle or Operate Enclosed Equipment | Health and Safety of Other Workers | Work Outcomes and Results of Other Workers | Telephone Conversations | Exposed to High Places | Importance of Being Exact or Accurate | Consequence of Error | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Minor Burns, Cuts, Bites, or Stings | Time Pressure | Spend Time Bending or Twisting Your Body | Exposed to Contaminants | Spend Time Making Repetitive Motions | Level of Competition</t>
+  </si>
+  <si>
+    <t>Agricultural Equipment Operators | Construction Laborers | Fallers | Farmworkers and Laborers, Crop, Nursery, and Greenhouse | Forest and Conservation Technicians | Forest and Conservation Workers | Grinding and Polishing Workers, Hand | Helpers--Extraction Workers | Highway Maintenance Workers | Hoist and Winch Operators | Laborers and Freight, Stock, and Material Movers, Hand | Landscaping and Groundskeeping Workers | Logging Equipment Operators | Operating Engineers and Other Construction Equipment Operators | Pesticide Handlers, Sprayers, and Applicators, Vegetation | Riggers | Roustabouts, Oil and Gas | Sawing Machine Setters, Operators, and Tenders, Wood | Tool Grinders, Filers, and Sharpeners | Woodworking Machine Setters, Operators, and Tenders, Except Sawing</t>
+  </si>
+  <si>
+    <t>Using sophisticated climbing and rigging techniques, cut away dead or excess branches from trees or shrubs to maintain right-of-way for roads, sidewalks, or utilities, or to improve appearance, health, and value of tree. Prune or treat trees or shrubs using handsaws, hand pruners, clippers, and power pruners. Works off the ground in the tree canopy and may use truck-mounted lifts.</t>
+  </si>
+  <si>
+    <t>Apply tar or other protective substances to cut surfaces or seal surfaces and to protect them from fungi and insects. | Cable, brace, tie, bolt, stake, and guy trees and branches to provide support. | Clean, sharpen, and lubricate tools and equipment. | Clear sites, streets, and grounds of woody and herbaceous materials, such as tree stumps and fallen trees and limbs. | Climb trees, using climbing hooks and belts, or climb ladders to gain access to work areas. | Collect debris and refuse from tree trimming and removal operations into piles, using shovels, rakes, or other tools. | Cut away dead and excess branches from trees, or clear branches around power lines, using climbing equipment or buckets of extended truck booms, or chainsaws, hooks, handsaws, shears, and clippers. | Hoist tools and equipment to tree trimmers, and lower branches with ropes or block and tackle. | Inspect trees to determine if they have diseases or pest problems. | Load debris and refuse onto trucks and haul it away for disposal. | Operate boom trucks, loaders, stump chippers, brush chippers, tractors, power saws, trucks, sprayers, and other equipment and tools. | Operate shredding and chipping equipment, and feed limbs and brush into the machines. | Plan and develop budgets for tree work, and estimate the monetary value of trees. | Provide information to the public regarding trees, such as advice on tree care. | Prune, cut down, fertilize, and spray trees as directed by tree surgeons. | Remove broken limbs from wires, using hooked extension poles. | Scrape decayed matter from cavities in trees and fill holes with cement to promote healing and to prevent further deterioration. | Split logs or wooden blocks into bolts, pickets, posts, or stakes, using hand tools such as ax wedges, sledgehammers, and mallets. | Spray trees to treat diseased or unhealthy trees, including mixing chemicals and calibrating spray equipment. | Supervise others engaged in tree trimming work and train lower-level employees. | Transplant and remove trees and shrubs, and prepare trees for moving. | Trim jagged stumps, using saws or pruning shears. | Trim, top, and reshape trees to achieve attractive shapes or to remove low-hanging branches. | Water, root-feed, and fertilize trees.</t>
+  </si>
+  <si>
+    <t>37-3019.00</t>
+  </si>
+  <si>
+    <t>Grounds Maintenance Workers, All Other</t>
+  </si>
+  <si>
+    <t>Athletic Field Maintenance Worker | Cemetery Worker | Golf Course Worker | Greenskeeper | Grounds Maintenance Worker | Grounds Worker | Irrigation Technician | Park Maintenance Worker | Turf Maintenance Worker | Nursery Grounds Worker</t>
+  </si>
+  <si>
+    <t>Food Production | Mechanical | English Language | Customer and Personal Service | Public Safety and Security | Chemistry | Biology</t>
+  </si>
+  <si>
+    <t>Outdoors, Exposed to All Weather Conditions | Outdoors, Under Cover | Exposed to Very Hot or Cold Temperatures | In an Open Vehicle or Operating Equipment | Spend Time Climbing Ladders, Scaffolds, or Poles | Exposed to High Places | Spend Time Kneeling, Crouching, Stooping, or Crawling | Spend Time Keeping or Regaining Balance | Spend Time Walking or Running | Exposed to Minor Burns, Cuts, Bites, or Stings | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Contaminants | Exposed to Hazardous Equipment | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Repeating Same Tasks | Health and Safety of Other Workers</t>
+  </si>
+  <si>
+    <t>Landscaping and Groundskeeping Workers | Tree Trimmers and Pruners | Pesticide Handlers, Sprayers, and Applicators, Vegetation | First-Line Supervisors of Landscaping, Lawn Service, and Groundskeeping Workers | Pest Control Workers | Janitors and Cleaners, Except Maids and Housekeeping Cleaners | Building Cleaning Workers, All Other | Farmworkers and Laborers, Crop, Nursery, and Greenhouse | Agricultural Equipment Operators | Forest and Conservation Workers | Maintenance and Repair Workers, General | Operating Engineers and Other Construction Equipment Operators | Construction Laborers | Highway Maintenance Workers | Farmers, Ranchers, and Other Agricultural Managers | Soil and Plant Scientists | Forest and Conservation Technicians | Amusement and Recreation Attendants | Facilities Managers | Recreation Workers</t>
+  </si>
+  <si>
+    <t>All grounds maintenance workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Maintain grounds and outdoor areas in roles not classified separately. | Mow, edge, trim, and fertilize turf areas to maintain appearance and health. | Install, adjust, and repair irrigation systems and drainage features. | Plant, water, prune, and mulch trees, shrubs, and flower beds. | Apply fertilizers, herbicides, and pesticides according to label directions. | Prepare and maintain athletic fields, greens, and playing surfaces. | Remove snow, ice, leaves, and debris from walkways and parking areas. | Operate and maintain mowers, trimmers, blowers, and small tractors. | Inspect grounds for hazards, damage, and pest or disease problems. | Repair fences, benches, signs, and other outdoor fixtures. | Follow safety procedures for equipment, chemicals, and personal protection. | Maintain records of applications, maintenance performed, and supplies used. | Assist with special events, setup, and grounds preparation. | Monitor soil, water, and turf conditions and recommend treatments.</t>
+  </si>
+  <si>
+    <t>39-1013.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Gambling Services Workers</t>
+  </si>
+  <si>
+    <t>Casino Manager | Casino Shift Manager (CSM) | Floor Supervisor | Pit Boss | Pit Supervisor | Slot Floor Person | Slot Shift Manager | Slot Shift Supervisor | Slot Supervisor | Table Games Supervisor</t>
+  </si>
+  <si>
+    <t>Corel WordPerfect Office Suite | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Speaking | Reading Comprehension | Critical Thinking | Writing | Active Learning</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Mathematics | English Language | Administration and Management | Computers and Electronics | Education and Training | Economics and Accounting | Public Safety and Security | Sales and Marketing | Personnel and Human Resources | Administrative | Psychology</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Speech Recognition | Speech Clarity | Near Vision | Deductive Reasoning | Written Expression | Written Comprehension | Selective Attention | Information Ordering | Far Vision | Inductive Reasoning | Memorization | Flexibility of Closure | Speed of Closure</t>
+  </si>
+  <si>
+    <t>Deal With External Customers or the Public in General | Contact With Others | Indoors, Environmentally Controlled | Work With or Contribute to a Work Group or Team | E-Mail | Importance of Being Exact or Accurate | Physical Proximity | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Face-to-Face Discussions with Individuals and Within Teams | Dealing With Unpleasant, Angry, or Discourteous People | Importance of Repeating Same Tasks | Impact of Decisions on Co-workers or Company Results | Work Outcomes and Results of Other Workers | Conflict Situations | Frequency of Decision Making | Spend Time Standing | Time Pressure | Spend Time Walking or Running | Coordinate or Lead Others in Accomplishing Work Activities | Telephone Conversations | Freedom to Make Decisions | Exposed to Contaminants | Determine Tasks, Priorities and Goals | Health and Safety of Other Workers | Level of Competition</t>
+  </si>
+  <si>
+    <t>Amusement and Recreation Attendants | Cashiers | Coin, Vending, and Amusement Machine Servicers and Repairers | First-Line Supervisors of Food Preparation and Serving Workers | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Mechanics, Installers, and Repairers | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Office and Administrative Support Workers | First-Line Supervisors of Production and Operating Workers | First-Line Supervisors of Retail Sales Workers | First-Line Supervisors of Security Workers | Gambling Cage Workers | Gambling Change Persons and Booth Cashiers | Gambling Dealers | Gambling Managers | Gambling Surveillance Officers and Gambling Investigators | Gambling and Sports Book Writers and Runners | Tellers</t>
+  </si>
+  <si>
+    <t>Directly supervise and coordinate activities of workers in assigned gambling areas. May circulate among tables, observe operations, and ensure that stations and games are covered for each shift. May verify and pay off jackpots. May reset slot machines after payoffs and make repairs or adjustments to slot machines or recommend removal of slot machines for repair. May plan and organize activities and services for guests in hotels/casinos.</t>
+  </si>
+  <si>
+    <t>Answer patrons' questions about gaming machine functions and payouts. | Attach "out of order" signs to malfunctioning machines, and notify technicians when machines need to be repaired or removed. | Clean and maintain slot machines and surrounding areas. | Determine how many gaming tables to open each day and schedule staff accordingly. | Direct workers compiling summary sheets for each race or event to record amounts wagered and amounts to be paid to winners. | Enforce safety rules, and report or remove safety hazards as well as guests who are underage, intoxicated, disruptive, or cheating. | Establish and maintain banks and table limits for each game. | Establish policies on types of gambling offered, odds, or extension of credit. | Evaluate workers' performance and prepare written performance evaluations. | Exchange currency for customers, converting currency into requested combinations of bills and coins. | Explain and interpret house rules, such as game rules or betting limits, for patrons. | Greet customers and ask about the quality of service they are receiving. | Interview and hire workers. | Maintain familiarity with the games at a facility and with strategies or tricks used by cheaters at such games. | Monitor functioning of slot machine coin dispensers and fill coin hoppers when necessary. | Monitor game operations to ensure that house rules are followed, that tribal, state, and federal regulations are adhered to, and that employees provide prompt and courteous service. | Monitor patrons for signs of compulsive gambling, offering assistance if necessary. | Monitor payment of hand-delivered jackpots to ensure promptness. | Monitor stations and games and move dealers from game to game to ensure adequate staffing. | Observe gamblers' behavior for signs of cheating, such as marking, switching, or counting cards, and notify security staff of suspected cheating. | Perform minor repairs or make adjustments to slot machines, resolving problems such as machine tilts and coin jams. | Perform paperwork required for monetary transactions. | Record the specifics of malfunctioning machines and document malfunctions needing repair. | Record, issue receipts for, and pay off bets. | Report customer-related incidents occurring in gaming areas to supervisors. | Reset slot machines after payoffs. | Respond to and resolve patrons' complaints. | Review operational expenses, budget estimates, betting accounts, or collection reports for accuracy. | Supervise the distribution of complimentary meals, hotel rooms, discounts, or other items given to players, based on length of play and amount bet. | Train, supervise, schedule, and evaluate workers.</t>
+  </si>
+  <si>
+    <t>39-1014.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services</t>
+  </si>
+  <si>
+    <t>Caddymaster | Community Life Director | Hair Salon Manager | Hotel Services Supervisor | Recreation Coordinator | Salon Manager</t>
+  </si>
+  <si>
+    <t>Inventory management systems | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Timekeeping software | Web browser software | Work scheduling software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Active Listening | Speaking | Writing | Monitoring | Active Learning | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Administration and Management | English Language | Personnel and Human Resources | Education and Training | Public Safety and Security | Sales and Marketing | Psychology | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Near Vision | Problem Sensitivity | Information Ordering | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Selective Attention | Category Flexibility | Time Sharing | Finger Dexterity | Manual Dexterity | Far Vision | Memorization | Fluency of Ideas | Written Expression | Originality</t>
+  </si>
+  <si>
+    <t>Contact With Others | Deal With External Customers or the Public in General | Face-to-Face Discussions with Individuals and Within Teams | Physical Proximity | Spend Time Standing | Spend Time Walking or Running | Work With or Contribute to a Work Group or Team | Telephone Conversations | Indoors, Environmentally Controlled | Importance of Repeating Same Tasks | Time Pressure | Dealing With Unpleasant, Angry, or Discourteous People | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Frequency of Decision Making | Freedom to Make Decisions | Coordinate or Lead Others in Accomplishing Work Activities | Work Outcomes and Results of Other Workers | Public Speaking | Conflict Situations | Level of Competition | E-Mail | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Construction Trades and Extraction Workers | First-Line Supervisors of Farming, Fishing, and Forestry Workers | First-Line Supervisors of Food Preparation and Serving Workers | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Landscaping, Lawn Service, and Groundskeeping Workers | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Mechanics, Installers, and Repairers | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Office and Administrative Support Workers | First-Line Supervisors of Passenger Attendants | First-Line Supervisors of Personal Service Workers | First-Line Supervisors of Production and Operating Workers | First-Line Supervisors of Retail Sales Workers | First-Line Supervisors of Security Workers | General and Operations Managers | Human Resources Specialists | Recreation Workers | Training and Development Managers | Training and Development Specialists</t>
+  </si>
+  <si>
+    <t>Directly supervise and coordinate activities of entertainment and recreation related workers.</t>
+  </si>
+  <si>
+    <t>Analyze and record personnel or operational data and write related activity reports. | Apply customer feedback to service improvement efforts. | Assign work schedules, following work requirements, to ensure quality and timely delivery of service. | Collaborate with staff members to plan or develop programs of events or schedules of activities. | Direct or coordinate the activities of entertainment and recreation related workers. | Furnish customers with information on events or activities. | Inform workers about interests or special needs of specific groups. | Inspect work areas or operating equipment to ensure conformance to established standards in areas such as cleanliness or maintenance. | Meet with managers or other supervisors to stay informed of changes affecting workers or operations. | Observe and evaluate workers' appearance and performance to ensure quality service and compliance with specifications. | Participate in continuing education to stay abreast of industry trends and developments. | Plan, direct, or supervise recreational and entertainment activities led by staff, such as sports, aquatics, games, or performing arts. | Provide staff with assistance in performing difficult or complicated duties. | Recruit and hire staff members. | Requisition supplies and equipment necessary for workers to facilitate recreational or entertainment activities, such as safety harnesses, flash lights, or first aid kits. | Resolve customer complaints regarding worker performance or services rendered. | Serve as a point of contact between managerial staff and leaders of recreational or entertainment activities. | Take disciplinary action to address performance problems. | Train workers in proper operational procedures and functions and explain company policies.</t>
+  </si>
+  <si>
+    <t>39-1022.00</t>
+  </si>
+  <si>
+    <t>First-Line Supervisors of Personal Service Workers</t>
+  </si>
+  <si>
+    <t>Adult Family Home Program Manager | Aquatics Supervisor | Bar and Restaurant Manager | Clinical Care Coordinator | Clinical Coordinator | Clinical Services Program Manager | Direct Care Supervisor | Housekeeping Supervisor | Resident Care Supervisor</t>
+  </si>
+  <si>
+    <t>Critical Thinking | Active Listening | Speaking | Reading Comprehension | Monitoring | Writing | Active Learning | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Administration and Management | Public Safety and Security | Psychology | Personnel and Human Resources | Education and Training | Administrative | Computers and Electronics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Written Comprehension | Speech Recognition | Speech Clarity | Deductive Reasoning | Written Expression | Near Vision | Information Ordering | Inductive Reasoning | Selective Attention | Category Flexibility | Originality | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>Contact With Others | Work Outcomes and Results of Other Workers | Telephone Conversations | Work With or Contribute to a Work Group or Team | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Indoors, Environmentally Controlled | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results | Freedom to Make Decisions | Face-to-Face Discussions with Individuals and Within Teams | Health and Safety of Other Workers | Frequency of Decision Making | E-Mail | Time Pressure | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Deal With External Customers or the Public in General | Physical Proximity | Dealing With Unpleasant, Angry, or Discourteous People | Consequence of Error | Conflict Situations | Written Letters and Memos | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Education and Childcare Administrators, Preschool and Daycare | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Farming, Fishing, and Forestry Workers | First-Line Supervisors of Food Preparation and Serving Workers | First-Line Supervisors of Helpers, Laborers, and Material Movers, Hand | First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Landscaping, Lawn Service, and Groundskeeping Workers | First-Line Supervisors of Material-Moving Machine and Vehicle Operators | First-Line Supervisors of Mechanics, Installers, and Repairers | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Office and Administrative Support Workers | First-Line Supervisors of Passenger Attendants | First-Line Supervisors of Production and Operating Workers | First-Line Supervisors of Retail Sales Workers | First-Line Supervisors of Security Workers | Human Resources Specialists | Medical and Health Services Managers | Patient Representatives | Residential Advisors | Social and Community Service Managers</t>
+  </si>
+  <si>
+    <t>Supervise and coordinate activities of personal service workers.</t>
+  </si>
+  <si>
+    <t>Apply customer feedback to service improvement efforts. | Arrange worker breaks to ensure services are adequately staffed throughout each shift. | Assign work schedules, following work requirements, to ensure quality and timely delivery of service. | Direct marketing, advertising, or other customer recruitment efforts. | Direct or coordinate the activities of workers, such as hotel staff or hair stylists. | Inform management about problems, such as employee disputes. | Inform workers about interests or special needs of specific groups. | Inspect work areas or operating equipment to ensure conformance to established standards in areas such as cleanliness or maintenance. | Investigate employee complaints and resolve problems following management rules and regulations. | Meet with managers or other supervisors to stay informed of changes affecting operations. | Observe and evaluate workers' appearance and performance to ensure quality service and compliance with specifications. | Participate in continuing education to stay abreast of industry trends and developments. | Recruit and hire staff members. | Requisition necessary supplies, equipment, or services. | Resolve customer complaints regarding worker performance or services rendered. | Take disciplinary action to address performance problems. | Train workers in proper operational procedures and functions and explain company policies.</t>
+  </si>
+  <si>
+    <t>39-2011.00</t>
+  </si>
+  <si>
+    <t>Animal Trainers</t>
+  </si>
+  <si>
+    <t>Agility Instructor | Dog Obedience Instructor | Dog Trainer | Guide Dog Instructor | Guide Dog Mobility Instructor (GDMI) | Guide Dog Trainer | Horse Trainer | Racehorse Trainer | Service Dog Trainer | Trainer</t>
+  </si>
+  <si>
+    <t>Atlassian JIRA | Customer information control system CICS | Database software | Epic Systems | Facebook | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Windows | Microsoft Word | Oracle Database | Oracle PeopleSoft | SAP software | Tracks Software | Work scheduling software</t>
+  </si>
+  <si>
+    <t>Learning Strategies | Speaking | Critical Thinking | Active Learning | Active Listening | Monitoring</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Education and Training | Psychology | Administration and Management | English Language</t>
+  </si>
+  <si>
+    <t>Problem Sensitivity | Oral Expression | Oral Comprehension | Information Ordering | Speech Clarity | Speech Recognition | Deductive Reasoning | Originality | Fluency of Ideas | Stamina | Trunk Strength | Multilimb Coordination | Manual Dexterity | Selective Attention | Category Flexibility | Inductive Reasoning | Written Expression | Written Comprehension | Far Vision | Near Vision | Gross Body Coordination</t>
+  </si>
+  <si>
+    <t>Freedom to Make Decisions | Face-to-Face Discussions with Individuals and Within Teams | Determine Tasks, Priorities and Goals | Spend Time Standing | Contact With Others | Outdoors, Exposed to All Weather Conditions | Telephone Conversations | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | E-Mail | Coordinate or Lead Others in Accomplishing Work Activities | Frequency of Decision Making | Spend Time Walking or Running | Work With or Contribute to a Work Group or Team | Health and Safety of Other Workers | Outdoors, Under Cover</t>
+  </si>
+  <si>
+    <t>Amusement and Recreation Attendants | Animal Breeders | Animal Caretakers | Animal Control Workers | Animal Scientists | Athletes and Sports Competitors | Athletic Trainers | Coaches and Scouts | Exercise Physiologists | Exercise Trainers and Group Fitness Instructors | Farmworkers, Farm, Ranch, and Aquacultural Animals | Lifeguards, Ski Patrol, and Other Recreational Protective Service Workers | Self-Enrichment Teachers | Training and Development Managers | Training and Development Specialists | Umpires, Referees, and Other Sports Officials | Veterinarians | Veterinary Assistants and Laboratory Animal Caretakers | Veterinary Technologists and Technicians | Zoologists and Wildlife Biologists</t>
+  </si>
+  <si>
+    <t>Train animals for riding, harness, security, performance, or obedience, or for assisting persons with disabilities. Accustom animals to human voice and contact, and condition animals to respond to commands. Train animals according to prescribed standards for show or competition. May train animals to carry pack loads or work as part of pack team.</t>
+  </si>
+  <si>
+    <t>Administer prescribed medications to animals. | Advise animal owners regarding the purchase of specific animals. | Conduct training programs to develop or maintain desired animal behaviors for competition, entertainment, obedience, security, riding, or related purposes. | Cue or signal animals during performances. | Evaluate animals for trainability and ability to perform. | Evaluate animals to determine their temperaments, abilities, or aptitude for training. | Feed or exercise animals or provide other general care, such as cleaning or maintaining holding or performance areas. | Keep records documenting animal health, diet, or behavior. | Observe animals' physical conditions to detect illness or unhealthy conditions requiring medical care. | Organize or conduct animal shows. | Retrain horses to break bad habits, such as kicking, bolting, or resisting bridling or grooming. | Talk to or interact with animals to familiarize them to human voices or contact. | Train dogs in human assistance or property protection duties. | Train horses or other equines for riding, harness, show, racing, or other work, using knowledge of breed characteristics, training methods, performance standards, and the peculiarities of each animal. | Use oral, spur, rein, or hand commands to condition horses to carry riders or to pull horse-drawn equipment.</t>
+  </si>
+  <si>
+    <t>39-2021.00</t>
+  </si>
+  <si>
+    <t>Animal Caretakers</t>
+  </si>
+  <si>
+    <t>Animal Care Giver (ACG) | Aquarist | Dog Bather | Dog Groomer | Groomer | Kennel Attendant | Kennel Technician (Kennel Tech) | Pet Groomer | Pet Stylist | Zookeeper</t>
+  </si>
+  <si>
+    <t>CEEJS The Pet Groomer's Secretary | DaySmart Software 123Pet | DaySmart Software Appointment-Plus | Envision Pet Grooming | Groom Pro | Groomsoft | K9 Bytes K9 Koordinator | Kennel Link | Microsoft Access | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Mobile Dog Grooming Software mGroomer | Petschedule | The Groomer's Write Hand</t>
+  </si>
+  <si>
+    <t>Monitoring | Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Administrative | English Language</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Problem Sensitivity | Oral Expression | Near Vision | Static Strength | Information Ordering | Speech Clarity | Speech Recognition | Trunk Strength | Inductive Reasoning | Deductive Reasoning</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Contact With Others | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Work With or Contribute to a Work Group or Team | Spend Time Standing | Frequency of Decision Making | Outdoors, Exposed to All Weather Conditions | Telephone Conversations | Exposed to Contaminants | Exposed to Minor Burns, Cuts, Bites, or Stings | Impact of Decisions on Co-workers or Company Results | Determine Tasks, Priorities and Goals | Physical Proximity | Freedom to Make Decisions | Deal With External Customers or the Public in General | Exposed to Disease or Infections | Importance of Being Exact or Accurate | Spend Time Walking or Running</t>
+  </si>
+  <si>
+    <t>Animal Breeders | Animal Control Workers | Animal Scientists | Animal Trainers | Child, Family, and School Social Workers | Childcare Workers | Farmers, Ranchers, and Other Agricultural Managers | Farmworkers, Farm, Ranch, and Aquacultural Animals | First-Line Supervisors of Farming, Fishing, and Forestry Workers | First-Line Supervisors of Personal Service Workers | Home Health Aides | Licensed Practical and Licensed Vocational Nurses | Locker Room, Coatroom, and Dressing Room Attendants | Nursing Assistants | Personal Care Aides | Phlebotomists | Veterinarians | Veterinary Assistants and Laboratory Animal Caretakers | Veterinary Technologists and Technicians | Zoologists and Wildlife Biologists</t>
+  </si>
+  <si>
+    <t>Feed, water, groom, bathe, exercise, or otherwise provide care to promote and maintain the well-being of pets and other animals that are not raised for consumption, such as dogs, cats, race horses, ornamental fish or birds, zoo animals, and mice. Work in settings such as kennels, animal shelters, zoos, circuses, and aquariums. May keep records of feedings, treatments, and animals received or discharged. May clean, disinfect, and repair cages, pens, or fish tanks.</t>
+  </si>
+  <si>
+    <t>Adjust controls to regulate specified temperature and humidity of animal quarters, nurseries, or exhibit areas. | Advise pet owners on how to care for their pets' health. | Anesthetize and inoculate animals, according to instructions. | Answer telephones and schedule appointments. | Clean and disinfect surgical equipment. | Collect and record animal information, such as weight, size, physical condition, treatments received, medications given, and food intake. | Discuss with clients their pets' grooming needs. | Do facility laundry and clean, organize, maintain, and disinfect animal quarters, such as pens and stables, and equipment, such as saddles and bridles. | Examine and observe animals to detect signs of illness, disease, or injury. | Exercise animals to maintain their physical and mental health. | Feed and water animals according to schedules and feeding instructions. | Find homes for stray or unwanted animals. | Install, maintain, and repair animal care facility equipment, such as infrared lights, feeding devices, and cages. | Mix food, liquid formulas, medications, or food supplements according to instructions, prescriptions, and knowledge of animal species. | Observe and caution children petting and feeding animals in designated areas to ensure the safety of humans and animals. | Order, unload, and store feed and supplies. | Perform animal grooming duties, such as washing, brushing, clipping, and trimming coats, cutting nails, and cleaning ears. | Provide treatment to sick or injured animals, or contact veterinarians to secure treatment. | Respond to questions from patrons, and provide information about animals, such as behavior, habitat, breeding habits, or facility activities. | Sell pet food and supplies. | Train animals to perform certain tasks. | Transfer animals between enclosures to facilitate breeding, birthing, shipping, or rearrangement of exhibits.</t>
+  </si>
+  <si>
+    <t>39-3011.00</t>
+  </si>
+  <si>
+    <t>Gambling Dealers</t>
+  </si>
+  <si>
+    <t>Black Jack Dealer | Blackjack Dealer | Card Dealer | Casino Dealer | Dealer | Dual Rate Dealer | Games Dealer | Poker Dealer | Table Games Dealer | Twenty-One Dealer</t>
+  </si>
+  <si>
+    <t>Apache Hadoop | Apache Spark | Email software | Microsoft Excel | Microsoft Office software | Slack</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Monitoring | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Mathematics | English Language</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Near Vision | Problem Sensitivity | Finger Dexterity | Information Ordering | Deductive Reasoning | Manual Dexterity | Selective Attention</t>
+  </si>
+  <si>
+    <t>Importance of Being Exact or Accurate | Indoors, Environmentally Controlled | Contact With Others | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Face-to-Face Discussions with Individuals and Within Teams | Physical Proximity | Deal With External Customers or the Public in General | Work With or Contribute to a Work Group or Team | Dealing With Unpleasant, Angry, or Discourteous People | Frequency of Decision Making | Spend Time Making Repetitive Motions | Importance of Repeating Same Tasks | Impact of Decisions on Co-workers or Company Results | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Level of Competition</t>
+  </si>
+  <si>
+    <t>Amusement and Recreation Attendants | Athletes and Sports Competitors | Brokerage Clerks | Cashiers | Coin, Vending, and Amusement Machine Servicers and Repairers | Counter and Rental Clerks | Customer Service Representatives | Door-to-Door Sales Workers, News and Street Vendors, and Related Workers | First-Line Supervisors of Gambling Services Workers | Gambling Cage Workers | Gambling Change Persons and Booth Cashiers | Gambling Managers | Gambling Surveillance Officers and Gambling Investigators | Gambling and Sports Book Writers and Runners | New Accounts Clerks | Retail Salespersons | Securities, Commodities, and Financial Services Sales Agents | Tellers | Umpires, Referees, and Other Sports Officials | Wholesale and Retail Buyers, Except Farm Products</t>
+  </si>
+  <si>
+    <t>Operate table games. Stand or sit behind table and operate games of chance by dispensing the appropriate number of cards or blocks to players, or operating other gambling equipment. Distribute winnings or collect players' money or chips. May compare the house's hand against players' hands.</t>
+  </si>
+  <si>
+    <t>Answer questions about game rules and casino policies. | Apply rule variations to card games such as poker, in which players bet on the value of their hands. | Check to ensure that all players have placed bets before play begins. | Compute amounts of players' wins or losses, or scan winning tickets presented by patrons to calculate the amount of money won. | Conduct gambling games, such as dice, roulette, cards, or keno, following all applicable rules and regulations. | Deal cards to house hands, and compare these with players' hands to determine winners, as in black jack. | Exchange paper currency for playing chips or coin money. | Greet customers and make them feel welcome. | Inspect cards and equipment to be used in games to ensure that they are in good condition. | Open and close cash floats and game tables. | Participate in games for gambling establishments to provide the minimum complement of players at a table. | Pay winnings or collect losing bets as established by the rules and procedures of a specific game. | Prepare collection reports for submission to supervisors. | Receive, verify, and record patrons' cash wagers. | Refer patrons to gaming cashiers to collect winnings. | Seat patrons at gaming tables. | Stand behind a gaming table and deal the appropriate number of cards to each player. | Start and control games and gaming equipment, and announce winning numbers or colors. | Supervise staff and monitor gambling tables to ensure security of the game. | Train new dealers. | Work as part of a team of dealers in games, such as baccarat or craps.</t>
+  </si>
+  <si>
+    <t>39-3012.00</t>
+  </si>
+  <si>
+    <t>Gambling and Sports Book Writers and Runners</t>
+  </si>
+  <si>
+    <t>Bingo Clerk | Casino Attendant | Casino Floor Runner | Casino Runner | Floor Runner | Keno Attendant | Keno Writer | Race and Sports Book Writer | Racebook Writer</t>
+  </si>
+  <si>
+    <t>Credit card processing software | Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Web browser software</t>
+  </si>
+  <si>
+    <t>Active Listening | Speaking | Monitoring | Mathematics</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Mathematics</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Near Vision | Problem Sensitivity | Speech Clarity | Speech Recognition | Information Ordering | Far Vision | Deductive Reasoning | Mathematical Reasoning | Inductive Reasoning | Written Expression | Written Comprehension | Number Facility</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Contact With Others | Work With or Contribute to a Work Group or Team | Physical Proximity | Importance of Being Exact or Accurate | Importance of Repeating Same Tasks | Face-to-Face Discussions with Individuals and Within Teams | Deal With External Customers or the Public in General | Spend Time Making Repetitive Motions | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Amusement and Recreation Attendants | Athletes and Sports Competitors | Bookkeeping, Accounting, and Auditing Clerks | Cashiers | Counter and Rental Clerks | Credit Authorizers, Checkers, and Clerks | Door-to-Door Sales Workers, News and Street Vendors, and Related Workers | First-Line Supervisors of Gambling Services Workers | Gambling Cage Workers | Gambling Change Persons and Booth Cashiers | Gambling Dealers | Gambling Managers | Hosts and Hostesses, Restaurant, Lounge, and Coffee Shop | Hotel, Motel, and Resort Desk Clerks | New Accounts Clerks | Retail Salespersons | Securities, Commodities, and Financial Services Sales Agents | Stockers and Order Fillers | Tellers | Umpires, Referees, and Other Sports Officials</t>
+  </si>
+  <si>
+    <t>Post information enabling patrons to wager on various races and sporting events. Assist in the operation of games such as keno and bingo. May operate random number-generating equipment and announce the numbers for patrons. Receive, verify, and record patrons' wagers. Scan and process winning tickets presented by patrons and pay out winnings for those wagers.</t>
+  </si>
+  <si>
+    <t>Answer questions about game rules or casino policies. | Check to ensure that all players have placed their bets before play begins. | Collect bets in the form of cash or chips, verifying and recording amounts. | Collect cards or tickets from players. | Compare the house hand with players' hands to determine the winner. | Compute and verify amounts won or lost, paying out winnings or referring patrons to workers, such as gaming cashiers, so that winnings can be collected. | Conduct gambling tables or games, such as dice, roulette, cards, or keno, and ensure that game rules are followed. | Deliver tickets, cards, and money to bingo callers. | Exchange paper currency for playing chips or coins. | Inspect cards or equipment to be used in games to ensure they are in proper condition. | Open or close cash floats or game tables. | Operate games in which players bet that a ball will come to rest in a particular slot on a rotating wheel, performing actions such as spinning the wheel and releasing the ball. | Pay off or move bets as established by game rules and procedures. | Prepare collection reports for submission to supervisors. | Record the number of tickets cashed and the amount paid out after each race or event. | Sell food, beverages, or tobacco to players. | Start gaming equipment that randomly selects numbered balls and announce winning numbers and colors. | Supervise staff and games and mediate disputes.</t>
+  </si>
+  <si>
+    <t>39-3019.00</t>
+  </si>
+  <si>
+    <t>Gambling Service Workers, All Other</t>
+  </si>
+  <si>
+    <t>Bingo Attendant | Card Room Attendant | Casino Attendant | Gaming Attendant | Keno Runner | Race Book Attendant | Slot Attendant | Gaming Service Worker | Casino Floor Attendant | Pari-Mutuel Clerk</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Mathematics | Law and Government | Public Safety and Security | Computers and Electronics | Sales and Marketing</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Speech Clarity | Speech Recognition | Near Vision | Problem Sensitivity | Information Ordering | Deductive Reasoning | Inductive Reasoning | Written Comprehension | Selective Attention | Category Flexibility | Time Sharing | Finger Dexterity | Manual Dexterity | Far Vision | Memorization | Fluency of Ideas</t>
+  </si>
+  <si>
+    <t>Contact With Others | Deal With External Customers or the Public in General | Face-to-Face Discussions with Individuals and Within Teams | Physical Proximity | Spend Time Standing | Spend Time Walking or Running | Work With or Contribute to a Work Group or Team | Telephone Conversations | Indoors, Environmentally Controlled | Importance of Repeating Same Tasks | Time Pressure | Dealing With Unpleasant, Angry, or Discourteous People | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Frequency of Decision Making | Freedom to Make Decisions | Level of Competition | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Being Exact or Accurate | Consequence of Error</t>
+  </si>
+  <si>
+    <t>Gambling Dealers | Gambling and Sports Book Writers and Runners | Gambling Cage Workers | Gambling Change Persons and Booth Cashiers | First-Line Supervisors of Gambling Services Workers | Gambling Surveillance Officers and Gambling Investigators | Gambling Managers | Amusement and Recreation Attendants | Ushers, Lobby Attendants, and Ticket Takers | Cashiers | Counter and Rental Clerks | Customer Service Representatives | Hosts and Hostesses, Restaurant, Lounge, and Coffee Shop | Bartenders | Waiters and Waitresses | Security Guards | Concierges | Entertainment Attendants and Related Workers, All Other | Entertainment and Recreation Managers, Except Gambling | Recreation Workers</t>
+  </si>
+  <si>
+    <t>All gambling service workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Perform gambling service duties in roles not classified separately. | Attend gaming areas and assist patrons with games, machines, and wagering. | Sell and redeem tickets, chips, tokens, and vouchers. | Verify winning tickets and process payouts according to established limits. | Explain game rules, odds, and house policies to patrons. | Monitor gaming activity for irregularities and report suspicious behavior. | Balance receipts, count cash and tokens, and reconcile drawers. | Maintain accurate records of transactions, payouts, and machine activity. | Perform minor troubleshooting on gaming machines and summon technicians. | Enforce age restrictions, wagering limits, and gaming regulations. | Respond to patron complaints and refer disputes to supervisors. | Keep gaming areas clean, stocked, and orderly. | Promote games, events, and player loyalty programs. | Comply with licensing requirements and mandatory reporting rules.</t>
+  </si>
+  <si>
+    <t>39-3021.00</t>
+  </si>
+  <si>
+    <t>Motion Picture Projectionists</t>
+  </si>
+  <si>
+    <t>Booth Operator | Cinema Projectionist | Digital Projectionist | Film Specialist | Motion Picture Projectionist | Movie Projectionist | Projection Technician | Projectionist | Projector Booth Operator | Technical Projection Guide</t>
+  </si>
+  <si>
+    <t>Apple macOS | Audio calibration software | Autodesk AutoCAD | Avid Technology iNEWS | Facebook | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Web browser software</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Computers and Electronics | Customer and Personal Service | Mechanical | English Language</t>
+  </si>
+  <si>
+    <t>Far Vision | Near Vision | Control Precision | Problem Sensitivity | Oral Expression | Oral Comprehension | Perceptual Speed | Information Ordering | Written Comprehension | Visual Color Discrimination | Reaction Time | Finger Dexterity | Manual Dexterity | Arm-Hand Steadiness | Selective Attention | Speech Clarity | Speech Recognition</t>
+  </si>
+  <si>
+    <t>Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Freedom to Make Decisions | Telephone Conversations | Frequency of Decision Making | Time Pressure | Determine Tasks, Priorities and Goals | E-Mail | Contact With Others</t>
+  </si>
+  <si>
+    <t>Audio and Video Technicians | Audiovisual Equipment Installers and Repairers | Broadcast Technicians | Camera Operators, Television, Video, and Film | Camera and Photographic Equipment Repairers | Coin, Vending, and Amusement Machine Servicers and Repairers | Computer, Automated Teller, and Office Machine Repairers | Electronic Equipment Installers and Repairers, Motor Vehicles | Extruding and Forming Machine Setters, Operators, and Tenders, Synthetic and Glass Fibers | Lighting Technicians | Media Technical Directors/Managers | Milling and Planing Machine Setters, Operators, and Tenders, Metal and Plastic | Office Machine Operators, Except Computer | Ophthalmic Laboratory Technicians | Photographic Process Workers and Processing Machine Operators | Photonics Technicians | Prepress Technicians and Workers | Radio, Cellular, and Tower Equipment Installers and Repairers | Sound Engineering Technicians | Telecommunications Equipment Installers and Repairers, Except Line Installers</t>
+  </si>
+  <si>
+    <t>Set up and operate motion picture projection and related sound reproduction equipment.</t>
+  </si>
+  <si>
+    <t>Clean the projection booth. | Coordinate equipment operation with presentation of supplemental material, such as music, oral commentaries, or sound effects. | Inspect movie films to ensure that they are complete and in good condition. | Inspect projection equipment prior to operation to ensure proper working order. | Install and connect auxiliary equipment, such as microphones, amplifiers, disc playback machines, and lights. | Monitor operations to ensure that standards for sound and image projection quality are met. | Observe projector operation to anticipate need to transfer operations from one projector to another. | Open and close facilities according to rules and schedules. | Operate equipment to show films in a number of theaters simultaneously. | Perform minor repairs, such as replacing worn sprockets, or notify maintenance personnel of the need for major repairs. | Perform regular maintenance tasks, such as rotating or replacing xenon bulbs, cleaning projectors and lenses, lubricating machinery, and keeping electrical contacts clean and tight. | Prepare film inspection reports, attendance sheets, and log books. | Remove full take-up reels and run film through rewinding machines to rewind projected films so they may be shown again. | Set up and adjust picture projectors and screens to achieve proper size, illumination, and focus of images, and proper volume and tone of sound. | Set up and inspect curtain and screen controls. | Splice separate film reels, advertisements, and movie trailers together to form a feature-length presentation on one continuous reel. | Start projectors and open shutters to project images onto screens.</t>
+  </si>
+  <si>
+    <t>39-3031.00</t>
+  </si>
+  <si>
+    <t>Ushers, Lobby Attendants, and Ticket Takers</t>
+  </si>
+  <si>
+    <t>Docent | Lobby Attendant | Ticket Attendant | Ticket Taker | Usher | Visitor Services Assistant | Visitor Services Associate | Visitor Services Representative | Visitor Services Specialist</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows Mobile | Microsoft Word | Ticket Alternative Express Entry | Ticket scanning software</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Public Safety and Security | Communications and Media</t>
+  </si>
+  <si>
+    <t>Speech Clarity | Oral Comprehension | Oral Expression | Near Vision | Speech Recognition | Problem Sensitivity</t>
+  </si>
+  <si>
+    <t>Contact With Others | Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Deal With External Customers or the Public in General | Physical Proximity | Spend Time Standing | Work With or Contribute to a Work Group or Team | Dealing With Unpleasant, Angry, or Discourteous People | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Being Exact or Accurate | Telephone Conversations | Freedom to Make Decisions</t>
+  </si>
+  <si>
+    <t>Amusement and Recreation Attendants | Baggage Porters and Bellhops | Cashiers | Concierges | Counter and Rental Clerks | Customer Service Representatives | Dining Room and Cafeteria Attendants and Bartender Helpers | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | Flight Attendants | Hosts and Hostesses, Restaurant, Lounge, and Coffee Shop | Hotel, Motel, and Resort Desk Clerks | Locker Room, Coatroom, and Dressing Room Attendants | Lodging Managers | Meeting, Convention, and Event Planners | Parking Attendants | Passenger Attendants | Receptionists and Information Clerks | Reservation and Transportation Ticket Agents and Travel Clerks | Tour Guides and Escorts | Travel Guides</t>
+  </si>
+  <si>
+    <t>Assist patrons at entertainment events by performing duties, such as collecting admission tickets and passes from patrons, assisting in finding seats, searching for lost articles, and helping patrons locate such facilities as restrooms and telephones.</t>
+  </si>
+  <si>
+    <t>Assist patrons by giving directions to points in or outside of the facility or providing information about local attractions. | Assist patrons in finding seats, lighting the way with flashlights, if necessary. | Clean facilities. | Count and record number of tickets collected. | Distribute programs to patrons. | Examine tickets or passes to verify authenticity, using criteria such as color or date issued. | Give door checks to patrons who are temporarily leaving establishments. | Greet patrons attending entertainment events. | Guide patrons to exits or provide other instructions or assistance in case of emergency. | Lead tours and answer visitors' questions about the exhibits. | Maintain order and ensure adherence to safety rules. | Manage informational kiosks or displays of event signs or posters. | Manage inventory or sale of artist merchandise. | Operate refreshment stands during intermission or obtain refreshments for press box patrons during performances. | Page individuals wanted at the box office. | Provide assistance with patrons' special needs, such as helping those with wheelchairs. | Refuse admittance to undesirable persons or persons without tickets or passes. | Schedule or manage staff, such as volunteer usher corps. | Search for lost articles or for parents of lost children. | Sell or collect admission tickets, passes, or facility memberships from patrons at entertainment events. | Settle seating disputes or help solve other customer concerns. | Verify credentials of patrons desiring entrance into press box and permit only authorized persons to enter. | Work with others to change advertising displays.</t>
+  </si>
+  <si>
+    <t>39-3091.00</t>
+  </si>
+  <si>
+    <t>Amusement and Recreation Attendants</t>
+  </si>
+  <si>
+    <t>Activities Attendant | Coaster Attendant | Golf Course Ranger | Golf Course Starter | Recreation Aide | Recreation Attendant | Recreation Clerk | Ride Operator | Ski Lift Operator | Sports Complex Attendant</t>
+  </si>
+  <si>
+    <t>Adobe PageMaker | Database software | Facebook | Microsoft Excel | Microsoft Internet Explorer | Microsoft Office software | Microsoft Outlook | Microsoft Windows | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Speech Clarity | Oral Expression | Oral Comprehension | Problem Sensitivity | Speech Recognition | Near Vision</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Deal With External Customers or the Public in General | Work With or Contribute to a Work Group or Team | Spend Time Standing | Physical Proximity | Outdoors, Exposed to All Weather Conditions | Coordinate or Lead Others in Accomplishing Work Activities | Spend Time Walking or Running</t>
+  </si>
+  <si>
+    <t>Athletes and Sports Competitors | Baggage Porters and Bellhops | Cashiers | Coin, Vending, and Amusement Machine Servicers and Repairers | Concierges | Counter and Rental Clerks | Dining Room and Cafeteria Attendants and Bartender Helpers | Dispatchers, Except Police, Fire, and Ambulance | Door-to-Door Sales Workers, News and Street Vendors, and Related Workers | Entertainment and Recreation Managers, Except Gambling | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | First-Line Supervisors of Gambling Services Workers | Hotel, Motel, and Resort Desk Clerks | Laborers and Freight, Stock, and Material Movers, Hand | Lifeguards, Ski Patrol, and Other Recreational Protective Service Workers | Locker Room, Coatroom, and Dressing Room Attendants | Parking Attendants | Passenger Attendants | Umpires, Referees, and Other Sports Officials | Ushers, Lobby Attendants, and Ticket Takers</t>
+  </si>
+  <si>
+    <t>Perform a variety of attending duties at amusement or recreation facility. May schedule use of recreation facilities, maintain and provide equipment to participants of sporting events or recreational pursuits, or operate amusement concessions and rides.</t>
+  </si>
+  <si>
+    <t>Announce or describe amusement park attractions to patrons to entice customers to games and other entertainment. | Clean sporting equipment, vehicles, rides, booths, facilities, or grounds. | Direct patrons to rides, seats, or attractions. | Fasten safety devices for patrons, or provide them with directions for fastening devices. | Inspect equipment to detect wear and damage and perform minor repairs, adjustments, or maintenance tasks, such as oiling parts. | Keep informed of shut-down and emergency evacuation procedures. | Maintain inventories of equipment, storing and retrieving items and assembling and disassembling equipment as necessary. | Monitor activities to ensure adherence to rules and safety procedures, or arrange for the removal of unruly patrons. | Operate, drive, or explain the use of mechanical riding devices or other automatic equipment in amusement parks, carnivals, or recreation areas. | Provide assistance to patrons entering or exiting amusement rides, boats, or ski lifts, or mounting or dismounting animals. | Provide information about facilities, entertainment options, and rules and regulations. | Record details of attendance, sales, receipts, reservations, or repair activities. | Rent, sell, or issue sporting equipment and supplies, such as bowling shoes, golf balls, swimming suits, or beach chairs. | Schedule the use of recreation facilities, such as golf courses, tennis courts, bowling alleys, or softball diamonds. | Sell and serve refreshments to customers. | Sell tickets and collect fees from customers. | Verify, collect, or punch tickets before admitting patrons to venues, such as amusement parks and rides.</t>
+  </si>
+  <si>
+    <t>39-3092.00</t>
+  </si>
+  <si>
+    <t>Costume Attendants</t>
+  </si>
+  <si>
+    <t>Costume Draper | Costume Seamstress | Costumer | Draper | Dresser | Wardrobe Assistant | Wardrobe Attendant | Wardrobe Supervisor</t>
+  </si>
+  <si>
+    <t>Database software | Garment tracking software | Microsoft Excel | Microsoft Office software | Microsoft Outlook | Microsoft Word | Web browser software</t>
+  </si>
+  <si>
+    <t>Fine Arts | Design | Production and Processing | Customer and Personal Service | English Language | Psychology</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Oral Expression | Problem Sensitivity | Near Vision | Speech Clarity | Category Flexibility | Information Ordering | Fluency of Ideas | Arm-Hand Steadiness | Selective Attention | Inductive Reasoning | Deductive Reasoning | Originality | Written Comprehension | Speech Recognition | Finger Dexterity</t>
+  </si>
+  <si>
+    <t>Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Work With or Contribute to a Work Group or Team | Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Contact With Others | Time Pressure | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Physical Proximity | E-Mail | Coordinate or Lead Others in Accomplishing Work Activities | Work Outcomes and Results of Other Workers | Spend Time Making Repetitive Motions | Frequency of Decision Making</t>
+  </si>
+  <si>
+    <t>Choreographers | Commercial and Industrial Designers | Craft Artists | Fabric and Apparel Patternmakers | Fashion Designers | Furniture Finishers | Hairdressers, Hairstylists, and Cosmetologists | Interior Designers | Jewelers and Precious Stone and Metal Workers | Laundry and Dry-Cleaning Workers | Makeup Artists, Theatrical and Performance | Merchandise Displayers and Window Trimmers | Painting, Coating, and Decorating Workers | Retail Salespersons | Set and Exhibit Designers | Sewers, Hand | Sewing Machine Operators | Shoe and Leather Workers and Repairers | Tailors, Dressmakers, and Custom Sewers | Upholsterers</t>
+  </si>
+  <si>
+    <t>Select, fit, and take care of costumes for cast members, and aid entertainers. May assist with multiple costume changes during performances.</t>
+  </si>
+  <si>
+    <t>Arrange costumes in order of use to facilitate quick-change procedures for performances. | Assign lockers to employees and maintain locker rooms, dressing rooms, wig rooms, or costume storage or laundry areas. | Care for non-clothing items, such as flags, table skirts, or draperies. | Check the appearance of costumes on stage or under lights to determine whether desired effects are being achieved. | Clean and press costumes before and after performances and perform any minor repairs. | Collaborate with production designers, costume designers, or other production staff to discuss and execute costume design details. | Create worksheets for dressing lists, show notes, or costume checks. | Design or construct costumes or send them to tailors for construction, major repairs, or alterations. | Direct the work of wardrobe crews during dress rehearsals or performances. | Distribute costumes or related equipment and keep records of item status. | Examine costume fit on cast members and sketch or write notes for alterations. | Inventory stock to determine types or conditions of available costuming. | Monitor, maintain, or secure inventories of costumes, wigs, or makeup, providing keys or access to assigned directors, costume designers, or wardrobe mistresses/masters. | Participate in the hiring, training, scheduling, or supervision of alteration workers. | Provide dressing assistance to cast members or assign cast dressers to assist specific cast members with costume changes. | Provide managers with budget recommendations and take responsibility for budgetary line items related to costumes, storage, or makeup needs. | Purchase, rent, or requisition costumes or other wardrobe necessities. | Recommend vendors and monitor their work. | Return borrowed or rented items when productions are complete and return other items to storage. | Review scripts or other production information to determine a story's locale or period, as well as the number of characters and required costumes. | Study books, pictures, or examples of period clothing to determine styles worn during specific periods in history.</t>
+  </si>
+  <si>
+    <t>39-3093.00</t>
+  </si>
+  <si>
+    <t>Locker Room, Coatroom, and Dressing Room Attendants</t>
+  </si>
+  <si>
+    <t>Athletic Equipment Manager | Coat Check Attendant | Coat Checker | Coat Room Attendant | Fitting Room Attendant | Ladies Locker Room Attendant | Locker Room Attendant | Spa Attendant</t>
+  </si>
+  <si>
+    <t>Facebook | IBM Lotus 1-2-3 | IntelliTrack DMS Check In-Out | Inventory tracking software | Microsoft Excel | Microsoft Office software | Microsoft Word | SportSoft Equipment Manager | Web browser software</t>
+  </si>
+  <si>
+    <t>Speech Recognition | Speech Clarity | Oral Comprehension | Oral Expression</t>
+  </si>
+  <si>
+    <t>Contact With Others | Indoors, Environmentally Controlled | Face-to-Face Discussions with Individuals and Within Teams | Deal With External Customers or the Public in General | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Physical Proximity | Telephone Conversations</t>
+  </si>
+  <si>
+    <t>Amusement and Recreation Attendants | Baggage Porters and Bellhops | Concierges | Counter and Rental Clerks | Dining Room and Cafeteria Attendants and Bartender Helpers | First-Line Supervisors of Housekeeping and Janitorial Workers | First-Line Supervisors of Personal Service Workers | Food Servers, Nonrestaurant | Food Service Managers | Hosts and Hostesses, Restaurant, Lounge, and Coffee Shop | Hotel, Motel, and Resort Desk Clerks | Janitors and Cleaners, Except Maids and Housekeeping Cleaners | Laundry and Dry-Cleaning Workers | Lodging Managers | Maids and Housekeeping Cleaners | Parking Attendants | Passenger Attendants | Retail Salespersons | Ushers, Lobby Attendants, and Ticket Takers | Waiters and Waitresses</t>
+  </si>
+  <si>
+    <t>Provide personal items to patrons or customers in locker rooms, dressing rooms, or coatrooms.</t>
+  </si>
+  <si>
+    <t>Activate emergency action plans and administer first aid, as necessary. | Answer customer inquiries or explain cost, availability, policies, and procedures of facilities. | Assign dressing room facilities, locker space, or clothing containers to patrons of athletic or bathing establishments. | Attend to needs of athletic teams in clubhouses. | Check supplies to ensure adequate availability, and order new supplies when necessary. | Clean and polish footwear, using brushes, sponges, cleaning fluid, polishes, waxes, liquid or sole dressing, and daubers. | Clean facilities such as floors or locker rooms. | Collect soiled linen or clothing for laundering. | Issue gym clothes, uniforms, towels, athletic equipment, and special athletic apparel. | Maintain a lost-and-found collection. | Maintain inventories of clothing or uniforms, accessories, equipment, or linens. | Monitor patrons' facility use to ensure that rules and regulations are followed, and safety and order are maintained. | Operate controls that regulate temperatures or room environments. | Operate washing machines and dryers to clean soiled apparel and towels. | Procure beverages, food, and other items as requested. | Provide assistance to patrons by performing duties such as opening doors or carrying bags. | Provide or arrange for services such as clothes pressing, cleaning, or repair. | Provide towels and sheets to clients in public baths, steam rooms, and restrooms. | Refer guest problems or complaints to supervisors. | Report and document safety hazards, potentially hazardous conditions, and unsafe practices and procedures. | Set up various apparatus or athletic equipment. | Stencil identifying information on equipment. | Store personal possessions for patrons, issue claim checks for articles stored, and return articles on receipt of checks.</t>
+  </si>
+  <si>
+    <t>39-3099.00</t>
+  </si>
+  <si>
+    <t>Entertainment Attendants and Related Workers, All Other</t>
+  </si>
+  <si>
+    <t>Arcade Attendant | Box Office Attendant | Event Attendant | Entertainment Attendant | Guest Services Attendant | Recreation Attendant | Ride Attendant | Theater Attendant | Venue Attendant | Wardrobe Attendant</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | English Language | Public Safety and Security | Sales and Marketing | Computers and Electronics | Education and Training</t>
+  </si>
+  <si>
+    <t>Contact With Others | Deal With External Customers or the Public in General | Face-to-Face Discussions with Individuals and Within Teams | Physical Proximity | Spend Time Standing | Spend Time Walking or Running | Work With or Contribute to a Work Group or Team | Telephone Conversations | Indoors, Environmentally Controlled | Importance of Repeating Same Tasks | Time Pressure | Dealing With Unpleasant, Angry, or Discourteous People | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Frequency of Decision Making | Freedom to Make Decisions</t>
+  </si>
+  <si>
+    <t>Amusement and Recreation Attendants | Ushers, Lobby Attendants, and Ticket Takers | Costume Attendants | Locker Room, Coatroom, and Dressing Room Attendants | Motion Picture Projectionists | Recreation Workers | Concierges | Tour Guides and Escorts | Travel Guides | Baggage Porters and Bellhops | Cashiers | Counter and Rental Clerks | Customer Service Representatives | Security Guards | Lifeguards, Ski Patrol, and Other Recreational Protective Service Workers | First-Line Supervisors of Entertainment and Recreation Workers, Except Gambling Services | Entertainment and Recreation Managers, Except Gambling | Hosts and Hostesses, Restaurant, Lounge, and Coffee Shop | Reservation and Transportation Ticket Agents and Travel Clerks | Gambling Service Workers, All Other</t>
+  </si>
+  <si>
+    <t>All entertainment attendants and related workers not listed separately.</t>
+  </si>
+  <si>
+    <t>Perform entertainment attendant duties in roles not classified separately. | Greet and direct patrons and provide information about facilities and events. | Sell, collect, and verify tickets, passes, and admissions. | Operate rides, games, projection, or recreational equipment. | Monitor patron activity to enforce safety rules and capacity limits. | Issue, fit, and collect equipment, costumes, or rental items. | Clean and prepare venues, seating areas, and equipment between events. | Respond to patron questions, complaints, and lost-and-found requests. | Assist patrons with disabilities and special seating requirements. | Handle cash and process transactions for admissions and concessions. | Report equipment malfunctions, injuries, and safety concerns. | Assist with crowd control, queue management, and emergency evacuation. | Maintain records of attendance, sales, and equipment usage. | Set up and take down displays, seating, and event materials.</t>
+  </si>
+  <si>
+    <t>39-4011.00</t>
+  </si>
+  <si>
+    <t>Embalmers</t>
+  </si>
+  <si>
+    <t>Embalmer | Licensed Embalmer | Trade Embalmer</t>
+  </si>
+  <si>
+    <t>Belmar &amp; Associates Mortware | Corel WordPerfect Office Suite | Custom Data Systems Sterling Management Software | FPA Software MACCS | HMIS Advantage | Microsoft Excel | Microsoft Office software | Microsoft Word | Twin Tier Technologies MIMS | Web browser software</t>
+  </si>
+  <si>
+    <t>Speaking | Active Listening | Writing | Critical Thinking | Monitoring | Active Learning | Reading Comprehension</t>
+  </si>
+  <si>
+    <t>Customer and Personal Service | Chemistry | Psychology | English Language | Law and Government | Biology | Administration and Management | Administrative | Philosophy and Theology</t>
+  </si>
+  <si>
+    <t>Near Vision | Oral Comprehension | Problem Sensitivity | Arm-Hand Steadiness | Speech Recognition | Oral Expression | Deductive Reasoning | Information Ordering | Speech Clarity | Manual Dexterity | Visualization | Inductive Reasoning | Written Comprehension | Written Expression | Visual Color Discrimination | Trunk Strength | Control Precision | Finger Dexterity</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Indoors, Environmentally Controlled | Time Pressure | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | E-Mail | Deal With External Customers or the Public in General | Importance of Being Exact or Accurate | Contact With Others | Freedom to Make Decisions | Exposed to Disease or Infections | Coordinate or Lead Others in Accomplishing Work Activities | Exposed to Contaminants | Determine Tasks, Priorities and Goals | Exposed to Hazardous Conditions | Physical Proximity | Written Letters and Memos | Work With or Contribute to a Work Group or Team | In an Enclosed Vehicle or Operate Enclosed Equipment | Consequence of Error | Conflict Situations | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Health and Safety of Other Workers | Work Outcomes and Results of Other Workers | Outdoors, Exposed to All Weather Conditions | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Acute Care Nurses | Anesthesiologist Assistants | Coroners | Crematory Operators | Endoscopy Technicians | Funeral Attendants | Funeral Home Managers | Home Health Aides | Licensed Practical and Licensed Vocational Nurses | Morticians, Undertakers, and Funeral Arrangers | Nurse Anesthetists | Nursing Assistants | Occupational Therapy Assistants | Phlebotomists | Physical Therapist Aides | Physical Therapist Assistants | Registered Nurses | Respiratory Therapists | Surgical Assistants | Surgical Technologists</t>
+  </si>
+  <si>
+    <t>Prepare bodies for interment in conformity with legal requirements.</t>
+  </si>
+  <si>
+    <t>Apply cosmetics to impart lifelike appearance to the deceased. | Arrange for transporting the deceased to another state for interment. | Arrange funeral home equipment and perform general maintenance. | Assist coroners at death scenes or at autopsies, file police reports, and testify at inquests or in court, if employed by a coroner. | Assist with placing caskets in hearses and organize cemetery processions. | Attach trocar to pump-tube, start pump, and repeat probing to force embalming fluid into organs. | Clean and disinfect areas in which bodies are prepared and embalmed. | Close incisions, using needles and sutures. | Conduct interviews to arrange for the preparation of obituary notices, to assist with the selection of caskets or urns, and to determine the location and time of burials or cremations. | Conform to laws of health and sanitation and ensure that legal requirements concerning embalming are met. | Direct casket and floral display placement and arrange guest seating. | Dress bodies and place them in caskets. | Incise stomach and abdominal walls and probe internal organs, using trocar, to withdraw blood and waste matter from organs. | Insert convex celluloid or cotton between eyeballs and eyelids to prevent slipping and sinking of eyelids. | Join lips, using needles and thread or wire. | Maintain records, such as itemized lists of clothing or valuables delivered with body and names of persons embalmed. | Make incisions in arms or thighs and drain blood from circulatory system and replace it with embalming fluid, using pump. | Pack body orifices with cotton saturated with embalming fluid to prevent escape of gases or waste matter. | Perform special procedures necessary for remains that are to be transported to other states or overseas, or where death was caused by infectious disease. | Perform the duties of funeral directors, including coordinating funeral activities. | Press diaphragm to evacuate air from lungs. | Remove the deceased from place of death and transport to funeral home. | Reshape or reconstruct disfigured or maimed bodies when necessary, using dermasurgery techniques and materials such as clay, cotton, plaster of Paris, and wax. | Serve as pallbearers, attend visiting rooms, and provide other assistance to the bereaved. | Supervise funeral attendants and other funeral home staff. | Wash and dry bodies, using germicidal soap and towels or hot air dryers.</t>
+  </si>
+  <si>
+    <t>39-4012.00</t>
+  </si>
+  <si>
+    <t>Crematory Operators</t>
+  </si>
+  <si>
+    <t>Crematorium Operator | Crematory Attendant | Crematory Manager | Crematory Operator | Crematory Technician | Cremation Specialist | Cremation Technician | Funeral Services Technician | Retort Operator | Cremationist</t>
+  </si>
+  <si>
+    <t>Belmar &amp; Associates Mortware | HMIS Advantage | Microsoft Excel | Microsoft Office software | Microsoft Word</t>
+  </si>
+  <si>
+    <t>Public Safety and Security | Customer and Personal Service | Mechanical | English Language | Law and Government | Chemistry | Administration and Management</t>
+  </si>
+  <si>
+    <t>Manual Dexterity | Finger Dexterity | Arm-Hand Steadiness | Multilimb Coordination | Control Precision | Static Strength | Trunk Strength | Stamina | Near Vision | Far Vision | Depth Perception | Gross Body Coordination | Gross Body Equilibrium | Extent Flexibility | Reaction Time | Problem Sensitivity | Oral Comprehension | Selective Attention | Written Comprehension | Information Ordering</t>
+  </si>
+  <si>
+    <t>Indoors, Not Environmentally Controlled | Exposed to Very Hot or Cold Temperatures | Exposed to Contaminants | Exposed to Hazardous Equipment | Exposed to Hazardous Conditions | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Being Exact or Accurate | Consequence of Error | Importance of Repeating Same Tasks | Health and Safety of Other Workers | Face-to-Face Discussions with Individuals and Within Teams | Deal With External Customers or the Public in General | Contact With Others | Telephone Conversations | Freedom to Make Decisions | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable</t>
+  </si>
+  <si>
+    <t>Animal Caretakers | Coroners | Embalmers | Excavating and Loading Machine and Dragline Operators, Surface Mining | Floral Designers | Funeral Attendants | Funeral Home Managers | Hazardous Materials Removal Workers | Home Health Aides | Laundry and Dry-Cleaning Workers | Maids and Housekeeping Cleaners | Maintenance Workers, Machinery | Medical Equipment Preparers | Morticians, Undertakers, and Funeral Arrangers | Orderlies | Personal Care Aides | Recycling and Reclamation Workers | Surgical Technologists | Veterinary Assistants and Laboratory Animal Caretakers | Veterinary Technologists and Technicians</t>
+  </si>
+  <si>
+    <t>Operate crematory equipment to reduce human or animal remains to bone fragments in accordance with state and local regulations. Duties may include preparing the body for cremation and performing general maintenance on crematory equipment. May use traditional flame-based cremation, calcination, or alkaline hydrolysis.</t>
+  </si>
+  <si>
+    <t>Clean the crematorium, including tables, floors, and equipment. | Document divided remains to ensure parts are not misplaced. | Embalm, dress, or otherwise prepare the deceased for viewing. | Explain the cremation process to family or friends of the deceased. | Offer counsel and comfort to bereaved families or friends. | Pick up and handle human or pet remains in a respectful manner. | Place corpses into crematory machines to reduce remains to bone fragments using flame, heat, or alkaline hydrolysis. | Pulverize remaining bone fragments into smaller pieces, using specialized equipment, such as a cremulator or grinder. | Read documentation to confirm the identity of the deceased. | Remove jewelry, watches, or other personal items from the deceased prior to cremation. | Sweep or vacuum the cremation chamber to retrieve remains for storage in an urn or other container. | Transport the deceased to a funeral home or crematory using a van, hearse, or other vehicle.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -330,10 +1907,1761 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" t="s">
+        <v>62</v>
+      </c>
+      <c r="J6" t="s">
+        <v>63</v>
+      </c>
+      <c r="K6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J7" t="s">
+        <v>74</v>
+      </c>
+      <c r="K7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J8" t="s">
+        <v>85</v>
+      </c>
+      <c r="K8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H9" t="s">
+        <v>94</v>
+      </c>
+      <c r="I9" t="s">
+        <v>95</v>
+      </c>
+      <c r="J9" t="s">
+        <v>96</v>
+      </c>
+      <c r="K9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F10" t="s">
+        <v>103</v>
+      </c>
+      <c r="G10" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" t="s">
+        <v>105</v>
+      </c>
+      <c r="I10" t="s">
+        <v>106</v>
+      </c>
+      <c r="J10" t="s">
+        <v>107</v>
+      </c>
+      <c r="K10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G11" t="s">
+        <v>115</v>
+      </c>
+      <c r="H11" t="s">
+        <v>116</v>
+      </c>
+      <c r="I11" t="s">
+        <v>117</v>
+      </c>
+      <c r="J11" t="s">
+        <v>118</v>
+      </c>
+      <c r="K11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E12" t="s">
+        <v>124</v>
+      </c>
+      <c r="F12" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12" t="s">
+        <v>126</v>
+      </c>
+      <c r="H12" t="s">
+        <v>127</v>
+      </c>
+      <c r="I12" t="s">
+        <v>128</v>
+      </c>
+      <c r="J12" t="s">
+        <v>129</v>
+      </c>
+      <c r="K12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E13" t="s">
+        <v>135</v>
+      </c>
+      <c r="F13" t="s">
+        <v>136</v>
+      </c>
+      <c r="G13" t="s">
+        <v>137</v>
+      </c>
+      <c r="H13" t="s">
+        <v>138</v>
+      </c>
+      <c r="I13" t="s">
+        <v>139</v>
+      </c>
+      <c r="J13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" t="s">
+        <v>145</v>
+      </c>
+      <c r="E14" t="s">
+        <v>146</v>
+      </c>
+      <c r="F14" t="s">
+        <v>147</v>
+      </c>
+      <c r="G14" t="s">
+        <v>148</v>
+      </c>
+      <c r="H14" t="s">
+        <v>149</v>
+      </c>
+      <c r="I14" t="s">
+        <v>150</v>
+      </c>
+      <c r="J14" t="s">
+        <v>151</v>
+      </c>
+      <c r="K14" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>153</v>
+      </c>
+      <c r="B15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C15" t="s">
+        <v>155</v>
+      </c>
+      <c r="D15" t="s">
+        <v>156</v>
+      </c>
+      <c r="E15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" t="s">
+        <v>157</v>
+      </c>
+      <c r="G15" t="s">
+        <v>158</v>
+      </c>
+      <c r="H15" t="s">
+        <v>159</v>
+      </c>
+      <c r="I15" t="s">
+        <v>160</v>
+      </c>
+      <c r="J15" t="s">
+        <v>161</v>
+      </c>
+      <c r="K15" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B16" t="s">
+        <v>164</v>
+      </c>
+      <c r="C16" t="s">
+        <v>165</v>
+      </c>
+      <c r="D16" t="s">
+        <v>166</v>
+      </c>
+      <c r="E16" t="s">
+        <v>167</v>
+      </c>
+      <c r="F16" t="s">
+        <v>168</v>
+      </c>
+      <c r="G16" t="s">
+        <v>169</v>
+      </c>
+      <c r="H16" t="s">
+        <v>170</v>
+      </c>
+      <c r="I16" t="s">
+        <v>171</v>
+      </c>
+      <c r="J16" t="s">
+        <v>172</v>
+      </c>
+      <c r="K16" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>174</v>
+      </c>
+      <c r="B17" t="s">
+        <v>175</v>
+      </c>
+      <c r="C17" t="s">
+        <v>176</v>
+      </c>
+      <c r="D17" t="s">
+        <v>177</v>
+      </c>
+      <c r="E17" t="s">
+        <v>91</v>
+      </c>
+      <c r="F17" t="s">
+        <v>178</v>
+      </c>
+      <c r="G17" t="s">
+        <v>179</v>
+      </c>
+      <c r="H17" t="s">
+        <v>180</v>
+      </c>
+      <c r="I17" t="s">
+        <v>181</v>
+      </c>
+      <c r="J17" t="s">
+        <v>182</v>
+      </c>
+      <c r="K17" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>184</v>
+      </c>
+      <c r="B18" t="s">
+        <v>185</v>
+      </c>
+      <c r="C18" t="s">
+        <v>186</v>
+      </c>
+      <c r="D18" t="s">
+        <v>187</v>
+      </c>
+      <c r="E18" t="s">
+        <v>188</v>
+      </c>
+      <c r="F18" t="s">
+        <v>189</v>
+      </c>
+      <c r="G18" t="s">
+        <v>190</v>
+      </c>
+      <c r="H18" t="s">
+        <v>191</v>
+      </c>
+      <c r="I18" t="s">
+        <v>192</v>
+      </c>
+      <c r="J18" t="s">
+        <v>193</v>
+      </c>
+      <c r="K18" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>195</v>
+      </c>
+      <c r="B19" t="s">
+        <v>196</v>
+      </c>
+      <c r="C19" t="s">
+        <v>197</v>
+      </c>
+      <c r="D19" t="s">
+        <v>198</v>
+      </c>
+      <c r="E19" t="s">
+        <v>199</v>
+      </c>
+      <c r="F19" t="s">
+        <v>189</v>
+      </c>
+      <c r="G19" t="s">
+        <v>200</v>
+      </c>
+      <c r="H19" t="s">
+        <v>201</v>
+      </c>
+      <c r="I19" t="s">
+        <v>202</v>
+      </c>
+      <c r="J19" t="s">
+        <v>203</v>
+      </c>
+      <c r="K19" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>205</v>
+      </c>
+      <c r="B20" t="s">
+        <v>206</v>
+      </c>
+      <c r="C20" t="s">
+        <v>207</v>
+      </c>
+      <c r="D20" t="s">
+        <v>208</v>
+      </c>
+      <c r="E20" t="s">
+        <v>209</v>
+      </c>
+      <c r="F20" t="s">
+        <v>210</v>
+      </c>
+      <c r="G20" t="s">
+        <v>211</v>
+      </c>
+      <c r="H20" t="s">
+        <v>212</v>
+      </c>
+      <c r="I20" t="s">
+        <v>213</v>
+      </c>
+      <c r="J20" t="s">
+        <v>214</v>
+      </c>
+      <c r="K20" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>216</v>
+      </c>
+      <c r="B21" t="s">
+        <v>217</v>
+      </c>
+      <c r="C21" t="s">
+        <v>218</v>
+      </c>
+      <c r="D21" t="s">
+        <v>219</v>
+      </c>
+      <c r="E21" t="s">
+        <v>91</v>
+      </c>
+      <c r="F21" t="s">
+        <v>220</v>
+      </c>
+      <c r="G21" t="s">
+        <v>221</v>
+      </c>
+      <c r="H21" t="s">
+        <v>222</v>
+      </c>
+      <c r="I21" t="s">
+        <v>223</v>
+      </c>
+      <c r="J21" t="s">
+        <v>224</v>
+      </c>
+      <c r="K21" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>226</v>
+      </c>
+      <c r="B22" t="s">
+        <v>227</v>
+      </c>
+      <c r="C22" t="s">
+        <v>228</v>
+      </c>
+      <c r="D22" t="s">
+        <v>229</v>
+      </c>
+      <c r="E22" t="s">
+        <v>230</v>
+      </c>
+      <c r="F22" t="s">
+        <v>231</v>
+      </c>
+      <c r="G22" t="s">
+        <v>232</v>
+      </c>
+      <c r="H22" t="s">
+        <v>233</v>
+      </c>
+      <c r="I22" t="s">
+        <v>234</v>
+      </c>
+      <c r="J22" t="s">
+        <v>235</v>
+      </c>
+      <c r="K22" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>237</v>
+      </c>
+      <c r="B23" t="s">
+        <v>238</v>
+      </c>
+      <c r="C23" t="s">
+        <v>239</v>
+      </c>
+      <c r="D23" t="s">
+        <v>240</v>
+      </c>
+      <c r="E23" t="s">
+        <v>241</v>
+      </c>
+      <c r="F23" t="s">
+        <v>242</v>
+      </c>
+      <c r="G23" t="s">
+        <v>243</v>
+      </c>
+      <c r="H23" t="s">
+        <v>244</v>
+      </c>
+      <c r="I23" t="s">
+        <v>245</v>
+      </c>
+      <c r="J23" t="s">
+        <v>246</v>
+      </c>
+      <c r="K23" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>248</v>
+      </c>
+      <c r="B24" t="s">
+        <v>249</v>
+      </c>
+      <c r="C24" t="s">
+        <v>250</v>
+      </c>
+      <c r="D24" t="s">
+        <v>145</v>
+      </c>
+      <c r="E24" t="s">
+        <v>146</v>
+      </c>
+      <c r="F24" t="s">
+        <v>251</v>
+      </c>
+      <c r="G24" t="s">
+        <v>252</v>
+      </c>
+      <c r="H24" t="s">
+        <v>253</v>
+      </c>
+      <c r="I24" t="s">
+        <v>254</v>
+      </c>
+      <c r="J24" t="s">
+        <v>255</v>
+      </c>
+      <c r="K24" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>257</v>
+      </c>
+      <c r="B25" t="s">
+        <v>258</v>
+      </c>
+      <c r="C25" t="s">
+        <v>259</v>
+      </c>
+      <c r="D25" t="s">
+        <v>260</v>
+      </c>
+      <c r="E25" t="s">
+        <v>261</v>
+      </c>
+      <c r="F25" t="s">
+        <v>262</v>
+      </c>
+      <c r="G25" t="s">
+        <v>263</v>
+      </c>
+      <c r="H25" t="s">
+        <v>264</v>
+      </c>
+      <c r="I25" t="s">
+        <v>265</v>
+      </c>
+      <c r="J25" t="s">
+        <v>266</v>
+      </c>
+      <c r="K25" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>268</v>
+      </c>
+      <c r="B26" t="s">
+        <v>269</v>
+      </c>
+      <c r="C26" t="s">
+        <v>270</v>
+      </c>
+      <c r="D26" t="s">
+        <v>271</v>
+      </c>
+      <c r="E26" t="s">
+        <v>272</v>
+      </c>
+      <c r="F26" t="s">
+        <v>273</v>
+      </c>
+      <c r="G26" t="s">
+        <v>274</v>
+      </c>
+      <c r="H26" t="s">
+        <v>275</v>
+      </c>
+      <c r="I26" t="s">
+        <v>276</v>
+      </c>
+      <c r="J26" t="s">
+        <v>277</v>
+      </c>
+      <c r="K26" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>279</v>
+      </c>
+      <c r="B27" t="s">
+        <v>280</v>
+      </c>
+      <c r="C27" t="s">
+        <v>281</v>
+      </c>
+      <c r="D27" t="s">
+        <v>282</v>
+      </c>
+      <c r="E27" t="s">
+        <v>209</v>
+      </c>
+      <c r="F27" t="s">
+        <v>283</v>
+      </c>
+      <c r="G27" t="s">
+        <v>284</v>
+      </c>
+      <c r="H27" t="s">
+        <v>285</v>
+      </c>
+      <c r="I27" t="s">
+        <v>286</v>
+      </c>
+      <c r="J27" t="s">
+        <v>287</v>
+      </c>
+      <c r="K27" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>289</v>
+      </c>
+      <c r="B28" t="s">
+        <v>290</v>
+      </c>
+      <c r="C28" t="s">
+        <v>291</v>
+      </c>
+      <c r="D28" t="s">
+        <v>292</v>
+      </c>
+      <c r="E28" t="s">
+        <v>36</v>
+      </c>
+      <c r="F28" t="s">
+        <v>293</v>
+      </c>
+      <c r="G28" t="s">
+        <v>294</v>
+      </c>
+      <c r="H28" t="s">
+        <v>295</v>
+      </c>
+      <c r="I28" t="s">
+        <v>296</v>
+      </c>
+      <c r="J28" t="s">
+        <v>297</v>
+      </c>
+      <c r="K28" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>299</v>
+      </c>
+      <c r="B29" t="s">
+        <v>300</v>
+      </c>
+      <c r="C29" t="s">
+        <v>301</v>
+      </c>
+      <c r="D29" t="s">
+        <v>145</v>
+      </c>
+      <c r="E29" t="s">
+        <v>146</v>
+      </c>
+      <c r="F29" t="s">
+        <v>302</v>
+      </c>
+      <c r="G29" t="s">
+        <v>303</v>
+      </c>
+      <c r="H29" t="s">
+        <v>304</v>
+      </c>
+      <c r="I29" t="s">
+        <v>305</v>
+      </c>
+      <c r="J29" t="s">
+        <v>306</v>
+      </c>
+      <c r="K29" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>308</v>
+      </c>
+      <c r="B30" t="s">
+        <v>309</v>
+      </c>
+      <c r="C30" t="s">
+        <v>310</v>
+      </c>
+      <c r="D30" t="s">
+        <v>311</v>
+      </c>
+      <c r="E30" t="s">
+        <v>312</v>
+      </c>
+      <c r="F30" t="s">
+        <v>313</v>
+      </c>
+      <c r="G30" t="s">
+        <v>314</v>
+      </c>
+      <c r="H30" t="s">
+        <v>315</v>
+      </c>
+      <c r="I30" t="s">
+        <v>316</v>
+      </c>
+      <c r="J30" t="s">
+        <v>317</v>
+      </c>
+      <c r="K30" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>319</v>
+      </c>
+      <c r="B31" t="s">
+        <v>320</v>
+      </c>
+      <c r="C31" t="s">
+        <v>321</v>
+      </c>
+      <c r="D31" t="s">
+        <v>322</v>
+      </c>
+      <c r="E31" t="s">
+        <v>146</v>
+      </c>
+      <c r="F31" t="s">
+        <v>323</v>
+      </c>
+      <c r="G31" t="s">
+        <v>324</v>
+      </c>
+      <c r="H31" t="s">
+        <v>325</v>
+      </c>
+      <c r="I31" t="s">
+        <v>326</v>
+      </c>
+      <c r="J31" t="s">
+        <v>327</v>
+      </c>
+      <c r="K31" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>329</v>
+      </c>
+      <c r="B32" t="s">
+        <v>330</v>
+      </c>
+      <c r="C32" t="s">
+        <v>331</v>
+      </c>
+      <c r="D32" t="s">
+        <v>332</v>
+      </c>
+      <c r="E32" t="s">
+        <v>333</v>
+      </c>
+      <c r="F32" t="s">
+        <v>334</v>
+      </c>
+      <c r="G32" t="s">
+        <v>335</v>
+      </c>
+      <c r="H32" t="s">
+        <v>336</v>
+      </c>
+      <c r="I32" t="s">
+        <v>337</v>
+      </c>
+      <c r="J32" t="s">
+        <v>338</v>
+      </c>
+      <c r="K32" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>340</v>
+      </c>
+      <c r="B33" t="s">
+        <v>341</v>
+      </c>
+      <c r="C33" t="s">
+        <v>342</v>
+      </c>
+      <c r="D33" t="s">
+        <v>343</v>
+      </c>
+      <c r="E33" t="s">
+        <v>344</v>
+      </c>
+      <c r="F33" t="s">
+        <v>345</v>
+      </c>
+      <c r="G33" t="s">
+        <v>346</v>
+      </c>
+      <c r="H33" t="s">
+        <v>347</v>
+      </c>
+      <c r="I33" t="s">
+        <v>348</v>
+      </c>
+      <c r="J33" t="s">
+        <v>349</v>
+      </c>
+      <c r="K33" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>351</v>
+      </c>
+      <c r="B34" t="s">
+        <v>352</v>
+      </c>
+      <c r="C34" t="s">
+        <v>353</v>
+      </c>
+      <c r="D34" t="s">
+        <v>145</v>
+      </c>
+      <c r="E34" t="s">
+        <v>146</v>
+      </c>
+      <c r="F34" t="s">
+        <v>354</v>
+      </c>
+      <c r="G34" t="s">
+        <v>303</v>
+      </c>
+      <c r="H34" t="s">
+        <v>355</v>
+      </c>
+      <c r="I34" t="s">
+        <v>356</v>
+      </c>
+      <c r="J34" t="s">
+        <v>357</v>
+      </c>
+      <c r="K34" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>359</v>
+      </c>
+      <c r="B35" t="s">
+        <v>360</v>
+      </c>
+      <c r="C35" t="s">
+        <v>361</v>
+      </c>
+      <c r="D35" t="s">
+        <v>362</v>
+      </c>
+      <c r="E35" t="s">
+        <v>363</v>
+      </c>
+      <c r="F35" t="s">
+        <v>364</v>
+      </c>
+      <c r="G35" t="s">
+        <v>365</v>
+      </c>
+      <c r="H35" t="s">
+        <v>366</v>
+      </c>
+      <c r="I35" t="s">
+        <v>367</v>
+      </c>
+      <c r="J35" t="s">
+        <v>368</v>
+      </c>
+      <c r="K35" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>370</v>
+      </c>
+      <c r="B36" t="s">
+        <v>371</v>
+      </c>
+      <c r="C36" t="s">
+        <v>372</v>
+      </c>
+      <c r="D36" t="s">
+        <v>373</v>
+      </c>
+      <c r="E36" t="s">
+        <v>374</v>
+      </c>
+      <c r="F36" t="s">
+        <v>375</v>
+      </c>
+      <c r="G36" t="s">
+        <v>376</v>
+      </c>
+      <c r="H36" t="s">
+        <v>377</v>
+      </c>
+      <c r="I36" t="s">
+        <v>378</v>
+      </c>
+      <c r="J36" t="s">
+        <v>379</v>
+      </c>
+      <c r="K36" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>381</v>
+      </c>
+      <c r="B37" t="s">
+        <v>382</v>
+      </c>
+      <c r="C37" t="s">
+        <v>383</v>
+      </c>
+      <c r="D37" t="s">
+        <v>373</v>
+      </c>
+      <c r="E37" t="s">
+        <v>384</v>
+      </c>
+      <c r="F37" t="s">
+        <v>385</v>
+      </c>
+      <c r="G37" t="s">
+        <v>386</v>
+      </c>
+      <c r="H37" t="s">
+        <v>387</v>
+      </c>
+      <c r="I37" t="s">
+        <v>388</v>
+      </c>
+      <c r="J37" t="s">
+        <v>389</v>
+      </c>
+      <c r="K37" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>391</v>
+      </c>
+      <c r="B38" t="s">
+        <v>392</v>
+      </c>
+      <c r="C38" t="s">
+        <v>393</v>
+      </c>
+      <c r="D38" t="s">
+        <v>394</v>
+      </c>
+      <c r="E38" t="s">
+        <v>395</v>
+      </c>
+      <c r="F38" t="s">
+        <v>396</v>
+      </c>
+      <c r="G38" t="s">
+        <v>397</v>
+      </c>
+      <c r="H38" t="s">
+        <v>398</v>
+      </c>
+      <c r="I38" t="s">
+        <v>399</v>
+      </c>
+      <c r="J38" t="s">
+        <v>400</v>
+      </c>
+      <c r="K38" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>402</v>
+      </c>
+      <c r="B39" t="s">
+        <v>403</v>
+      </c>
+      <c r="C39" t="s">
+        <v>404</v>
+      </c>
+      <c r="D39" t="s">
+        <v>405</v>
+      </c>
+      <c r="E39" t="s">
+        <v>406</v>
+      </c>
+      <c r="F39" t="s">
+        <v>407</v>
+      </c>
+      <c r="G39" t="s">
+        <v>408</v>
+      </c>
+      <c r="H39" t="s">
+        <v>409</v>
+      </c>
+      <c r="I39" t="s">
+        <v>410</v>
+      </c>
+      <c r="J39" t="s">
+        <v>411</v>
+      </c>
+      <c r="K39" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>413</v>
+      </c>
+      <c r="B40" t="s">
+        <v>414</v>
+      </c>
+      <c r="C40" t="s">
+        <v>415</v>
+      </c>
+      <c r="D40" t="s">
+        <v>416</v>
+      </c>
+      <c r="E40" t="s">
+        <v>417</v>
+      </c>
+      <c r="F40" t="s">
+        <v>418</v>
+      </c>
+      <c r="G40" t="s">
+        <v>419</v>
+      </c>
+      <c r="H40" t="s">
+        <v>420</v>
+      </c>
+      <c r="I40" t="s">
+        <v>421</v>
+      </c>
+      <c r="J40" t="s">
+        <v>422</v>
+      </c>
+      <c r="K40" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>424</v>
+      </c>
+      <c r="B41" t="s">
+        <v>425</v>
+      </c>
+      <c r="C41" t="s">
+        <v>426</v>
+      </c>
+      <c r="D41" t="s">
+        <v>427</v>
+      </c>
+      <c r="E41" t="s">
+        <v>428</v>
+      </c>
+      <c r="F41" t="s">
+        <v>429</v>
+      </c>
+      <c r="G41" t="s">
+        <v>430</v>
+      </c>
+      <c r="H41" t="s">
+        <v>431</v>
+      </c>
+      <c r="I41" t="s">
+        <v>432</v>
+      </c>
+      <c r="J41" t="s">
+        <v>433</v>
+      </c>
+      <c r="K41" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>435</v>
+      </c>
+      <c r="B42" t="s">
+        <v>436</v>
+      </c>
+      <c r="C42" t="s">
+        <v>437</v>
+      </c>
+      <c r="D42" t="s">
+        <v>145</v>
+      </c>
+      <c r="E42" t="s">
+        <v>47</v>
+      </c>
+      <c r="F42" t="s">
+        <v>438</v>
+      </c>
+      <c r="G42" t="s">
+        <v>439</v>
+      </c>
+      <c r="H42" t="s">
+        <v>440</v>
+      </c>
+      <c r="I42" t="s">
+        <v>441</v>
+      </c>
+      <c r="J42" t="s">
+        <v>442</v>
+      </c>
+      <c r="K42" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>444</v>
+      </c>
+      <c r="B43" t="s">
+        <v>445</v>
+      </c>
+      <c r="C43" t="s">
+        <v>446</v>
+      </c>
+      <c r="D43" t="s">
+        <v>447</v>
+      </c>
+      <c r="E43" t="s">
+        <v>448</v>
+      </c>
+      <c r="F43" t="s">
+        <v>449</v>
+      </c>
+      <c r="G43" t="s">
+        <v>450</v>
+      </c>
+      <c r="H43" t="s">
+        <v>451</v>
+      </c>
+      <c r="I43" t="s">
+        <v>452</v>
+      </c>
+      <c r="J43" t="s">
+        <v>453</v>
+      </c>
+      <c r="K43" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>455</v>
+      </c>
+      <c r="B44" t="s">
+        <v>456</v>
+      </c>
+      <c r="C44" t="s">
+        <v>457</v>
+      </c>
+      <c r="D44" t="s">
+        <v>458</v>
+      </c>
+      <c r="E44" t="s">
+        <v>209</v>
+      </c>
+      <c r="F44" t="s">
+        <v>459</v>
+      </c>
+      <c r="G44" t="s">
+        <v>460</v>
+      </c>
+      <c r="H44" t="s">
+        <v>461</v>
+      </c>
+      <c r="I44" t="s">
+        <v>462</v>
+      </c>
+      <c r="J44" t="s">
+        <v>463</v>
+      </c>
+      <c r="K44" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>465</v>
+      </c>
+      <c r="B45" t="s">
+        <v>466</v>
+      </c>
+      <c r="C45" t="s">
+        <v>467</v>
+      </c>
+      <c r="D45" t="s">
+        <v>468</v>
+      </c>
+      <c r="E45" t="s">
+        <v>209</v>
+      </c>
+      <c r="F45" t="s">
+        <v>293</v>
+      </c>
+      <c r="G45" t="s">
+        <v>469</v>
+      </c>
+      <c r="H45" t="s">
+        <v>470</v>
+      </c>
+      <c r="I45" t="s">
+        <v>471</v>
+      </c>
+      <c r="J45" t="s">
+        <v>472</v>
+      </c>
+      <c r="K45" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>474</v>
+      </c>
+      <c r="B46" t="s">
+        <v>475</v>
+      </c>
+      <c r="C46" t="s">
+        <v>476</v>
+      </c>
+      <c r="D46" t="s">
+        <v>477</v>
+      </c>
+      <c r="E46" t="s">
+        <v>199</v>
+      </c>
+      <c r="F46" t="s">
+        <v>478</v>
+      </c>
+      <c r="G46" t="s">
+        <v>479</v>
+      </c>
+      <c r="H46" t="s">
+        <v>480</v>
+      </c>
+      <c r="I46" t="s">
+        <v>481</v>
+      </c>
+      <c r="J46" t="s">
+        <v>482</v>
+      </c>
+      <c r="K46" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>484</v>
+      </c>
+      <c r="B47" t="s">
+        <v>485</v>
+      </c>
+      <c r="C47" t="s">
+        <v>486</v>
+      </c>
+      <c r="D47" t="s">
+        <v>487</v>
+      </c>
+      <c r="E47" t="s">
+        <v>209</v>
+      </c>
+      <c r="F47" t="s">
+        <v>242</v>
+      </c>
+      <c r="G47" t="s">
+        <v>488</v>
+      </c>
+      <c r="H47" t="s">
+        <v>489</v>
+      </c>
+      <c r="I47" t="s">
+        <v>490</v>
+      </c>
+      <c r="J47" t="s">
+        <v>491</v>
+      </c>
+      <c r="K47" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>493</v>
+      </c>
+      <c r="B48" t="s">
+        <v>494</v>
+      </c>
+      <c r="C48" t="s">
+        <v>495</v>
+      </c>
+      <c r="D48" t="s">
+        <v>145</v>
+      </c>
+      <c r="E48" t="s">
+        <v>47</v>
+      </c>
+      <c r="F48" t="s">
+        <v>496</v>
+      </c>
+      <c r="G48" t="s">
+        <v>439</v>
+      </c>
+      <c r="H48" t="s">
+        <v>497</v>
+      </c>
+      <c r="I48" t="s">
+        <v>498</v>
+      </c>
+      <c r="J48" t="s">
+        <v>499</v>
+      </c>
+      <c r="K48" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>501</v>
+      </c>
+      <c r="B49" t="s">
+        <v>502</v>
+      </c>
+      <c r="C49" t="s">
+        <v>503</v>
+      </c>
+      <c r="D49" t="s">
+        <v>504</v>
+      </c>
+      <c r="E49" t="s">
+        <v>505</v>
+      </c>
+      <c r="F49" t="s">
+        <v>506</v>
+      </c>
+      <c r="G49" t="s">
+        <v>507</v>
+      </c>
+      <c r="H49" t="s">
+        <v>508</v>
+      </c>
+      <c r="I49" t="s">
+        <v>509</v>
+      </c>
+      <c r="J49" t="s">
+        <v>510</v>
+      </c>
+      <c r="K49" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>512</v>
+      </c>
+      <c r="B50" t="s">
+        <v>513</v>
+      </c>
+      <c r="C50" t="s">
+        <v>514</v>
+      </c>
+      <c r="D50" t="s">
+        <v>515</v>
+      </c>
+      <c r="E50" t="s">
+        <v>146</v>
+      </c>
+      <c r="F50" t="s">
+        <v>516</v>
+      </c>
+      <c r="G50" t="s">
+        <v>517</v>
+      </c>
+      <c r="H50" t="s">
+        <v>518</v>
+      </c>
+      <c r="I50" t="s">
+        <v>519</v>
+      </c>
+      <c r="J50" t="s">
+        <v>520</v>
+      </c>
+      <c r="K50" t="s">
+        <v>521</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>